--- a/NV Play Midweek League bowling stats for season.xlsx
+++ b/NV Play Midweek League bowling stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4419" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4667" uniqueCount="581">
   <si>
     <t>Group</t>
   </si>
@@ -1730,6 +1730,39 @@
   <si>
     <t>Anu Pillai</t>
   </si>
+  <si>
+    <t>Cliftonville Academy MW XI v Dunmurry MW2 XI, TBC - 16 July 2026</t>
+  </si>
+  <si>
+    <t>Suryakrishna Saneesh</t>
+  </si>
+  <si>
+    <t>Belfast Superkings MW XI v BISC MW XI, TBC - 16 July 2026</t>
+  </si>
+  <si>
+    <t>NIMACC MW XI v Dunmurry MW1 XI, TBC - 16 July 2026</t>
+  </si>
+  <si>
+    <t>Yashvanth Annaiah Vijayalakshmi</t>
+  </si>
+  <si>
+    <t>Lokesh Gehani</t>
+  </si>
+  <si>
+    <t>Jaibin Jacob</t>
+  </si>
+  <si>
+    <t>Cregagh MW XI v Ardent Blues MW2 XI, Cregagh Memorial Recreation Ground - 17 July 2026</t>
+  </si>
+  <si>
+    <t>Sonu Soman</t>
+  </si>
+  <si>
+    <t>Sandeep Ganesh Srinivasan</t>
+  </si>
+  <si>
+    <t>Harry Stone</t>
+  </si>
 </sst>
 </file>
 
@@ -2537,7 +2570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U910"/>
+  <dimension ref="A1:U959"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="69.28515625" bestFit="1" customWidth="1"/>
@@ -59331,6 +59364,3035 @@
         <v>24</v>
       </c>
     </row>
+    <row r="911" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A911" t="s">
+        <v>570</v>
+      </c>
+      <c r="B911" t="s">
+        <v>114</v>
+      </c>
+      <c r="C911">
+        <v>1</v>
+      </c>
+      <c r="D911">
+        <v>1</v>
+      </c>
+      <c r="E911">
+        <v>4</v>
+      </c>
+      <c r="F911">
+        <v>0</v>
+      </c>
+      <c r="G911">
+        <v>22</v>
+      </c>
+      <c r="H911">
+        <v>1</v>
+      </c>
+      <c r="I911">
+        <v>22</v>
+      </c>
+      <c r="J911">
+        <v>5.5</v>
+      </c>
+      <c r="K911">
+        <v>0</v>
+      </c>
+      <c r="L911">
+        <v>0</v>
+      </c>
+      <c r="M911" s="1">
+        <v>44562</v>
+      </c>
+      <c r="N911" s="1">
+        <v>44562</v>
+      </c>
+      <c r="O911">
+        <v>24</v>
+      </c>
+      <c r="P911">
+        <v>12</v>
+      </c>
+      <c r="Q911">
+        <v>2</v>
+      </c>
+      <c r="R911">
+        <v>0</v>
+      </c>
+      <c r="S911" t="s">
+        <v>31</v>
+      </c>
+      <c r="T911" t="s">
+        <v>24</v>
+      </c>
+      <c r="U911">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="912" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A912" t="s">
+        <v>570</v>
+      </c>
+      <c r="B912" t="s">
+        <v>520</v>
+      </c>
+      <c r="C912">
+        <v>1</v>
+      </c>
+      <c r="D912">
+        <v>1</v>
+      </c>
+      <c r="E912">
+        <v>3</v>
+      </c>
+      <c r="F912">
+        <v>0</v>
+      </c>
+      <c r="G912">
+        <v>35</v>
+      </c>
+      <c r="H912">
+        <v>1</v>
+      </c>
+      <c r="I912">
+        <v>35</v>
+      </c>
+      <c r="J912">
+        <v>11.67</v>
+      </c>
+      <c r="K912">
+        <v>0</v>
+      </c>
+      <c r="L912">
+        <v>0</v>
+      </c>
+      <c r="M912" s="1">
+        <v>12785</v>
+      </c>
+      <c r="N912" s="1">
+        <v>12785</v>
+      </c>
+      <c r="O912">
+        <v>18</v>
+      </c>
+      <c r="P912">
+        <v>4</v>
+      </c>
+      <c r="Q912">
+        <v>4</v>
+      </c>
+      <c r="R912">
+        <v>0</v>
+      </c>
+      <c r="S912" t="s">
+        <v>34</v>
+      </c>
+      <c r="T912" t="s">
+        <v>24</v>
+      </c>
+      <c r="U912">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="913" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A913" t="s">
+        <v>570</v>
+      </c>
+      <c r="B913" t="s">
+        <v>271</v>
+      </c>
+      <c r="C913">
+        <v>1</v>
+      </c>
+      <c r="D913">
+        <v>1</v>
+      </c>
+      <c r="E913">
+        <v>4</v>
+      </c>
+      <c r="F913">
+        <v>0</v>
+      </c>
+      <c r="G913">
+        <v>37</v>
+      </c>
+      <c r="H913">
+        <v>3</v>
+      </c>
+      <c r="I913">
+        <v>12.33</v>
+      </c>
+      <c r="J913">
+        <v>9.25</v>
+      </c>
+      <c r="K913">
+        <v>0</v>
+      </c>
+      <c r="L913">
+        <v>0</v>
+      </c>
+      <c r="M913" s="1">
+        <v>13575</v>
+      </c>
+      <c r="N913" s="1">
+        <v>13575</v>
+      </c>
+      <c r="O913">
+        <v>24</v>
+      </c>
+      <c r="P913">
+        <v>11</v>
+      </c>
+      <c r="Q913">
+        <v>6</v>
+      </c>
+      <c r="R913">
+        <v>0</v>
+      </c>
+      <c r="S913" t="s">
+        <v>40</v>
+      </c>
+      <c r="T913" t="s">
+        <v>129</v>
+      </c>
+      <c r="U913">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="914" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A914" t="s">
+        <v>570</v>
+      </c>
+      <c r="B914" t="s">
+        <v>465</v>
+      </c>
+      <c r="C914">
+        <v>1</v>
+      </c>
+      <c r="D914">
+        <v>1</v>
+      </c>
+      <c r="E914">
+        <v>3</v>
+      </c>
+      <c r="F914">
+        <v>0</v>
+      </c>
+      <c r="G914">
+        <v>25</v>
+      </c>
+      <c r="H914">
+        <v>0</v>
+      </c>
+      <c r="J914">
+        <v>8.33</v>
+      </c>
+      <c r="K914">
+        <v>0</v>
+      </c>
+      <c r="L914">
+        <v>0</v>
+      </c>
+      <c r="M914" t="s">
+        <v>33</v>
+      </c>
+      <c r="N914" t="s">
+        <v>33</v>
+      </c>
+      <c r="O914">
+        <v>18</v>
+      </c>
+      <c r="P914">
+        <v>8</v>
+      </c>
+      <c r="Q914">
+        <v>2</v>
+      </c>
+      <c r="R914">
+        <v>0</v>
+      </c>
+      <c r="S914" t="s">
+        <v>40</v>
+      </c>
+      <c r="T914" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="915" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A915" t="s">
+        <v>570</v>
+      </c>
+      <c r="B915" t="s">
+        <v>121</v>
+      </c>
+      <c r="C915">
+        <v>1</v>
+      </c>
+      <c r="D915">
+        <v>1</v>
+      </c>
+      <c r="E915">
+        <v>4</v>
+      </c>
+      <c r="F915">
+        <v>0</v>
+      </c>
+      <c r="G915">
+        <v>22</v>
+      </c>
+      <c r="H915">
+        <v>2</v>
+      </c>
+      <c r="I915">
+        <v>11</v>
+      </c>
+      <c r="J915">
+        <v>5.5</v>
+      </c>
+      <c r="K915">
+        <v>0</v>
+      </c>
+      <c r="L915">
+        <v>0</v>
+      </c>
+      <c r="M915" s="1">
+        <v>44593</v>
+      </c>
+      <c r="N915" s="1">
+        <v>44593</v>
+      </c>
+      <c r="O915">
+        <v>24</v>
+      </c>
+      <c r="P915">
+        <v>7</v>
+      </c>
+      <c r="Q915">
+        <v>1</v>
+      </c>
+      <c r="R915">
+        <v>0</v>
+      </c>
+      <c r="S915" t="s">
+        <v>24</v>
+      </c>
+      <c r="T915" t="s">
+        <v>31</v>
+      </c>
+      <c r="U915">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="916" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A916" t="s">
+        <v>570</v>
+      </c>
+      <c r="B916" t="s">
+        <v>368</v>
+      </c>
+      <c r="C916">
+        <v>1</v>
+      </c>
+      <c r="D916">
+        <v>1</v>
+      </c>
+      <c r="E916">
+        <v>4</v>
+      </c>
+      <c r="F916">
+        <v>0</v>
+      </c>
+      <c r="G916">
+        <v>38</v>
+      </c>
+      <c r="H916">
+        <v>3</v>
+      </c>
+      <c r="I916">
+        <v>12.67</v>
+      </c>
+      <c r="J916">
+        <v>9.5</v>
+      </c>
+      <c r="K916">
+        <v>0</v>
+      </c>
+      <c r="L916">
+        <v>0</v>
+      </c>
+      <c r="M916" s="1">
+        <v>13940</v>
+      </c>
+      <c r="N916" s="1">
+        <v>13940</v>
+      </c>
+      <c r="O916">
+        <v>24</v>
+      </c>
+      <c r="P916">
+        <v>11</v>
+      </c>
+      <c r="Q916">
+        <v>3</v>
+      </c>
+      <c r="R916">
+        <v>1</v>
+      </c>
+      <c r="S916" t="s">
+        <v>155</v>
+      </c>
+      <c r="T916" t="s">
+        <v>24</v>
+      </c>
+      <c r="U916">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="917" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A917" t="s">
+        <v>570</v>
+      </c>
+      <c r="B917" t="s">
+        <v>571</v>
+      </c>
+      <c r="C917">
+        <v>1</v>
+      </c>
+      <c r="D917">
+        <v>1</v>
+      </c>
+      <c r="E917">
+        <v>2</v>
+      </c>
+      <c r="F917">
+        <v>0</v>
+      </c>
+      <c r="G917">
+        <v>16</v>
+      </c>
+      <c r="H917">
+        <v>0</v>
+      </c>
+      <c r="J917">
+        <v>8</v>
+      </c>
+      <c r="K917">
+        <v>0</v>
+      </c>
+      <c r="L917">
+        <v>0</v>
+      </c>
+      <c r="M917" t="s">
+        <v>70</v>
+      </c>
+      <c r="N917" t="s">
+        <v>70</v>
+      </c>
+      <c r="O917">
+        <v>12</v>
+      </c>
+      <c r="P917">
+        <v>10</v>
+      </c>
+      <c r="Q917">
+        <v>2</v>
+      </c>
+      <c r="R917">
+        <v>0</v>
+      </c>
+      <c r="S917" t="s">
+        <v>308</v>
+      </c>
+      <c r="T917" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="918" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A918" t="s">
+        <v>570</v>
+      </c>
+      <c r="B918" t="s">
+        <v>369</v>
+      </c>
+      <c r="C918">
+        <v>1</v>
+      </c>
+      <c r="D918">
+        <v>1</v>
+      </c>
+      <c r="E918">
+        <v>4</v>
+      </c>
+      <c r="F918">
+        <v>0</v>
+      </c>
+      <c r="G918">
+        <v>28</v>
+      </c>
+      <c r="H918">
+        <v>0</v>
+      </c>
+      <c r="J918">
+        <v>7</v>
+      </c>
+      <c r="K918">
+        <v>0</v>
+      </c>
+      <c r="L918">
+        <v>0</v>
+      </c>
+      <c r="M918" t="s">
+        <v>100</v>
+      </c>
+      <c r="N918" t="s">
+        <v>100</v>
+      </c>
+      <c r="O918">
+        <v>24</v>
+      </c>
+      <c r="P918">
+        <v>15</v>
+      </c>
+      <c r="Q918">
+        <v>2</v>
+      </c>
+      <c r="R918">
+        <v>1</v>
+      </c>
+      <c r="S918" t="s">
+        <v>34</v>
+      </c>
+      <c r="T918" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="919" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A919" t="s">
+        <v>570</v>
+      </c>
+      <c r="B919" t="s">
+        <v>126</v>
+      </c>
+      <c r="C919">
+        <v>1</v>
+      </c>
+      <c r="D919">
+        <v>1</v>
+      </c>
+      <c r="E919">
+        <v>4</v>
+      </c>
+      <c r="F919">
+        <v>0</v>
+      </c>
+      <c r="G919">
+        <v>22</v>
+      </c>
+      <c r="H919">
+        <v>1</v>
+      </c>
+      <c r="I919">
+        <v>22</v>
+      </c>
+      <c r="J919">
+        <v>5.5</v>
+      </c>
+      <c r="K919">
+        <v>0</v>
+      </c>
+      <c r="L919">
+        <v>0</v>
+      </c>
+      <c r="M919" s="1">
+        <v>44562</v>
+      </c>
+      <c r="N919" s="1">
+        <v>44562</v>
+      </c>
+      <c r="O919">
+        <v>24</v>
+      </c>
+      <c r="P919">
+        <v>11</v>
+      </c>
+      <c r="Q919">
+        <v>1</v>
+      </c>
+      <c r="R919">
+        <v>0</v>
+      </c>
+      <c r="S919" t="s">
+        <v>29</v>
+      </c>
+      <c r="T919" t="s">
+        <v>24</v>
+      </c>
+      <c r="U919">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="920" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A920" t="s">
+        <v>570</v>
+      </c>
+      <c r="B920" t="s">
+        <v>553</v>
+      </c>
+      <c r="C920">
+        <v>1</v>
+      </c>
+      <c r="D920">
+        <v>1</v>
+      </c>
+      <c r="E920">
+        <v>3</v>
+      </c>
+      <c r="F920">
+        <v>0</v>
+      </c>
+      <c r="G920">
+        <v>15</v>
+      </c>
+      <c r="H920">
+        <v>0</v>
+      </c>
+      <c r="J920">
+        <v>5</v>
+      </c>
+      <c r="K920">
+        <v>0</v>
+      </c>
+      <c r="L920">
+        <v>0</v>
+      </c>
+      <c r="M920" t="s">
+        <v>145</v>
+      </c>
+      <c r="N920" t="s">
+        <v>145</v>
+      </c>
+      <c r="O920">
+        <v>18</v>
+      </c>
+      <c r="P920">
+        <v>12</v>
+      </c>
+      <c r="Q920">
+        <v>1</v>
+      </c>
+      <c r="R920">
+        <v>0</v>
+      </c>
+      <c r="S920" t="s">
+        <v>34</v>
+      </c>
+      <c r="T920" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="921" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A921" t="s">
+        <v>570</v>
+      </c>
+      <c r="B921" t="s">
+        <v>235</v>
+      </c>
+      <c r="C921">
+        <v>1</v>
+      </c>
+      <c r="D921">
+        <v>1</v>
+      </c>
+      <c r="E921">
+        <v>4</v>
+      </c>
+      <c r="F921">
+        <v>0</v>
+      </c>
+      <c r="G921">
+        <v>26</v>
+      </c>
+      <c r="H921">
+        <v>1</v>
+      </c>
+      <c r="I921">
+        <v>26</v>
+      </c>
+      <c r="J921">
+        <v>6.5</v>
+      </c>
+      <c r="K921">
+        <v>0</v>
+      </c>
+      <c r="L921">
+        <v>0</v>
+      </c>
+      <c r="M921" s="1">
+        <v>46023</v>
+      </c>
+      <c r="N921" s="1">
+        <v>46023</v>
+      </c>
+      <c r="O921">
+        <v>24</v>
+      </c>
+      <c r="P921">
+        <v>10</v>
+      </c>
+      <c r="Q921">
+        <v>1</v>
+      </c>
+      <c r="R921">
+        <v>0</v>
+      </c>
+      <c r="S921" t="s">
+        <v>34</v>
+      </c>
+      <c r="T921" t="s">
+        <v>24</v>
+      </c>
+      <c r="U921">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="922" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A922" t="s">
+        <v>572</v>
+      </c>
+      <c r="B922" t="s">
+        <v>277</v>
+      </c>
+      <c r="C922">
+        <v>1</v>
+      </c>
+      <c r="D922">
+        <v>1</v>
+      </c>
+      <c r="E922">
+        <v>3</v>
+      </c>
+      <c r="F922">
+        <v>0</v>
+      </c>
+      <c r="G922">
+        <v>35</v>
+      </c>
+      <c r="H922">
+        <v>0</v>
+      </c>
+      <c r="J922">
+        <v>11.67</v>
+      </c>
+      <c r="K922">
+        <v>0</v>
+      </c>
+      <c r="L922">
+        <v>0</v>
+      </c>
+      <c r="M922" t="s">
+        <v>303</v>
+      </c>
+      <c r="N922" t="s">
+        <v>303</v>
+      </c>
+      <c r="O922">
+        <v>18</v>
+      </c>
+      <c r="P922">
+        <v>5</v>
+      </c>
+      <c r="Q922">
+        <v>1</v>
+      </c>
+      <c r="R922">
+        <v>3</v>
+      </c>
+      <c r="S922" t="s">
+        <v>40</v>
+      </c>
+      <c r="T922" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="923" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A923" t="s">
+        <v>572</v>
+      </c>
+      <c r="B923" t="s">
+        <v>504</v>
+      </c>
+      <c r="C923">
+        <v>1</v>
+      </c>
+      <c r="D923">
+        <v>1</v>
+      </c>
+      <c r="E923">
+        <v>3.4</v>
+      </c>
+      <c r="F923">
+        <v>0</v>
+      </c>
+      <c r="G923">
+        <v>35</v>
+      </c>
+      <c r="H923">
+        <v>1</v>
+      </c>
+      <c r="I923">
+        <v>35</v>
+      </c>
+      <c r="J923">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="K923">
+        <v>0</v>
+      </c>
+      <c r="L923">
+        <v>0</v>
+      </c>
+      <c r="M923" s="1">
+        <v>12785</v>
+      </c>
+      <c r="N923" s="1">
+        <v>12785</v>
+      </c>
+      <c r="O923">
+        <v>22</v>
+      </c>
+      <c r="P923">
+        <v>7</v>
+      </c>
+      <c r="Q923">
+        <v>3</v>
+      </c>
+      <c r="R923">
+        <v>1</v>
+      </c>
+      <c r="S923" t="s">
+        <v>34</v>
+      </c>
+      <c r="T923" t="s">
+        <v>24</v>
+      </c>
+      <c r="U923">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="924" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A924" t="s">
+        <v>572</v>
+      </c>
+      <c r="B924" t="s">
+        <v>161</v>
+      </c>
+      <c r="C924">
+        <v>1</v>
+      </c>
+      <c r="D924">
+        <v>1</v>
+      </c>
+      <c r="E924">
+        <v>3</v>
+      </c>
+      <c r="F924">
+        <v>0</v>
+      </c>
+      <c r="G924">
+        <v>26</v>
+      </c>
+      <c r="H924">
+        <v>1</v>
+      </c>
+      <c r="I924">
+        <v>26</v>
+      </c>
+      <c r="J924">
+        <v>8.67</v>
+      </c>
+      <c r="K924">
+        <v>0</v>
+      </c>
+      <c r="L924">
+        <v>0</v>
+      </c>
+      <c r="M924" s="1">
+        <v>46023</v>
+      </c>
+      <c r="N924" s="1">
+        <v>46023</v>
+      </c>
+      <c r="O924">
+        <v>18</v>
+      </c>
+      <c r="P924">
+        <v>7</v>
+      </c>
+      <c r="Q924">
+        <v>3</v>
+      </c>
+      <c r="R924">
+        <v>1</v>
+      </c>
+      <c r="S924" t="s">
+        <v>31</v>
+      </c>
+      <c r="T924" t="s">
+        <v>24</v>
+      </c>
+      <c r="U924">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="925" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A925" t="s">
+        <v>572</v>
+      </c>
+      <c r="B925" t="s">
+        <v>385</v>
+      </c>
+      <c r="C925">
+        <v>1</v>
+      </c>
+      <c r="D925">
+        <v>1</v>
+      </c>
+      <c r="E925">
+        <v>1</v>
+      </c>
+      <c r="F925">
+        <v>0</v>
+      </c>
+      <c r="G925">
+        <v>29</v>
+      </c>
+      <c r="H925">
+        <v>0</v>
+      </c>
+      <c r="J925">
+        <v>29</v>
+      </c>
+      <c r="K925">
+        <v>0</v>
+      </c>
+      <c r="L925">
+        <v>0</v>
+      </c>
+      <c r="M925" t="s">
+        <v>263</v>
+      </c>
+      <c r="N925" t="s">
+        <v>263</v>
+      </c>
+      <c r="O925">
+        <v>6</v>
+      </c>
+      <c r="P925">
+        <v>0</v>
+      </c>
+      <c r="Q925">
+        <v>1</v>
+      </c>
+      <c r="R925">
+        <v>4</v>
+      </c>
+      <c r="S925" t="s">
+        <v>24</v>
+      </c>
+      <c r="T925" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="926" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A926" t="s">
+        <v>572</v>
+      </c>
+      <c r="B926" t="s">
+        <v>183</v>
+      </c>
+      <c r="C926">
+        <v>1</v>
+      </c>
+      <c r="D926">
+        <v>1</v>
+      </c>
+      <c r="E926">
+        <v>4</v>
+      </c>
+      <c r="F926">
+        <v>0</v>
+      </c>
+      <c r="G926">
+        <v>27</v>
+      </c>
+      <c r="H926">
+        <v>0</v>
+      </c>
+      <c r="J926">
+        <v>6.75</v>
+      </c>
+      <c r="K926">
+        <v>0</v>
+      </c>
+      <c r="L926">
+        <v>0</v>
+      </c>
+      <c r="M926" t="s">
+        <v>93</v>
+      </c>
+      <c r="N926" t="s">
+        <v>93</v>
+      </c>
+      <c r="O926">
+        <v>24</v>
+      </c>
+      <c r="P926">
+        <v>10</v>
+      </c>
+      <c r="Q926">
+        <v>2</v>
+      </c>
+      <c r="R926">
+        <v>1</v>
+      </c>
+      <c r="S926" t="s">
+        <v>29</v>
+      </c>
+      <c r="T926" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="927" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A927" t="s">
+        <v>572</v>
+      </c>
+      <c r="B927" t="s">
+        <v>169</v>
+      </c>
+      <c r="C927">
+        <v>1</v>
+      </c>
+      <c r="D927">
+        <v>1</v>
+      </c>
+      <c r="E927">
+        <v>2</v>
+      </c>
+      <c r="F927">
+        <v>0</v>
+      </c>
+      <c r="G927">
+        <v>20</v>
+      </c>
+      <c r="H927">
+        <v>1</v>
+      </c>
+      <c r="I927">
+        <v>20</v>
+      </c>
+      <c r="J927">
+        <v>10</v>
+      </c>
+      <c r="K927">
+        <v>0</v>
+      </c>
+      <c r="L927">
+        <v>0</v>
+      </c>
+      <c r="M927" s="1">
+        <v>43831</v>
+      </c>
+      <c r="N927" s="1">
+        <v>43831</v>
+      </c>
+      <c r="O927">
+        <v>12</v>
+      </c>
+      <c r="P927">
+        <v>7</v>
+      </c>
+      <c r="Q927">
+        <v>0</v>
+      </c>
+      <c r="R927">
+        <v>3</v>
+      </c>
+      <c r="S927" t="s">
+        <v>24</v>
+      </c>
+      <c r="T927" t="s">
+        <v>24</v>
+      </c>
+      <c r="U927">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="928" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A928" t="s">
+        <v>572</v>
+      </c>
+      <c r="B928" t="s">
+        <v>188</v>
+      </c>
+      <c r="C928">
+        <v>1</v>
+      </c>
+      <c r="D928">
+        <v>1</v>
+      </c>
+      <c r="E928">
+        <v>3</v>
+      </c>
+      <c r="F928">
+        <v>0</v>
+      </c>
+      <c r="G928">
+        <v>29</v>
+      </c>
+      <c r="H928">
+        <v>2</v>
+      </c>
+      <c r="I928">
+        <v>14.5</v>
+      </c>
+      <c r="J928">
+        <v>9.67</v>
+      </c>
+      <c r="K928">
+        <v>0</v>
+      </c>
+      <c r="L928">
+        <v>0</v>
+      </c>
+      <c r="M928" s="1">
+        <v>47150</v>
+      </c>
+      <c r="N928" s="1">
+        <v>47150</v>
+      </c>
+      <c r="O928">
+        <v>18</v>
+      </c>
+      <c r="P928">
+        <v>9</v>
+      </c>
+      <c r="Q928">
+        <v>5</v>
+      </c>
+      <c r="R928">
+        <v>0</v>
+      </c>
+      <c r="S928" t="s">
+        <v>34</v>
+      </c>
+      <c r="T928" t="s">
+        <v>24</v>
+      </c>
+      <c r="U928">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="929" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A929" t="s">
+        <v>572</v>
+      </c>
+      <c r="B929" t="s">
+        <v>505</v>
+      </c>
+      <c r="C929">
+        <v>1</v>
+      </c>
+      <c r="D929">
+        <v>1</v>
+      </c>
+      <c r="E929">
+        <v>4</v>
+      </c>
+      <c r="F929">
+        <v>0</v>
+      </c>
+      <c r="G929">
+        <v>33</v>
+      </c>
+      <c r="H929">
+        <v>2</v>
+      </c>
+      <c r="I929">
+        <v>16.5</v>
+      </c>
+      <c r="J929">
+        <v>8.25</v>
+      </c>
+      <c r="K929">
+        <v>0</v>
+      </c>
+      <c r="L929">
+        <v>0</v>
+      </c>
+      <c r="M929" s="1">
+        <v>12086</v>
+      </c>
+      <c r="N929" s="1">
+        <v>12086</v>
+      </c>
+      <c r="O929">
+        <v>24</v>
+      </c>
+      <c r="P929">
+        <v>13</v>
+      </c>
+      <c r="Q929">
+        <v>4</v>
+      </c>
+      <c r="R929">
+        <v>1</v>
+      </c>
+      <c r="S929" t="s">
+        <v>29</v>
+      </c>
+      <c r="T929" t="s">
+        <v>24</v>
+      </c>
+      <c r="U929">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="930" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A930" t="s">
+        <v>572</v>
+      </c>
+      <c r="B930" t="s">
+        <v>441</v>
+      </c>
+      <c r="C930">
+        <v>1</v>
+      </c>
+      <c r="D930">
+        <v>1</v>
+      </c>
+      <c r="E930">
+        <v>2</v>
+      </c>
+      <c r="F930">
+        <v>0</v>
+      </c>
+      <c r="G930">
+        <v>15</v>
+      </c>
+      <c r="H930">
+        <v>1</v>
+      </c>
+      <c r="I930">
+        <v>15</v>
+      </c>
+      <c r="J930">
+        <v>7.5</v>
+      </c>
+      <c r="K930">
+        <v>0</v>
+      </c>
+      <c r="L930">
+        <v>0</v>
+      </c>
+      <c r="M930" s="1">
+        <v>42005</v>
+      </c>
+      <c r="N930" s="1">
+        <v>42005</v>
+      </c>
+      <c r="O930">
+        <v>12</v>
+      </c>
+      <c r="P930">
+        <v>7</v>
+      </c>
+      <c r="Q930">
+        <v>2</v>
+      </c>
+      <c r="R930">
+        <v>0</v>
+      </c>
+      <c r="S930" t="s">
+        <v>109</v>
+      </c>
+      <c r="T930" t="s">
+        <v>24</v>
+      </c>
+      <c r="U930">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="931" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A931" t="s">
+        <v>572</v>
+      </c>
+      <c r="B931" t="s">
+        <v>364</v>
+      </c>
+      <c r="C931">
+        <v>1</v>
+      </c>
+      <c r="D931">
+        <v>1</v>
+      </c>
+      <c r="E931">
+        <v>2</v>
+      </c>
+      <c r="F931">
+        <v>0</v>
+      </c>
+      <c r="G931">
+        <v>24</v>
+      </c>
+      <c r="H931">
+        <v>0</v>
+      </c>
+      <c r="J931">
+        <v>12</v>
+      </c>
+      <c r="K931">
+        <v>0</v>
+      </c>
+      <c r="L931">
+        <v>0</v>
+      </c>
+      <c r="M931" t="s">
+        <v>162</v>
+      </c>
+      <c r="N931" t="s">
+        <v>162</v>
+      </c>
+      <c r="O931">
+        <v>12</v>
+      </c>
+      <c r="P931">
+        <v>3</v>
+      </c>
+      <c r="Q931">
+        <v>2</v>
+      </c>
+      <c r="R931">
+        <v>1</v>
+      </c>
+      <c r="S931" t="s">
+        <v>29</v>
+      </c>
+      <c r="T931" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="932" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A932" t="s">
+        <v>572</v>
+      </c>
+      <c r="B932" t="s">
+        <v>366</v>
+      </c>
+      <c r="C932">
+        <v>1</v>
+      </c>
+      <c r="D932">
+        <v>1</v>
+      </c>
+      <c r="E932">
+        <v>3.5</v>
+      </c>
+      <c r="F932">
+        <v>0</v>
+      </c>
+      <c r="G932">
+        <v>28</v>
+      </c>
+      <c r="H932">
+        <v>0</v>
+      </c>
+      <c r="J932">
+        <v>7.3</v>
+      </c>
+      <c r="K932">
+        <v>0</v>
+      </c>
+      <c r="L932">
+        <v>0</v>
+      </c>
+      <c r="M932" t="s">
+        <v>100</v>
+      </c>
+      <c r="N932" t="s">
+        <v>100</v>
+      </c>
+      <c r="O932">
+        <v>23</v>
+      </c>
+      <c r="P932">
+        <v>11</v>
+      </c>
+      <c r="Q932">
+        <v>2</v>
+      </c>
+      <c r="R932">
+        <v>1</v>
+      </c>
+      <c r="S932" t="s">
+        <v>29</v>
+      </c>
+      <c r="T932" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="933" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A933" t="s">
+        <v>572</v>
+      </c>
+      <c r="B933" t="s">
+        <v>432</v>
+      </c>
+      <c r="C933">
+        <v>1</v>
+      </c>
+      <c r="D933">
+        <v>1</v>
+      </c>
+      <c r="E933">
+        <v>4</v>
+      </c>
+      <c r="F933">
+        <v>0</v>
+      </c>
+      <c r="G933">
+        <v>32</v>
+      </c>
+      <c r="H933">
+        <v>2</v>
+      </c>
+      <c r="I933">
+        <v>16</v>
+      </c>
+      <c r="J933">
+        <v>8</v>
+      </c>
+      <c r="K933">
+        <v>0</v>
+      </c>
+      <c r="L933">
+        <v>0</v>
+      </c>
+      <c r="M933" s="1">
+        <v>11720</v>
+      </c>
+      <c r="N933" s="1">
+        <v>11720</v>
+      </c>
+      <c r="O933">
+        <v>24</v>
+      </c>
+      <c r="P933">
+        <v>12</v>
+      </c>
+      <c r="Q933">
+        <v>5</v>
+      </c>
+      <c r="R933">
+        <v>1</v>
+      </c>
+      <c r="S933" t="s">
+        <v>24</v>
+      </c>
+      <c r="T933" t="s">
+        <v>24</v>
+      </c>
+      <c r="U933">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="934" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A934" t="s">
+        <v>573</v>
+      </c>
+      <c r="B934" t="s">
+        <v>377</v>
+      </c>
+      <c r="C934">
+        <v>1</v>
+      </c>
+      <c r="D934">
+        <v>1</v>
+      </c>
+      <c r="E934">
+        <v>3</v>
+      </c>
+      <c r="F934">
+        <v>0</v>
+      </c>
+      <c r="G934">
+        <v>9</v>
+      </c>
+      <c r="H934">
+        <v>1</v>
+      </c>
+      <c r="I934">
+        <v>9</v>
+      </c>
+      <c r="J934">
+        <v>3</v>
+      </c>
+      <c r="K934">
+        <v>0</v>
+      </c>
+      <c r="L934">
+        <v>0</v>
+      </c>
+      <c r="M934" s="2">
+        <v>46266</v>
+      </c>
+      <c r="N934" s="2">
+        <v>46266</v>
+      </c>
+      <c r="O934">
+        <v>18</v>
+      </c>
+      <c r="P934">
+        <v>14</v>
+      </c>
+      <c r="Q934">
+        <v>0</v>
+      </c>
+      <c r="R934">
+        <v>0</v>
+      </c>
+      <c r="S934" t="s">
+        <v>109</v>
+      </c>
+      <c r="T934" t="s">
+        <v>24</v>
+      </c>
+      <c r="U934">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="935" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A935" t="s">
+        <v>573</v>
+      </c>
+      <c r="B935" t="s">
+        <v>574</v>
+      </c>
+      <c r="C935">
+        <v>1</v>
+      </c>
+      <c r="D935">
+        <v>1</v>
+      </c>
+      <c r="E935">
+        <v>2</v>
+      </c>
+      <c r="F935">
+        <v>0</v>
+      </c>
+      <c r="G935">
+        <v>22</v>
+      </c>
+      <c r="H935">
+        <v>0</v>
+      </c>
+      <c r="J935">
+        <v>11</v>
+      </c>
+      <c r="K935">
+        <v>0</v>
+      </c>
+      <c r="L935">
+        <v>0</v>
+      </c>
+      <c r="M935" t="s">
+        <v>98</v>
+      </c>
+      <c r="N935" t="s">
+        <v>98</v>
+      </c>
+      <c r="O935">
+        <v>12</v>
+      </c>
+      <c r="P935">
+        <v>4</v>
+      </c>
+      <c r="Q935">
+        <v>4</v>
+      </c>
+      <c r="R935">
+        <v>0</v>
+      </c>
+      <c r="S935" t="s">
+        <v>31</v>
+      </c>
+      <c r="T935" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="936" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A936" t="s">
+        <v>573</v>
+      </c>
+      <c r="B936" t="s">
+        <v>378</v>
+      </c>
+      <c r="C936">
+        <v>1</v>
+      </c>
+      <c r="D936">
+        <v>1</v>
+      </c>
+      <c r="E936">
+        <v>3</v>
+      </c>
+      <c r="F936">
+        <v>0</v>
+      </c>
+      <c r="G936">
+        <v>16</v>
+      </c>
+      <c r="H936">
+        <v>0</v>
+      </c>
+      <c r="J936">
+        <v>5.33</v>
+      </c>
+      <c r="K936">
+        <v>0</v>
+      </c>
+      <c r="L936">
+        <v>0</v>
+      </c>
+      <c r="M936" t="s">
+        <v>70</v>
+      </c>
+      <c r="N936" t="s">
+        <v>70</v>
+      </c>
+      <c r="O936">
+        <v>18</v>
+      </c>
+      <c r="P936">
+        <v>12</v>
+      </c>
+      <c r="Q936">
+        <v>1</v>
+      </c>
+      <c r="R936">
+        <v>0</v>
+      </c>
+      <c r="S936" t="s">
+        <v>56</v>
+      </c>
+      <c r="T936" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="937" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A937" t="s">
+        <v>573</v>
+      </c>
+      <c r="B937" t="s">
+        <v>575</v>
+      </c>
+      <c r="C937">
+        <v>1</v>
+      </c>
+      <c r="D937">
+        <v>1</v>
+      </c>
+      <c r="E937">
+        <v>1</v>
+      </c>
+      <c r="F937">
+        <v>0</v>
+      </c>
+      <c r="G937">
+        <v>14</v>
+      </c>
+      <c r="H937">
+        <v>0</v>
+      </c>
+      <c r="J937">
+        <v>14</v>
+      </c>
+      <c r="K937">
+        <v>0</v>
+      </c>
+      <c r="L937">
+        <v>0</v>
+      </c>
+      <c r="M937" t="s">
+        <v>193</v>
+      </c>
+      <c r="N937" t="s">
+        <v>193</v>
+      </c>
+      <c r="O937">
+        <v>6</v>
+      </c>
+      <c r="P937">
+        <v>2</v>
+      </c>
+      <c r="Q937">
+        <v>0</v>
+      </c>
+      <c r="R937">
+        <v>0</v>
+      </c>
+      <c r="S937" t="s">
+        <v>308</v>
+      </c>
+      <c r="T937" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="938" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A938" t="s">
+        <v>573</v>
+      </c>
+      <c r="B938" t="s">
+        <v>576</v>
+      </c>
+      <c r="C938">
+        <v>1</v>
+      </c>
+      <c r="D938">
+        <v>1</v>
+      </c>
+      <c r="E938">
+        <v>4</v>
+      </c>
+      <c r="F938">
+        <v>0</v>
+      </c>
+      <c r="G938">
+        <v>16</v>
+      </c>
+      <c r="H938">
+        <v>0</v>
+      </c>
+      <c r="J938">
+        <v>4</v>
+      </c>
+      <c r="K938">
+        <v>0</v>
+      </c>
+      <c r="L938">
+        <v>0</v>
+      </c>
+      <c r="M938" t="s">
+        <v>70</v>
+      </c>
+      <c r="N938" t="s">
+        <v>70</v>
+      </c>
+      <c r="O938">
+        <v>24</v>
+      </c>
+      <c r="P938">
+        <v>11</v>
+      </c>
+      <c r="Q938">
+        <v>0</v>
+      </c>
+      <c r="R938">
+        <v>0</v>
+      </c>
+      <c r="S938" t="s">
+        <v>31</v>
+      </c>
+      <c r="T938" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="939" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A939" t="s">
+        <v>573</v>
+      </c>
+      <c r="B939" t="s">
+        <v>315</v>
+      </c>
+      <c r="C939">
+        <v>1</v>
+      </c>
+      <c r="D939">
+        <v>1</v>
+      </c>
+      <c r="E939">
+        <v>2</v>
+      </c>
+      <c r="F939">
+        <v>0</v>
+      </c>
+      <c r="G939">
+        <v>8</v>
+      </c>
+      <c r="H939">
+        <v>1</v>
+      </c>
+      <c r="I939">
+        <v>8</v>
+      </c>
+      <c r="J939">
+        <v>4</v>
+      </c>
+      <c r="K939">
+        <v>0</v>
+      </c>
+      <c r="L939">
+        <v>0</v>
+      </c>
+      <c r="M939" s="2">
+        <v>46235</v>
+      </c>
+      <c r="N939" s="2">
+        <v>46235</v>
+      </c>
+      <c r="O939">
+        <v>12</v>
+      </c>
+      <c r="P939">
+        <v>7</v>
+      </c>
+      <c r="Q939">
+        <v>1</v>
+      </c>
+      <c r="R939">
+        <v>0</v>
+      </c>
+      <c r="S939" t="s">
+        <v>24</v>
+      </c>
+      <c r="T939" t="s">
+        <v>24</v>
+      </c>
+      <c r="U939">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="940" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A940" t="s">
+        <v>573</v>
+      </c>
+      <c r="B940" t="s">
+        <v>544</v>
+      </c>
+      <c r="C940">
+        <v>1</v>
+      </c>
+      <c r="D940">
+        <v>1</v>
+      </c>
+      <c r="E940">
+        <v>4</v>
+      </c>
+      <c r="F940">
+        <v>0</v>
+      </c>
+      <c r="G940">
+        <v>24</v>
+      </c>
+      <c r="H940">
+        <v>0</v>
+      </c>
+      <c r="J940">
+        <v>6</v>
+      </c>
+      <c r="K940">
+        <v>0</v>
+      </c>
+      <c r="L940">
+        <v>0</v>
+      </c>
+      <c r="M940" t="s">
+        <v>162</v>
+      </c>
+      <c r="N940" t="s">
+        <v>162</v>
+      </c>
+      <c r="O940">
+        <v>24</v>
+      </c>
+      <c r="P940">
+        <v>15</v>
+      </c>
+      <c r="Q940">
+        <v>3</v>
+      </c>
+      <c r="R940">
+        <v>0</v>
+      </c>
+      <c r="S940" t="s">
+        <v>109</v>
+      </c>
+      <c r="T940" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="941" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A941" t="s">
+        <v>573</v>
+      </c>
+      <c r="B941" t="s">
+        <v>513</v>
+      </c>
+      <c r="C941">
+        <v>1</v>
+      </c>
+      <c r="D941">
+        <v>1</v>
+      </c>
+      <c r="E941">
+        <v>2</v>
+      </c>
+      <c r="F941">
+        <v>0</v>
+      </c>
+      <c r="G941">
+        <v>14</v>
+      </c>
+      <c r="H941">
+        <v>0</v>
+      </c>
+      <c r="J941">
+        <v>7</v>
+      </c>
+      <c r="K941">
+        <v>0</v>
+      </c>
+      <c r="L941">
+        <v>0</v>
+      </c>
+      <c r="M941" t="s">
+        <v>193</v>
+      </c>
+      <c r="N941" t="s">
+        <v>193</v>
+      </c>
+      <c r="O941">
+        <v>12</v>
+      </c>
+      <c r="P941">
+        <v>6</v>
+      </c>
+      <c r="Q941">
+        <v>2</v>
+      </c>
+      <c r="R941">
+        <v>0</v>
+      </c>
+      <c r="S941" t="s">
+        <v>29</v>
+      </c>
+      <c r="T941" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="942" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A942" t="s">
+        <v>573</v>
+      </c>
+      <c r="B942" t="s">
+        <v>54</v>
+      </c>
+      <c r="C942">
+        <v>1</v>
+      </c>
+      <c r="D942">
+        <v>1</v>
+      </c>
+      <c r="E942">
+        <v>3</v>
+      </c>
+      <c r="F942">
+        <v>0</v>
+      </c>
+      <c r="G942">
+        <v>26</v>
+      </c>
+      <c r="H942">
+        <v>1</v>
+      </c>
+      <c r="I942">
+        <v>26</v>
+      </c>
+      <c r="J942">
+        <v>8.67</v>
+      </c>
+      <c r="K942">
+        <v>0</v>
+      </c>
+      <c r="L942">
+        <v>0</v>
+      </c>
+      <c r="M942" s="1">
+        <v>46023</v>
+      </c>
+      <c r="N942" s="1">
+        <v>46023</v>
+      </c>
+      <c r="O942">
+        <v>18</v>
+      </c>
+      <c r="P942">
+        <v>9</v>
+      </c>
+      <c r="Q942">
+        <v>4</v>
+      </c>
+      <c r="R942">
+        <v>0</v>
+      </c>
+      <c r="S942" t="s">
+        <v>40</v>
+      </c>
+      <c r="T942" t="s">
+        <v>24</v>
+      </c>
+      <c r="U942">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="943" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A943" t="s">
+        <v>573</v>
+      </c>
+      <c r="B943" t="s">
+        <v>257</v>
+      </c>
+      <c r="C943">
+        <v>1</v>
+      </c>
+      <c r="D943">
+        <v>1</v>
+      </c>
+      <c r="E943">
+        <v>2</v>
+      </c>
+      <c r="F943">
+        <v>0</v>
+      </c>
+      <c r="G943">
+        <v>17</v>
+      </c>
+      <c r="H943">
+        <v>0</v>
+      </c>
+      <c r="J943">
+        <v>8.5</v>
+      </c>
+      <c r="K943">
+        <v>0</v>
+      </c>
+      <c r="L943">
+        <v>0</v>
+      </c>
+      <c r="M943" t="s">
+        <v>28</v>
+      </c>
+      <c r="N943" t="s">
+        <v>28</v>
+      </c>
+      <c r="O943">
+        <v>12</v>
+      </c>
+      <c r="P943">
+        <v>3</v>
+      </c>
+      <c r="Q943">
+        <v>2</v>
+      </c>
+      <c r="R943">
+        <v>0</v>
+      </c>
+      <c r="S943" t="s">
+        <v>29</v>
+      </c>
+      <c r="T943" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="944" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A944" t="s">
+        <v>573</v>
+      </c>
+      <c r="B944" t="s">
+        <v>318</v>
+      </c>
+      <c r="C944">
+        <v>1</v>
+      </c>
+      <c r="D944">
+        <v>1</v>
+      </c>
+      <c r="E944">
+        <v>2</v>
+      </c>
+      <c r="F944">
+        <v>0</v>
+      </c>
+      <c r="G944">
+        <v>8</v>
+      </c>
+      <c r="H944">
+        <v>0</v>
+      </c>
+      <c r="J944">
+        <v>4</v>
+      </c>
+      <c r="K944">
+        <v>0</v>
+      </c>
+      <c r="L944">
+        <v>0</v>
+      </c>
+      <c r="M944" t="s">
+        <v>219</v>
+      </c>
+      <c r="N944" t="s">
+        <v>219</v>
+      </c>
+      <c r="O944">
+        <v>12</v>
+      </c>
+      <c r="P944">
+        <v>6</v>
+      </c>
+      <c r="Q944">
+        <v>0</v>
+      </c>
+      <c r="R944">
+        <v>0</v>
+      </c>
+      <c r="S944" t="s">
+        <v>24</v>
+      </c>
+      <c r="T944" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="945" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A945" t="s">
+        <v>573</v>
+      </c>
+      <c r="B945" t="s">
+        <v>259</v>
+      </c>
+      <c r="C945">
+        <v>1</v>
+      </c>
+      <c r="D945">
+        <v>1</v>
+      </c>
+      <c r="E945">
+        <v>4</v>
+      </c>
+      <c r="F945">
+        <v>0</v>
+      </c>
+      <c r="G945">
+        <v>20</v>
+      </c>
+      <c r="H945">
+        <v>0</v>
+      </c>
+      <c r="J945">
+        <v>5</v>
+      </c>
+      <c r="K945">
+        <v>0</v>
+      </c>
+      <c r="L945">
+        <v>0</v>
+      </c>
+      <c r="M945" t="s">
+        <v>135</v>
+      </c>
+      <c r="N945" t="s">
+        <v>135</v>
+      </c>
+      <c r="O945">
+        <v>24</v>
+      </c>
+      <c r="P945">
+        <v>12</v>
+      </c>
+      <c r="Q945">
+        <v>2</v>
+      </c>
+      <c r="R945">
+        <v>0</v>
+      </c>
+      <c r="S945" t="s">
+        <v>31</v>
+      </c>
+      <c r="T945" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="946" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A946" t="s">
+        <v>573</v>
+      </c>
+      <c r="B946" t="s">
+        <v>59</v>
+      </c>
+      <c r="C946">
+        <v>1</v>
+      </c>
+      <c r="D946">
+        <v>1</v>
+      </c>
+      <c r="E946">
+        <v>4</v>
+      </c>
+      <c r="F946">
+        <v>0</v>
+      </c>
+      <c r="G946">
+        <v>28</v>
+      </c>
+      <c r="H946">
+        <v>0</v>
+      </c>
+      <c r="J946">
+        <v>7</v>
+      </c>
+      <c r="K946">
+        <v>0</v>
+      </c>
+      <c r="L946">
+        <v>0</v>
+      </c>
+      <c r="M946" t="s">
+        <v>100</v>
+      </c>
+      <c r="N946" t="s">
+        <v>100</v>
+      </c>
+      <c r="O946">
+        <v>24</v>
+      </c>
+      <c r="P946">
+        <v>10</v>
+      </c>
+      <c r="Q946">
+        <v>3</v>
+      </c>
+      <c r="R946">
+        <v>0</v>
+      </c>
+      <c r="S946" t="s">
+        <v>29</v>
+      </c>
+      <c r="T946" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="947" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A947" t="s">
+        <v>577</v>
+      </c>
+      <c r="B947" t="s">
+        <v>86</v>
+      </c>
+      <c r="C947">
+        <v>1</v>
+      </c>
+      <c r="D947">
+        <v>1</v>
+      </c>
+      <c r="E947">
+        <v>2</v>
+      </c>
+      <c r="F947">
+        <v>0</v>
+      </c>
+      <c r="G947">
+        <v>14</v>
+      </c>
+      <c r="H947">
+        <v>0</v>
+      </c>
+      <c r="J947">
+        <v>7</v>
+      </c>
+      <c r="K947">
+        <v>0</v>
+      </c>
+      <c r="L947">
+        <v>0</v>
+      </c>
+      <c r="M947" t="s">
+        <v>193</v>
+      </c>
+      <c r="N947" t="s">
+        <v>193</v>
+      </c>
+      <c r="O947">
+        <v>12</v>
+      </c>
+      <c r="P947">
+        <v>4</v>
+      </c>
+      <c r="Q947">
+        <v>1</v>
+      </c>
+      <c r="R947">
+        <v>0</v>
+      </c>
+      <c r="S947" t="s">
+        <v>31</v>
+      </c>
+      <c r="T947" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="948" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A948" t="s">
+        <v>577</v>
+      </c>
+      <c r="B948" t="s">
+        <v>322</v>
+      </c>
+      <c r="C948">
+        <v>1</v>
+      </c>
+      <c r="D948">
+        <v>1</v>
+      </c>
+      <c r="E948">
+        <v>4</v>
+      </c>
+      <c r="F948">
+        <v>0</v>
+      </c>
+      <c r="G948">
+        <v>36</v>
+      </c>
+      <c r="H948">
+        <v>0</v>
+      </c>
+      <c r="J948">
+        <v>9</v>
+      </c>
+      <c r="K948">
+        <v>0</v>
+      </c>
+      <c r="L948">
+        <v>0</v>
+      </c>
+      <c r="M948" t="s">
+        <v>66</v>
+      </c>
+      <c r="N948" t="s">
+        <v>66</v>
+      </c>
+      <c r="O948">
+        <v>24</v>
+      </c>
+      <c r="P948">
+        <v>9</v>
+      </c>
+      <c r="Q948">
+        <v>4</v>
+      </c>
+      <c r="R948">
+        <v>1</v>
+      </c>
+      <c r="S948" t="s">
+        <v>42</v>
+      </c>
+      <c r="T948" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="949" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A949" t="s">
+        <v>577</v>
+      </c>
+      <c r="B949" t="s">
+        <v>323</v>
+      </c>
+      <c r="C949">
+        <v>1</v>
+      </c>
+      <c r="D949">
+        <v>1</v>
+      </c>
+      <c r="E949">
+        <v>3</v>
+      </c>
+      <c r="F949">
+        <v>0</v>
+      </c>
+      <c r="G949">
+        <v>32</v>
+      </c>
+      <c r="H949">
+        <v>0</v>
+      </c>
+      <c r="J949">
+        <v>10.67</v>
+      </c>
+      <c r="K949">
+        <v>0</v>
+      </c>
+      <c r="L949">
+        <v>0</v>
+      </c>
+      <c r="M949" t="s">
+        <v>65</v>
+      </c>
+      <c r="N949" t="s">
+        <v>65</v>
+      </c>
+      <c r="O949">
+        <v>18</v>
+      </c>
+      <c r="P949">
+        <v>8</v>
+      </c>
+      <c r="Q949">
+        <v>4</v>
+      </c>
+      <c r="R949">
+        <v>0</v>
+      </c>
+      <c r="S949" t="s">
+        <v>46</v>
+      </c>
+      <c r="T949" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="950" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A950" t="s">
+        <v>577</v>
+      </c>
+      <c r="B950" t="s">
+        <v>232</v>
+      </c>
+      <c r="C950">
+        <v>1</v>
+      </c>
+      <c r="D950">
+        <v>1</v>
+      </c>
+      <c r="E950">
+        <v>4</v>
+      </c>
+      <c r="F950">
+        <v>0</v>
+      </c>
+      <c r="G950">
+        <v>21</v>
+      </c>
+      <c r="H950">
+        <v>2</v>
+      </c>
+      <c r="I950">
+        <v>10.5</v>
+      </c>
+      <c r="J950">
+        <v>5.25</v>
+      </c>
+      <c r="K950">
+        <v>0</v>
+      </c>
+      <c r="L950">
+        <v>0</v>
+      </c>
+      <c r="M950" s="1">
+        <v>44228</v>
+      </c>
+      <c r="N950" s="1">
+        <v>44228</v>
+      </c>
+      <c r="O950">
+        <v>24</v>
+      </c>
+      <c r="P950">
+        <v>9</v>
+      </c>
+      <c r="Q950">
+        <v>1</v>
+      </c>
+      <c r="R950">
+        <v>0</v>
+      </c>
+      <c r="S950" t="s">
+        <v>29</v>
+      </c>
+      <c r="T950" t="s">
+        <v>24</v>
+      </c>
+      <c r="U950">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="951" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A951" t="s">
+        <v>577</v>
+      </c>
+      <c r="B951" t="s">
+        <v>116</v>
+      </c>
+      <c r="C951">
+        <v>1</v>
+      </c>
+      <c r="D951">
+        <v>1</v>
+      </c>
+      <c r="E951">
+        <v>2</v>
+      </c>
+      <c r="F951">
+        <v>0</v>
+      </c>
+      <c r="G951">
+        <v>26</v>
+      </c>
+      <c r="H951">
+        <v>0</v>
+      </c>
+      <c r="J951">
+        <v>13</v>
+      </c>
+      <c r="K951">
+        <v>0</v>
+      </c>
+      <c r="L951">
+        <v>0</v>
+      </c>
+      <c r="M951" t="s">
+        <v>90</v>
+      </c>
+      <c r="N951" t="s">
+        <v>90</v>
+      </c>
+      <c r="O951">
+        <v>12</v>
+      </c>
+      <c r="P951">
+        <v>5</v>
+      </c>
+      <c r="Q951">
+        <v>1</v>
+      </c>
+      <c r="R951">
+        <v>1</v>
+      </c>
+      <c r="S951" t="s">
+        <v>324</v>
+      </c>
+      <c r="T951" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="952" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A952" t="s">
+        <v>577</v>
+      </c>
+      <c r="B952" t="s">
+        <v>492</v>
+      </c>
+      <c r="C952">
+        <v>1</v>
+      </c>
+      <c r="D952">
+        <v>1</v>
+      </c>
+      <c r="E952">
+        <v>3</v>
+      </c>
+      <c r="F952">
+        <v>0</v>
+      </c>
+      <c r="G952">
+        <v>10</v>
+      </c>
+      <c r="H952">
+        <v>2</v>
+      </c>
+      <c r="I952">
+        <v>5</v>
+      </c>
+      <c r="J952">
+        <v>3.33</v>
+      </c>
+      <c r="K952">
+        <v>0</v>
+      </c>
+      <c r="L952">
+        <v>0</v>
+      </c>
+      <c r="M952" s="2">
+        <v>46297</v>
+      </c>
+      <c r="N952" s="2">
+        <v>46297</v>
+      </c>
+      <c r="O952">
+        <v>18</v>
+      </c>
+      <c r="P952">
+        <v>14</v>
+      </c>
+      <c r="Q952">
+        <v>1</v>
+      </c>
+      <c r="R952">
+        <v>0</v>
+      </c>
+      <c r="S952" t="s">
+        <v>31</v>
+      </c>
+      <c r="T952" t="s">
+        <v>24</v>
+      </c>
+      <c r="U952">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="953" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A953" t="s">
+        <v>577</v>
+      </c>
+      <c r="B953" t="s">
+        <v>117</v>
+      </c>
+      <c r="C953">
+        <v>1</v>
+      </c>
+      <c r="D953">
+        <v>1</v>
+      </c>
+      <c r="E953">
+        <v>3</v>
+      </c>
+      <c r="F953">
+        <v>0</v>
+      </c>
+      <c r="G953">
+        <v>22</v>
+      </c>
+      <c r="H953">
+        <v>1</v>
+      </c>
+      <c r="I953">
+        <v>22</v>
+      </c>
+      <c r="J953">
+        <v>7.33</v>
+      </c>
+      <c r="K953">
+        <v>0</v>
+      </c>
+      <c r="L953">
+        <v>0</v>
+      </c>
+      <c r="M953" s="1">
+        <v>44562</v>
+      </c>
+      <c r="N953" s="1">
+        <v>44562</v>
+      </c>
+      <c r="O953">
+        <v>18</v>
+      </c>
+      <c r="P953">
+        <v>10</v>
+      </c>
+      <c r="Q953">
+        <v>3</v>
+      </c>
+      <c r="R953">
+        <v>0</v>
+      </c>
+      <c r="S953" t="s">
+        <v>107</v>
+      </c>
+      <c r="T953" t="s">
+        <v>24</v>
+      </c>
+      <c r="U953">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="954" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A954" t="s">
+        <v>577</v>
+      </c>
+      <c r="B954" t="s">
+        <v>196</v>
+      </c>
+      <c r="C954">
+        <v>1</v>
+      </c>
+      <c r="D954">
+        <v>1</v>
+      </c>
+      <c r="E954">
+        <v>1.4</v>
+      </c>
+      <c r="F954">
+        <v>0</v>
+      </c>
+      <c r="G954">
+        <v>19</v>
+      </c>
+      <c r="H954">
+        <v>1</v>
+      </c>
+      <c r="I954">
+        <v>19</v>
+      </c>
+      <c r="J954">
+        <v>11.4</v>
+      </c>
+      <c r="K954">
+        <v>0</v>
+      </c>
+      <c r="L954">
+        <v>0</v>
+      </c>
+      <c r="M954" s="1">
+        <v>43466</v>
+      </c>
+      <c r="N954" s="1">
+        <v>43466</v>
+      </c>
+      <c r="O954">
+        <v>10</v>
+      </c>
+      <c r="P954">
+        <v>4</v>
+      </c>
+      <c r="Q954">
+        <v>2</v>
+      </c>
+      <c r="R954">
+        <v>0</v>
+      </c>
+      <c r="S954" t="s">
+        <v>334</v>
+      </c>
+      <c r="T954" t="s">
+        <v>24</v>
+      </c>
+      <c r="U954">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="955" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A955" t="s">
+        <v>577</v>
+      </c>
+      <c r="B955" t="s">
+        <v>578</v>
+      </c>
+      <c r="C955">
+        <v>1</v>
+      </c>
+      <c r="D955">
+        <v>1</v>
+      </c>
+      <c r="E955">
+        <v>1</v>
+      </c>
+      <c r="F955">
+        <v>0</v>
+      </c>
+      <c r="G955">
+        <v>13</v>
+      </c>
+      <c r="H955">
+        <v>0</v>
+      </c>
+      <c r="J955">
+        <v>13</v>
+      </c>
+      <c r="K955">
+        <v>0</v>
+      </c>
+      <c r="L955">
+        <v>0</v>
+      </c>
+      <c r="M955" t="s">
+        <v>50</v>
+      </c>
+      <c r="N955" t="s">
+        <v>50</v>
+      </c>
+      <c r="O955">
+        <v>6</v>
+      </c>
+      <c r="P955">
+        <v>2</v>
+      </c>
+      <c r="Q955">
+        <v>1</v>
+      </c>
+      <c r="R955">
+        <v>1</v>
+      </c>
+      <c r="S955" t="s">
+        <v>31</v>
+      </c>
+      <c r="T955" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="956" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A956" t="s">
+        <v>577</v>
+      </c>
+      <c r="B956" t="s">
+        <v>579</v>
+      </c>
+      <c r="C956">
+        <v>1</v>
+      </c>
+      <c r="D956">
+        <v>1</v>
+      </c>
+      <c r="E956">
+        <v>2</v>
+      </c>
+      <c r="F956">
+        <v>0</v>
+      </c>
+      <c r="G956">
+        <v>13</v>
+      </c>
+      <c r="H956">
+        <v>0</v>
+      </c>
+      <c r="J956">
+        <v>6.5</v>
+      </c>
+      <c r="K956">
+        <v>0</v>
+      </c>
+      <c r="L956">
+        <v>0</v>
+      </c>
+      <c r="M956" t="s">
+        <v>50</v>
+      </c>
+      <c r="N956" t="s">
+        <v>50</v>
+      </c>
+      <c r="O956">
+        <v>12</v>
+      </c>
+      <c r="P956">
+        <v>6</v>
+      </c>
+      <c r="Q956">
+        <v>2</v>
+      </c>
+      <c r="R956">
+        <v>0</v>
+      </c>
+      <c r="S956" t="s">
+        <v>24</v>
+      </c>
+      <c r="T956" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="957" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A957" t="s">
+        <v>577</v>
+      </c>
+      <c r="B957" t="s">
+        <v>580</v>
+      </c>
+      <c r="C957">
+        <v>1</v>
+      </c>
+      <c r="D957">
+        <v>1</v>
+      </c>
+      <c r="E957">
+        <v>3.5</v>
+      </c>
+      <c r="F957">
+        <v>0</v>
+      </c>
+      <c r="G957">
+        <v>20</v>
+      </c>
+      <c r="H957">
+        <v>4</v>
+      </c>
+      <c r="I957">
+        <v>5</v>
+      </c>
+      <c r="J957">
+        <v>5.22</v>
+      </c>
+      <c r="K957">
+        <v>0</v>
+      </c>
+      <c r="L957">
+        <v>0</v>
+      </c>
+      <c r="M957" s="1">
+        <v>43922</v>
+      </c>
+      <c r="N957" s="1">
+        <v>43922</v>
+      </c>
+      <c r="O957">
+        <v>23</v>
+      </c>
+      <c r="P957">
+        <v>15</v>
+      </c>
+      <c r="Q957">
+        <v>2</v>
+      </c>
+      <c r="R957">
+        <v>0</v>
+      </c>
+      <c r="S957" t="s">
+        <v>46</v>
+      </c>
+      <c r="T957" t="s">
+        <v>24</v>
+      </c>
+      <c r="U957">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="958" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A958" t="s">
+        <v>577</v>
+      </c>
+      <c r="B958" t="s">
+        <v>125</v>
+      </c>
+      <c r="C958">
+        <v>1</v>
+      </c>
+      <c r="D958">
+        <v>1</v>
+      </c>
+      <c r="E958">
+        <v>3</v>
+      </c>
+      <c r="F958">
+        <v>0</v>
+      </c>
+      <c r="G958">
+        <v>13</v>
+      </c>
+      <c r="H958">
+        <v>0</v>
+      </c>
+      <c r="J958">
+        <v>4.33</v>
+      </c>
+      <c r="K958">
+        <v>0</v>
+      </c>
+      <c r="L958">
+        <v>0</v>
+      </c>
+      <c r="M958" t="s">
+        <v>50</v>
+      </c>
+      <c r="N958" t="s">
+        <v>50</v>
+      </c>
+      <c r="O958">
+        <v>18</v>
+      </c>
+      <c r="P958">
+        <v>6</v>
+      </c>
+      <c r="Q958">
+        <v>0</v>
+      </c>
+      <c r="R958">
+        <v>0</v>
+      </c>
+      <c r="S958" t="s">
+        <v>24</v>
+      </c>
+      <c r="T958" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="959" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A959" t="s">
+        <v>577</v>
+      </c>
+      <c r="B959" t="s">
+        <v>41</v>
+      </c>
+      <c r="C959">
+        <v>1</v>
+      </c>
+      <c r="D959">
+        <v>1</v>
+      </c>
+      <c r="E959">
+        <v>3</v>
+      </c>
+      <c r="F959">
+        <v>0</v>
+      </c>
+      <c r="G959">
+        <v>27</v>
+      </c>
+      <c r="H959">
+        <v>1</v>
+      </c>
+      <c r="I959">
+        <v>27</v>
+      </c>
+      <c r="J959">
+        <v>9</v>
+      </c>
+      <c r="K959">
+        <v>0</v>
+      </c>
+      <c r="L959">
+        <v>0</v>
+      </c>
+      <c r="M959" s="1">
+        <v>46388</v>
+      </c>
+      <c r="N959" s="1">
+        <v>46388</v>
+      </c>
+      <c r="O959">
+        <v>18</v>
+      </c>
+      <c r="P959">
+        <v>10</v>
+      </c>
+      <c r="Q959">
+        <v>3</v>
+      </c>
+      <c r="R959">
+        <v>0</v>
+      </c>
+      <c r="S959" t="s">
+        <v>187</v>
+      </c>
+      <c r="T959" t="s">
+        <v>24</v>
+      </c>
+      <c r="U959">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Midweek League bowling stats for season.xlsx
+++ b/NV Play Midweek League bowling stats for season.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="20260529-000142-bowling-stats-g" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4667" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4667" uniqueCount="579">
   <si>
     <t>Group</t>
   </si>
@@ -1527,9 +1527,6 @@
     <t>Mahesh Maniyan Baby</t>
   </si>
   <si>
-    <t>Pawan Thakur</t>
-  </si>
-  <si>
     <t>Belfast Superkings MW XI v PSNI MW XI, TBC - 2 July 2026</t>
   </si>
   <si>
@@ -1614,9 +1611,6 @@
     <t>Muckamore MW2 XI v Arches MW XI, Moylena - 8 July 2026</t>
   </si>
   <si>
-    <t>Pavan Kumar</t>
-  </si>
-  <si>
     <t>Wasim SM</t>
   </si>
   <si>
@@ -1692,9 +1686,6 @@
     <t>Aryan Thakur</t>
   </si>
   <si>
-    <t>Pavan Thakur</t>
-  </si>
-  <si>
     <t>Robin Varkey</t>
   </si>
   <si>
@@ -1762,6 +1753,9 @@
   </si>
   <si>
     <t>Harry Stone</t>
+  </si>
+  <si>
+    <t>Pawan Kumar</t>
   </si>
 </sst>
 </file>
@@ -37018,7 +37012,7 @@
         <v>405</v>
       </c>
       <c r="B552" t="s">
-        <v>502</v>
+        <v>578</v>
       </c>
       <c r="C552">
         <v>1</v>
@@ -41922,7 +41916,7 @@
     </row>
     <row r="631" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B631" t="s">
         <v>443</v>
@@ -41981,7 +41975,7 @@
     </row>
     <row r="632" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B632" t="s">
         <v>27</v>
@@ -42040,7 +42034,7 @@
     </row>
     <row r="633" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B633" t="s">
         <v>343</v>
@@ -42099,7 +42093,7 @@
     </row>
     <row r="634" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B634" t="s">
         <v>278</v>
@@ -42158,10 +42152,10 @@
     </row>
     <row r="635" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
+        <v>502</v>
+      </c>
+      <c r="B635" t="s">
         <v>503</v>
-      </c>
-      <c r="B635" t="s">
-        <v>504</v>
       </c>
       <c r="C635">
         <v>1</v>
@@ -42217,7 +42211,7 @@
     </row>
     <row r="636" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B636" t="s">
         <v>385</v>
@@ -42276,7 +42270,7 @@
     </row>
     <row r="637" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B637" t="s">
         <v>32</v>
@@ -42335,7 +42329,7 @@
     </row>
     <row r="638" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B638" t="s">
         <v>37</v>
@@ -42394,7 +42388,7 @@
     </row>
     <row r="639" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B639" t="s">
         <v>386</v>
@@ -42453,10 +42447,10 @@
     </row>
     <row r="640" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B640" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C640">
         <v>1</v>
@@ -42518,7 +42512,7 @@
     </row>
     <row r="641" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B641" t="s">
         <v>441</v>
@@ -42583,7 +42577,7 @@
     </row>
     <row r="642" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B642" t="s">
         <v>389</v>
@@ -42648,7 +42642,7 @@
     </row>
     <row r="643" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B643" t="s">
         <v>458</v>
@@ -43797,10 +43791,10 @@
         <v>0</v>
       </c>
       <c r="M661" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N661" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="O661">
         <v>4</v>
@@ -45258,7 +45252,7 @@
     </row>
     <row r="685" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B685" t="s">
         <v>114</v>
@@ -45323,7 +45317,7 @@
     </row>
     <row r="686" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B686" t="s">
         <v>378</v>
@@ -45382,7 +45376,7 @@
     </row>
     <row r="687" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B687" t="s">
         <v>54</v>
@@ -45441,7 +45435,7 @@
     </row>
     <row r="688" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B688" t="s">
         <v>480</v>
@@ -45506,7 +45500,7 @@
     </row>
     <row r="689" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B689" t="s">
         <v>330</v>
@@ -45571,7 +45565,7 @@
     </row>
     <row r="690" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B690" t="s">
         <v>394</v>
@@ -45636,11 +45630,11 @@
     </row>
     <row r="691" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
+        <v>506</v>
+      </c>
+      <c r="B691" t="s">
         <v>507</v>
       </c>
-      <c r="B691" t="s">
-        <v>508</v>
-      </c>
       <c r="C691">
         <v>1</v>
       </c>
@@ -45669,10 +45663,10 @@
         <v>0</v>
       </c>
       <c r="M691" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N691" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="O691">
         <v>6</v>
@@ -45695,7 +45689,7 @@
     </row>
     <row r="692" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B692" t="s">
         <v>248</v>
@@ -45754,7 +45748,7 @@
     </row>
     <row r="693" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B693" t="s">
         <v>122</v>
@@ -45805,7 +45799,7 @@
         <v>1</v>
       </c>
       <c r="S693" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="T693" t="s">
         <v>24</v>
@@ -45813,7 +45807,7 @@
     </row>
     <row r="694" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B694" t="s">
         <v>249</v>
@@ -45878,7 +45872,7 @@
     </row>
     <row r="695" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B695" t="s">
         <v>333</v>
@@ -45943,7 +45937,7 @@
     </row>
     <row r="696" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B696" t="s">
         <v>483</v>
@@ -46002,7 +45996,7 @@
     </row>
     <row r="697" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B697" t="s">
         <v>59</v>
@@ -46067,7 +46061,7 @@
     </row>
     <row r="698" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B698" t="s">
         <v>486</v>
@@ -46126,10 +46120,10 @@
     </row>
     <row r="699" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
+        <v>509</v>
+      </c>
+      <c r="B699" t="s">
         <v>510</v>
-      </c>
-      <c r="B699" t="s">
-        <v>511</v>
       </c>
       <c r="C699">
         <v>1</v>
@@ -46180,7 +46174,7 @@
         <v>1</v>
       </c>
       <c r="S699" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="T699" t="s">
         <v>24</v>
@@ -46191,7 +46185,7 @@
     </row>
     <row r="700" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B700" t="s">
         <v>45</v>
@@ -46256,7 +46250,7 @@
     </row>
     <row r="701" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B701" t="s">
         <v>313</v>
@@ -46321,7 +46315,7 @@
     </row>
     <row r="702" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B702" t="s">
         <v>246</v>
@@ -46386,10 +46380,10 @@
     </row>
     <row r="703" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B703" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C703">
         <v>1</v>
@@ -46451,7 +46445,7 @@
     </row>
     <row r="704" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B704" t="s">
         <v>501</v>
@@ -46516,7 +46510,7 @@
     </row>
     <row r="705" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B705" t="s">
         <v>256</v>
@@ -46581,7 +46575,7 @@
     </row>
     <row r="706" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B706" t="s">
         <v>358</v>
@@ -46646,7 +46640,7 @@
     </row>
     <row r="707" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B707" t="s">
         <v>469</v>
@@ -46679,10 +46673,10 @@
         <v>0</v>
       </c>
       <c r="M707" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N707" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="O707">
         <v>6</v>
@@ -46705,10 +46699,10 @@
     </row>
     <row r="708" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B708" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C708">
         <v>1</v>
@@ -46770,10 +46764,10 @@
     </row>
     <row r="709" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B709" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C709">
         <v>1</v>
@@ -46829,7 +46823,7 @@
     </row>
     <row r="710" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B710" t="s">
         <v>60</v>
@@ -46894,7 +46888,7 @@
     </row>
     <row r="711" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B711" t="s">
         <v>443</v>
@@ -46959,7 +46953,7 @@
     </row>
     <row r="712" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B712" t="s">
         <v>343</v>
@@ -47018,7 +47012,7 @@
     </row>
     <row r="713" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B713" t="s">
         <v>278</v>
@@ -47069,7 +47063,7 @@
         <v>1</v>
       </c>
       <c r="S713" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="T713" t="s">
         <v>24</v>
@@ -47077,7 +47071,7 @@
     </row>
     <row r="714" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B714" t="s">
         <v>180</v>
@@ -47142,7 +47136,7 @@
     </row>
     <row r="715" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B715" t="s">
         <v>265</v>
@@ -47207,7 +47201,7 @@
     </row>
     <row r="716" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B716" t="s">
         <v>410</v>
@@ -47272,7 +47266,7 @@
     </row>
     <row r="717" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B717" t="s">
         <v>32</v>
@@ -47337,7 +47331,7 @@
     </row>
     <row r="718" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B718" t="s">
         <v>184</v>
@@ -47402,7 +47396,7 @@
     </row>
     <row r="719" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B719" t="s">
         <v>37</v>
@@ -47467,7 +47461,7 @@
     </row>
     <row r="720" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B720" t="s">
         <v>266</v>
@@ -47526,10 +47520,10 @@
     </row>
     <row r="721" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B721" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C721">
         <v>1</v>
@@ -47591,7 +47585,7 @@
     </row>
     <row r="722" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B722" t="s">
         <v>201</v>
@@ -47656,10 +47650,10 @@
     </row>
     <row r="723" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
+        <v>518</v>
+      </c>
+      <c r="B723" t="s">
         <v>519</v>
-      </c>
-      <c r="B723" t="s">
-        <v>520</v>
       </c>
       <c r="C723">
         <v>1</v>
@@ -47715,10 +47709,10 @@
     </row>
     <row r="724" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B724" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C724">
         <v>1</v>
@@ -47780,7 +47774,7 @@
     </row>
     <row r="725" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B725" t="s">
         <v>230</v>
@@ -47839,10 +47833,10 @@
     </row>
     <row r="726" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B726" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C726">
         <v>1</v>
@@ -47904,7 +47898,7 @@
     </row>
     <row r="727" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B727" t="s">
         <v>116</v>
@@ -47969,10 +47963,10 @@
     </row>
     <row r="728" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B728" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C728">
         <v>1</v>
@@ -48034,7 +48028,7 @@
     </row>
     <row r="729" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B729" t="s">
         <v>119</v>
@@ -48093,10 +48087,10 @@
     </row>
     <row r="730" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B730" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C730">
         <v>1</v>
@@ -48152,7 +48146,7 @@
     </row>
     <row r="731" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B731" t="s">
         <v>137</v>
@@ -48211,10 +48205,10 @@
     </row>
     <row r="732" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B732" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C732">
         <v>1</v>
@@ -48276,7 +48270,7 @@
     </row>
     <row r="733" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B733" t="s">
         <v>39</v>
@@ -48335,10 +48329,10 @@
     </row>
     <row r="734" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B734" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C734">
         <v>1</v>
@@ -48400,7 +48394,7 @@
     </row>
     <row r="735" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B735" t="s">
         <v>214</v>
@@ -48459,7 +48453,7 @@
     </row>
     <row r="736" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B736" t="s">
         <v>467</v>
@@ -48518,7 +48512,7 @@
     </row>
     <row r="737" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B737" t="s">
         <v>235</v>
@@ -48577,7 +48571,7 @@
     </row>
     <row r="738" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B738" t="s">
         <v>25</v>
@@ -48636,7 +48630,7 @@
     </row>
     <row r="739" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B739" t="s">
         <v>205</v>
@@ -48695,7 +48689,7 @@
     </row>
     <row r="740" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B740" t="s">
         <v>164</v>
@@ -48760,7 +48754,7 @@
     </row>
     <row r="741" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B741" t="s">
         <v>309</v>
@@ -48819,10 +48813,10 @@
     </row>
     <row r="742" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
+        <v>526</v>
+      </c>
+      <c r="B742" t="s">
         <v>527</v>
-      </c>
-      <c r="B742" t="s">
-        <v>528</v>
       </c>
       <c r="C742">
         <v>1</v>
@@ -48884,10 +48878,10 @@
     </row>
     <row r="743" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B743" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C743">
         <v>1</v>
@@ -48943,7 +48937,7 @@
     </row>
     <row r="744" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B744" t="s">
         <v>431</v>
@@ -49008,7 +49002,7 @@
     </row>
     <row r="745" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B745" t="s">
         <v>310</v>
@@ -49073,7 +49067,7 @@
     </row>
     <row r="746" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B746" t="s">
         <v>400</v>
@@ -49132,7 +49126,7 @@
     </row>
     <row r="747" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B747" t="s">
         <v>41</v>
@@ -49197,7 +49191,7 @@
     </row>
     <row r="748" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B748" t="s">
         <v>202</v>
@@ -49256,7 +49250,7 @@
     </row>
     <row r="749" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B749" t="s">
         <v>130</v>
@@ -49315,7 +49309,7 @@
     </row>
     <row r="750" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B750" t="s">
         <v>204</v>
@@ -49374,7 +49368,7 @@
     </row>
     <row r="751" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B751" t="s">
         <v>302</v>
@@ -49433,7 +49427,7 @@
     </row>
     <row r="752" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B752" t="s">
         <v>427</v>
@@ -49492,10 +49486,10 @@
     </row>
     <row r="753" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B753" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="C753">
         <v>1</v>
@@ -49557,7 +49551,7 @@
     </row>
     <row r="754" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B754" t="s">
         <v>208</v>
@@ -49616,7 +49610,7 @@
     </row>
     <row r="755" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B755" t="s">
         <v>212</v>
@@ -49681,7 +49675,7 @@
     </row>
     <row r="756" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B756" t="s">
         <v>138</v>
@@ -49746,7 +49740,7 @@
     </row>
     <row r="757" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B757" t="s">
         <v>139</v>
@@ -49805,10 +49799,10 @@
     </row>
     <row r="758" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
+        <v>529</v>
+      </c>
+      <c r="B758" t="s">
         <v>530</v>
-      </c>
-      <c r="B758" t="s">
-        <v>532</v>
       </c>
       <c r="C758">
         <v>1</v>
@@ -49864,7 +49858,7 @@
     </row>
     <row r="759" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B759" t="s">
         <v>140</v>
@@ -49929,7 +49923,7 @@
     </row>
     <row r="760" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B760" t="s">
         <v>371</v>
@@ -49986,7 +49980,7 @@
         <v>24</v>
       </c>
       <c r="T760" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="U760">
         <v>6</v>
@@ -49994,7 +49988,7 @@
     </row>
     <row r="761" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B761" t="s">
         <v>114</v>
@@ -50059,7 +50053,7 @@
     </row>
     <row r="762" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B762" t="s">
         <v>427</v>
@@ -50118,10 +50112,10 @@
     </row>
     <row r="763" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B763" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C763">
         <v>1</v>
@@ -50177,7 +50171,7 @@
     </row>
     <row r="764" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B764" t="s">
         <v>121</v>
@@ -50236,10 +50230,10 @@
     </row>
     <row r="765" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
+        <v>532</v>
+      </c>
+      <c r="B765" t="s">
         <v>534</v>
-      </c>
-      <c r="B765" t="s">
-        <v>536</v>
       </c>
       <c r="C765">
         <v>1</v>
@@ -50295,7 +50289,7 @@
     </row>
     <row r="766" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B766" t="s">
         <v>124</v>
@@ -50360,7 +50354,7 @@
     </row>
     <row r="767" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B767" t="s">
         <v>138</v>
@@ -50425,7 +50419,7 @@
     </row>
     <row r="768" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B768" t="s">
         <v>59</v>
@@ -50490,7 +50484,7 @@
     </row>
     <row r="769" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B769" t="s">
         <v>140</v>
@@ -50555,7 +50549,7 @@
     </row>
     <row r="770" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B770" t="s">
         <v>486</v>
@@ -50620,7 +50614,7 @@
     </row>
     <row r="771" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B771" t="s">
         <v>126</v>
@@ -50685,7 +50679,7 @@
     </row>
     <row r="772" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B772" t="s">
         <v>22</v>
@@ -50750,7 +50744,7 @@
     </row>
     <row r="773" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B773" t="s">
         <v>275</v>
@@ -50809,10 +50803,10 @@
     </row>
     <row r="774" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B774" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C774">
         <v>1</v>
@@ -50874,7 +50868,7 @@
     </row>
     <row r="775" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B775" t="s">
         <v>277</v>
@@ -50933,7 +50927,7 @@
     </row>
     <row r="776" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B776" t="s">
         <v>116</v>
@@ -50998,7 +50992,7 @@
     </row>
     <row r="777" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B777" t="s">
         <v>169</v>
@@ -51063,7 +51057,7 @@
     </row>
     <row r="778" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B778" t="s">
         <v>400</v>
@@ -51122,7 +51116,7 @@
     </row>
     <row r="779" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B779" t="s">
         <v>137</v>
@@ -51187,7 +51181,7 @@
     </row>
     <row r="780" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B780" t="s">
         <v>364</v>
@@ -51246,7 +51240,7 @@
     </row>
     <row r="781" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B781" t="s">
         <v>174</v>
@@ -51311,7 +51305,7 @@
     </row>
     <row r="782" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B782" t="s">
         <v>41</v>
@@ -51376,7 +51370,7 @@
     </row>
     <row r="783" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B783" t="s">
         <v>366</v>
@@ -51435,10 +51429,10 @@
     </row>
     <row r="784" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B784" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C784">
         <v>1</v>
@@ -51500,10 +51494,10 @@
     </row>
     <row r="785" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
+        <v>537</v>
+      </c>
+      <c r="B785" t="s">
         <v>539</v>
-      </c>
-      <c r="B785" t="s">
-        <v>541</v>
       </c>
       <c r="C785">
         <v>1</v>
@@ -51565,7 +51559,7 @@
     </row>
     <row r="786" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B786" t="s">
         <v>104</v>
@@ -51630,7 +51624,7 @@
     </row>
     <row r="787" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B787" t="s">
         <v>398</v>
@@ -51689,10 +51683,10 @@
     </row>
     <row r="788" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B788" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C788">
         <v>1</v>
@@ -51748,7 +51742,7 @@
     </row>
     <row r="789" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B789" t="s">
         <v>183</v>
@@ -51813,7 +51807,7 @@
     </row>
     <row r="790" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B790" t="s">
         <v>106</v>
@@ -51872,7 +51866,7 @@
     </row>
     <row r="791" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B791" t="s">
         <v>108</v>
@@ -51937,7 +51931,7 @@
     </row>
     <row r="792" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B792" t="s">
         <v>399</v>
@@ -51996,7 +51990,7 @@
     </row>
     <row r="793" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B793" t="s">
         <v>441</v>
@@ -52055,10 +52049,10 @@
     </row>
     <row r="794" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B794" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C794">
         <v>1</v>
@@ -52120,7 +52114,7 @@
     </row>
     <row r="795" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B795" t="s">
         <v>458</v>
@@ -52179,7 +52173,7 @@
     </row>
     <row r="796" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B796" t="s">
         <v>253</v>
@@ -52238,7 +52232,7 @@
     </row>
     <row r="797" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B797" t="s">
         <v>142</v>
@@ -52297,7 +52291,7 @@
     </row>
     <row r="798" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B798" t="s">
         <v>146</v>
@@ -52362,7 +52356,7 @@
     </row>
     <row r="799" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B799" t="s">
         <v>284</v>
@@ -52427,10 +52421,10 @@
     </row>
     <row r="800" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B800" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C800">
         <v>1</v>
@@ -52492,10 +52486,10 @@
     </row>
     <row r="801" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B801" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C801">
         <v>1</v>
@@ -52557,7 +52551,7 @@
     </row>
     <row r="802" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B802" t="s">
         <v>482</v>
@@ -52622,7 +52616,7 @@
     </row>
     <row r="803" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B803" t="s">
         <v>257</v>
@@ -52687,10 +52681,10 @@
     </row>
     <row r="804" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
+        <v>541</v>
+      </c>
+      <c r="B804" t="s">
         <v>543</v>
-      </c>
-      <c r="B804" t="s">
-        <v>545</v>
       </c>
       <c r="C804">
         <v>1</v>
@@ -52752,7 +52746,7 @@
     </row>
     <row r="805" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B805" t="s">
         <v>447</v>
@@ -52811,10 +52805,10 @@
     </row>
     <row r="806" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B806" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C806">
         <v>1</v>
@@ -52870,7 +52864,7 @@
     </row>
     <row r="807" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B807" t="s">
         <v>448</v>
@@ -52929,7 +52923,7 @@
     </row>
     <row r="808" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B808" t="s">
         <v>443</v>
@@ -52994,7 +52988,7 @@
     </row>
     <row r="809" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B809" t="s">
         <v>27</v>
@@ -53053,7 +53047,7 @@
     </row>
     <row r="810" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B810" t="s">
         <v>343</v>
@@ -53112,7 +53106,7 @@
     </row>
     <row r="811" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B811" t="s">
         <v>103</v>
@@ -53171,7 +53165,7 @@
     </row>
     <row r="812" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B812" t="s">
         <v>278</v>
@@ -53236,7 +53230,7 @@
     </row>
     <row r="813" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B813" t="s">
         <v>105</v>
@@ -53301,7 +53295,7 @@
     </row>
     <row r="814" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B814" t="s">
         <v>32</v>
@@ -53366,7 +53360,7 @@
     </row>
     <row r="815" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B815" t="s">
         <v>280</v>
@@ -53425,7 +53419,7 @@
     </row>
     <row r="816" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B816" t="s">
         <v>434</v>
@@ -53484,10 +53478,10 @@
     </row>
     <row r="817" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B817" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C817">
         <v>1</v>
@@ -53549,10 +53543,10 @@
     </row>
     <row r="818" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
+        <v>545</v>
+      </c>
+      <c r="B818" t="s">
         <v>547</v>
-      </c>
-      <c r="B818" t="s">
-        <v>549</v>
       </c>
       <c r="C818">
         <v>1</v>
@@ -53608,7 +53602,7 @@
     </row>
     <row r="819" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B819" t="s">
         <v>426</v>
@@ -53673,10 +53667,10 @@
     </row>
     <row r="820" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B820" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C820">
         <v>1</v>
@@ -53738,10 +53732,10 @@
     </row>
     <row r="821" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B821" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C821">
         <v>1</v>
@@ -53803,7 +53797,7 @@
     </row>
     <row r="822" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B822" t="s">
         <v>43</v>
@@ -53868,7 +53862,7 @@
     </row>
     <row r="823" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B823" t="s">
         <v>114</v>
@@ -53927,7 +53921,7 @@
     </row>
     <row r="824" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B824" t="s">
         <v>202</v>
@@ -53986,7 +53980,7 @@
     </row>
     <row r="825" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B825" t="s">
         <v>204</v>
@@ -54051,7 +54045,7 @@
     </row>
     <row r="826" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B826" t="s">
         <v>271</v>
@@ -54116,7 +54110,7 @@
     </row>
     <row r="827" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B827" t="s">
         <v>302</v>
@@ -54181,7 +54175,7 @@
     </row>
     <row r="828" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B828" t="s">
         <v>208</v>
@@ -54246,7 +54240,7 @@
     </row>
     <row r="829" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B829" t="s">
         <v>121</v>
@@ -54305,7 +54299,7 @@
     </row>
     <row r="830" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B830" t="s">
         <v>124</v>
@@ -54364,7 +54358,7 @@
     </row>
     <row r="831" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B831" t="s">
         <v>212</v>
@@ -54429,7 +54423,7 @@
     </row>
     <row r="832" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B832" t="s">
         <v>59</v>
@@ -54494,10 +54488,10 @@
     </row>
     <row r="833" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B833" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C833">
         <v>1</v>
@@ -54559,7 +54553,7 @@
     </row>
     <row r="834" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B834" t="s">
         <v>203</v>
@@ -54618,10 +54612,10 @@
     </row>
     <row r="835" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B835" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C835">
         <v>1</v>
@@ -54677,7 +54671,7 @@
     </row>
     <row r="836" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B836" t="s">
         <v>116</v>
@@ -54736,7 +54730,7 @@
     </row>
     <row r="837" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B837" t="s">
         <v>136</v>
@@ -54790,7 +54784,7 @@
         <v>0</v>
       </c>
       <c r="S837" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="T837" t="s">
         <v>24</v>
@@ -54801,10 +54795,10 @@
     </row>
     <row r="838" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B838" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C838">
         <v>1</v>
@@ -54860,7 +54854,7 @@
     </row>
     <row r="839" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B839" t="s">
         <v>196</v>
@@ -54925,7 +54919,7 @@
     </row>
     <row r="840" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B840" t="s">
         <v>493</v>
@@ -54990,10 +54984,10 @@
     </row>
     <row r="841" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B841" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C841">
         <v>1</v>
@@ -55049,7 +55043,7 @@
     </row>
     <row r="842" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B842" t="s">
         <v>138</v>
@@ -55114,7 +55108,7 @@
     </row>
     <row r="843" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B843" t="s">
         <v>370</v>
@@ -55179,7 +55173,7 @@
     </row>
     <row r="844" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B844" t="s">
         <v>140</v>
@@ -55238,10 +55232,10 @@
     </row>
     <row r="845" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
+        <v>552</v>
+      </c>
+      <c r="B845" t="s">
         <v>554</v>
-      </c>
-      <c r="B845" t="s">
-        <v>556</v>
       </c>
       <c r="C845">
         <v>1</v>
@@ -55297,10 +55291,10 @@
     </row>
     <row r="846" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B846" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="C846">
         <v>1</v>
@@ -55362,7 +55356,7 @@
     </row>
     <row r="847" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B847" t="s">
         <v>125</v>
@@ -55421,10 +55415,10 @@
     </row>
     <row r="848" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B848" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C848">
         <v>1</v>
@@ -55480,7 +55474,7 @@
     </row>
     <row r="849" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B849" t="s">
         <v>422</v>
@@ -55539,10 +55533,10 @@
     </row>
     <row r="850" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B850" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C850">
         <v>1</v>
@@ -55598,7 +55592,7 @@
     </row>
     <row r="851" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B851" t="s">
         <v>87</v>
@@ -55657,7 +55651,7 @@
     </row>
     <row r="852" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B852" t="s">
         <v>348</v>
@@ -55722,7 +55716,7 @@
     </row>
     <row r="853" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B853" t="s">
         <v>408</v>
@@ -55781,10 +55775,10 @@
     </row>
     <row r="854" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B854" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C854">
         <v>1</v>
@@ -55840,7 +55834,7 @@
     </row>
     <row r="855" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B855" t="s">
         <v>337</v>
@@ -55905,7 +55899,7 @@
     </row>
     <row r="856" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B856" t="s">
         <v>67</v>
@@ -55970,7 +55964,7 @@
     </row>
     <row r="857" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B857" t="s">
         <v>375</v>
@@ -56029,7 +56023,7 @@
     </row>
     <row r="858" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B858" t="s">
         <v>225</v>
@@ -56094,7 +56088,7 @@
     </row>
     <row r="859" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B859" t="s">
         <v>350</v>
@@ -56153,7 +56147,7 @@
     </row>
     <row r="860" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B860" t="s">
         <v>351</v>
@@ -56218,7 +56212,7 @@
     </row>
     <row r="861" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B861" t="s">
         <v>95</v>
@@ -56277,7 +56271,7 @@
     </row>
     <row r="862" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B862" t="s">
         <v>79</v>
@@ -56342,7 +56336,7 @@
     </row>
     <row r="863" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B863" t="s">
         <v>312</v>
@@ -56401,7 +56395,7 @@
     </row>
     <row r="864" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B864" t="s">
         <v>313</v>
@@ -56460,7 +56454,7 @@
     </row>
     <row r="865" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B865" t="s">
         <v>315</v>
@@ -56525,10 +56519,10 @@
     </row>
     <row r="866" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B866" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C866">
         <v>1</v>
@@ -56590,7 +56584,7 @@
     </row>
     <row r="867" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B867" t="s">
         <v>480</v>
@@ -56649,7 +56643,7 @@
     </row>
     <row r="868" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B868" t="s">
         <v>394</v>
@@ -56714,7 +56708,7 @@
     </row>
     <row r="869" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B869" t="s">
         <v>248</v>
@@ -56779,7 +56773,7 @@
     </row>
     <row r="870" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B870" t="s">
         <v>249</v>
@@ -56844,10 +56838,10 @@
     </row>
     <row r="871" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B871" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C871">
         <v>1</v>
@@ -56903,7 +56897,7 @@
     </row>
     <row r="872" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B872" t="s">
         <v>250</v>
@@ -56968,7 +56962,7 @@
     </row>
     <row r="873" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B873" t="s">
         <v>333</v>
@@ -57033,7 +57027,7 @@
     </row>
     <row r="874" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B874" t="s">
         <v>45</v>
@@ -57098,10 +57092,10 @@
     </row>
     <row r="875" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B875" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C875">
         <v>1</v>
@@ -57157,7 +57151,7 @@
     </row>
     <row r="876" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B876" t="s">
         <v>142</v>
@@ -57222,7 +57216,7 @@
     </row>
     <row r="877" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B877" t="s">
         <v>146</v>
@@ -57281,7 +57275,7 @@
     </row>
     <row r="878" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B878" t="s">
         <v>246</v>
@@ -57346,7 +57340,7 @@
     </row>
     <row r="879" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B879" t="s">
         <v>501</v>
@@ -57405,7 +57399,7 @@
     </row>
     <row r="880" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B880" t="s">
         <v>358</v>
@@ -57470,7 +57464,7 @@
     </row>
     <row r="881" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B881" t="s">
         <v>482</v>
@@ -57535,7 +57529,7 @@
     </row>
     <row r="882" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B882" t="s">
         <v>447</v>
@@ -57600,7 +57594,7 @@
     </row>
     <row r="883" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B883" t="s">
         <v>60</v>
@@ -57665,7 +57659,7 @@
     </row>
     <row r="884" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B884" t="s">
         <v>471</v>
@@ -57730,7 +57724,7 @@
     </row>
     <row r="885" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B885" t="s">
         <v>102</v>
@@ -57795,10 +57789,10 @@
     </row>
     <row r="886" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B886" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C886">
         <v>1</v>
@@ -57854,7 +57848,7 @@
     </row>
     <row r="887" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B887" t="s">
         <v>415</v>
@@ -57919,7 +57913,7 @@
     </row>
     <row r="888" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B888" t="s">
         <v>104</v>
@@ -57978,7 +57972,7 @@
     </row>
     <row r="889" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B889" t="s">
         <v>398</v>
@@ -58043,7 +58037,7 @@
     </row>
     <row r="890" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B890" t="s">
         <v>164</v>
@@ -58108,10 +58102,10 @@
     </row>
     <row r="891" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B891" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C891">
         <v>1</v>
@@ -58167,7 +58161,7 @@
     </row>
     <row r="892" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B892" t="s">
         <v>309</v>
@@ -58232,7 +58226,7 @@
     </row>
     <row r="893" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B893" t="s">
         <v>108</v>
@@ -58297,10 +58291,10 @@
     </row>
     <row r="894" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B894" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C894">
         <v>1</v>
@@ -58362,7 +58356,7 @@
     </row>
     <row r="895" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B895" t="s">
         <v>310</v>
@@ -58427,7 +58421,7 @@
     </row>
     <row r="896" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B896" t="s">
         <v>267</v>
@@ -58492,7 +58486,7 @@
     </row>
     <row r="897" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B897" t="s">
         <v>25</v>
@@ -58557,7 +58551,7 @@
     </row>
     <row r="898" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B898" t="s">
         <v>178</v>
@@ -58622,7 +58616,7 @@
     </row>
     <row r="899" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B899" t="s">
         <v>203</v>
@@ -58681,7 +58675,7 @@
     </row>
     <row r="900" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B900" t="s">
         <v>180</v>
@@ -58740,7 +58734,7 @@
     </row>
     <row r="901" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B901" t="s">
         <v>265</v>
@@ -58805,7 +58799,7 @@
     </row>
     <row r="902" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B902" t="s">
         <v>207</v>
@@ -58864,7 +58858,7 @@
     </row>
     <row r="903" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B903" t="s">
         <v>184</v>
@@ -58929,7 +58923,7 @@
     </row>
     <row r="904" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B904" t="s">
         <v>185</v>
@@ -58994,7 +58988,7 @@
     </row>
     <row r="905" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B905" t="s">
         <v>119</v>
@@ -59053,10 +59047,10 @@
     </row>
     <row r="906" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B906" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C906">
         <v>1</v>
@@ -59112,7 +59106,7 @@
     </row>
     <row r="907" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B907" t="s">
         <v>196</v>
@@ -59177,10 +59171,10 @@
     </row>
     <row r="908" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B908" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C908">
         <v>1</v>
@@ -59236,7 +59230,7 @@
     </row>
     <row r="909" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B909" t="s">
         <v>266</v>
@@ -59301,7 +59295,7 @@
     </row>
     <row r="910" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B910" t="s">
         <v>41</v>
@@ -59366,7 +59360,7 @@
     </row>
     <row r="911" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B911" t="s">
         <v>114</v>
@@ -59431,10 +59425,10 @@
     </row>
     <row r="912" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B912" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C912">
         <v>1</v>
@@ -59496,7 +59490,7 @@
     </row>
     <row r="913" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B913" t="s">
         <v>271</v>
@@ -59561,7 +59555,7 @@
     </row>
     <row r="914" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B914" t="s">
         <v>465</v>
@@ -59620,7 +59614,7 @@
     </row>
     <row r="915" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B915" t="s">
         <v>121</v>
@@ -59685,7 +59679,7 @@
     </row>
     <row r="916" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B916" t="s">
         <v>368</v>
@@ -59750,10 +59744,10 @@
     </row>
     <row r="917" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B917" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C917">
         <v>1</v>
@@ -59809,7 +59803,7 @@
     </row>
     <row r="918" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B918" t="s">
         <v>369</v>
@@ -59868,7 +59862,7 @@
     </row>
     <row r="919" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B919" t="s">
         <v>126</v>
@@ -59933,10 +59927,10 @@
     </row>
     <row r="920" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B920" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C920">
         <v>1</v>
@@ -59992,7 +59986,7 @@
     </row>
     <row r="921" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B921" t="s">
         <v>235</v>
@@ -60057,7 +60051,7 @@
     </row>
     <row r="922" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B922" t="s">
         <v>277</v>
@@ -60116,10 +60110,10 @@
     </row>
     <row r="923" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B923" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C923">
         <v>1</v>
@@ -60181,7 +60175,7 @@
     </row>
     <row r="924" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B924" t="s">
         <v>161</v>
@@ -60246,7 +60240,7 @@
     </row>
     <row r="925" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B925" t="s">
         <v>385</v>
@@ -60305,7 +60299,7 @@
     </row>
     <row r="926" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B926" t="s">
         <v>183</v>
@@ -60364,7 +60358,7 @@
     </row>
     <row r="927" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B927" t="s">
         <v>169</v>
@@ -60429,7 +60423,7 @@
     </row>
     <row r="928" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B928" t="s">
         <v>188</v>
@@ -60494,10 +60488,10 @@
     </row>
     <row r="929" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B929" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C929">
         <v>1</v>
@@ -60559,7 +60553,7 @@
     </row>
     <row r="930" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B930" t="s">
         <v>441</v>
@@ -60624,7 +60618,7 @@
     </row>
     <row r="931" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B931" t="s">
         <v>364</v>
@@ -60683,7 +60677,7 @@
     </row>
     <row r="932" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B932" t="s">
         <v>366</v>
@@ -60742,7 +60736,7 @@
     </row>
     <row r="933" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B933" t="s">
         <v>432</v>
@@ -60807,7 +60801,7 @@
     </row>
     <row r="934" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B934" t="s">
         <v>377</v>
@@ -60872,10 +60866,10 @@
     </row>
     <row r="935" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B935" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C935">
         <v>1</v>
@@ -60931,7 +60925,7 @@
     </row>
     <row r="936" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B936" t="s">
         <v>378</v>
@@ -60990,10 +60984,10 @@
     </row>
     <row r="937" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B937" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C937">
         <v>1</v>
@@ -61049,10 +61043,10 @@
     </row>
     <row r="938" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
+        <v>570</v>
+      </c>
+      <c r="B938" t="s">
         <v>573</v>
-      </c>
-      <c r="B938" t="s">
-        <v>576</v>
       </c>
       <c r="C938">
         <v>1</v>
@@ -61108,7 +61102,7 @@
     </row>
     <row r="939" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B939" t="s">
         <v>315</v>
@@ -61173,10 +61167,10 @@
     </row>
     <row r="940" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B940" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C940">
         <v>1</v>
@@ -61232,10 +61226,10 @@
     </row>
     <row r="941" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B941" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C941">
         <v>1</v>
@@ -61291,7 +61285,7 @@
     </row>
     <row r="942" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B942" t="s">
         <v>54</v>
@@ -61356,7 +61350,7 @@
     </row>
     <row r="943" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B943" t="s">
         <v>257</v>
@@ -61415,7 +61409,7 @@
     </row>
     <row r="944" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B944" t="s">
         <v>318</v>
@@ -61474,7 +61468,7 @@
     </row>
     <row r="945" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B945" t="s">
         <v>259</v>
@@ -61533,7 +61527,7 @@
     </row>
     <row r="946" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B946" t="s">
         <v>59</v>
@@ -61592,7 +61586,7 @@
     </row>
     <row r="947" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B947" t="s">
         <v>86</v>
@@ -61651,7 +61645,7 @@
     </row>
     <row r="948" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B948" t="s">
         <v>322</v>
@@ -61710,7 +61704,7 @@
     </row>
     <row r="949" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B949" t="s">
         <v>323</v>
@@ -61769,7 +61763,7 @@
     </row>
     <row r="950" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B950" t="s">
         <v>232</v>
@@ -61834,7 +61828,7 @@
     </row>
     <row r="951" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B951" t="s">
         <v>116</v>
@@ -61893,7 +61887,7 @@
     </row>
     <row r="952" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B952" t="s">
         <v>492</v>
@@ -61958,7 +61952,7 @@
     </row>
     <row r="953" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B953" t="s">
         <v>117</v>
@@ -62023,7 +62017,7 @@
     </row>
     <row r="954" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B954" t="s">
         <v>196</v>
@@ -62088,10 +62082,10 @@
     </row>
     <row r="955" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B955" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C955">
         <v>1</v>
@@ -62147,10 +62141,10 @@
     </row>
     <row r="956" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B956" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C956">
         <v>1</v>
@@ -62206,10 +62200,10 @@
     </row>
     <row r="957" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
+        <v>574</v>
+      </c>
+      <c r="B957" t="s">
         <v>577</v>
-      </c>
-      <c r="B957" t="s">
-        <v>580</v>
       </c>
       <c r="C957">
         <v>1</v>
@@ -62271,7 +62265,7 @@
     </row>
     <row r="958" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B958" t="s">
         <v>125</v>
@@ -62330,7 +62324,7 @@
     </row>
     <row r="959" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B959" t="s">
         <v>41</v>

--- a/NV Play Midweek League bowling stats for season.xlsx
+++ b/NV Play Midweek League bowling stats for season.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="20260529-000142-bowling-stats-g" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4667" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4969" uniqueCount="596">
   <si>
     <t>Group</t>
   </si>
@@ -1757,6 +1757,57 @@
   <si>
     <t>Pawan Kumar</t>
   </si>
+  <si>
+    <t>CSNI MW XI v Arches MW XI, Stormont - 22 July 2026</t>
+  </si>
+  <si>
+    <t>Richard Gould Hocking</t>
+  </si>
+  <si>
+    <t>Dunmurry MW2 XI v Cooke Collegians MW XI, Fullerton Park - 22 July 2026</t>
+  </si>
+  <si>
+    <t>Billy Foster</t>
+  </si>
+  <si>
+    <t>Muckamore MW1 XI v Amigos Belfast MW XI, Moylena - 22 July 2026</t>
+  </si>
+  <si>
+    <t>Jack Kirkpatrick snr</t>
+  </si>
+  <si>
+    <t>Arjun Sasidharan</t>
+  </si>
+  <si>
+    <t>4 (12)</t>
+  </si>
+  <si>
+    <t>7 (10)</t>
+  </si>
+  <si>
+    <t>BISC MW XI v Ballymena MW XI, TBC - 22 July 2026</t>
+  </si>
+  <si>
+    <t>Hemanth Suma</t>
+  </si>
+  <si>
+    <t>15 (19)</t>
+  </si>
+  <si>
+    <t>Henry Montgomery</t>
+  </si>
+  <si>
+    <t>Rajendrakumar Patil</t>
+  </si>
+  <si>
+    <t>NIMACC MW XI v Instonians MW XI, TBC - 22 July 2026</t>
+  </si>
+  <si>
+    <t>Richard McKibbin</t>
+  </si>
+  <si>
+    <t>Byjo Varghese</t>
+  </si>
 </sst>
 </file>
 
@@ -2564,7 +2615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U959"/>
+  <dimension ref="A1:U1022"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="69.28515625" bestFit="1" customWidth="1"/>
@@ -62387,6 +62438,3951 @@
         <v>18</v>
       </c>
     </row>
+    <row r="960" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A960" t="s">
+        <v>579</v>
+      </c>
+      <c r="B960" t="s">
+        <v>348</v>
+      </c>
+      <c r="C960">
+        <v>1</v>
+      </c>
+      <c r="D960">
+        <v>1</v>
+      </c>
+      <c r="E960">
+        <v>4</v>
+      </c>
+      <c r="F960">
+        <v>0</v>
+      </c>
+      <c r="G960">
+        <v>22</v>
+      </c>
+      <c r="H960">
+        <v>2</v>
+      </c>
+      <c r="I960">
+        <v>11</v>
+      </c>
+      <c r="J960">
+        <v>5.5</v>
+      </c>
+      <c r="K960">
+        <v>0</v>
+      </c>
+      <c r="L960">
+        <v>0</v>
+      </c>
+      <c r="M960" s="1">
+        <v>44593</v>
+      </c>
+      <c r="N960" s="1">
+        <v>44593</v>
+      </c>
+      <c r="O960">
+        <v>24</v>
+      </c>
+      <c r="P960">
+        <v>12</v>
+      </c>
+      <c r="Q960">
+        <v>2</v>
+      </c>
+      <c r="R960">
+        <v>0</v>
+      </c>
+      <c r="S960" t="s">
+        <v>24</v>
+      </c>
+      <c r="T960" t="s">
+        <v>31</v>
+      </c>
+      <c r="U960">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="961" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A961" t="s">
+        <v>579</v>
+      </c>
+      <c r="B961" t="s">
+        <v>408</v>
+      </c>
+      <c r="C961">
+        <v>1</v>
+      </c>
+      <c r="D961">
+        <v>1</v>
+      </c>
+      <c r="E961">
+        <v>4</v>
+      </c>
+      <c r="F961">
+        <v>0</v>
+      </c>
+      <c r="G961">
+        <v>47</v>
+      </c>
+      <c r="H961">
+        <v>1</v>
+      </c>
+      <c r="I961">
+        <v>47</v>
+      </c>
+      <c r="J961">
+        <v>11.75</v>
+      </c>
+      <c r="K961">
+        <v>0</v>
+      </c>
+      <c r="L961">
+        <v>0</v>
+      </c>
+      <c r="M961" s="1">
+        <v>17168</v>
+      </c>
+      <c r="N961" s="1">
+        <v>17168</v>
+      </c>
+      <c r="O961">
+        <v>24</v>
+      </c>
+      <c r="P961">
+        <v>9</v>
+      </c>
+      <c r="Q961">
+        <v>1</v>
+      </c>
+      <c r="R961">
+        <v>4</v>
+      </c>
+      <c r="S961" t="s">
+        <v>85</v>
+      </c>
+      <c r="T961" t="s">
+        <v>24</v>
+      </c>
+      <c r="U961">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="962" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A962" t="s">
+        <v>579</v>
+      </c>
+      <c r="B962" t="s">
+        <v>349</v>
+      </c>
+      <c r="C962">
+        <v>1</v>
+      </c>
+      <c r="D962">
+        <v>1</v>
+      </c>
+      <c r="E962">
+        <v>4</v>
+      </c>
+      <c r="F962">
+        <v>0</v>
+      </c>
+      <c r="G962">
+        <v>38</v>
+      </c>
+      <c r="H962">
+        <v>3</v>
+      </c>
+      <c r="I962">
+        <v>12.67</v>
+      </c>
+      <c r="J962">
+        <v>9.5</v>
+      </c>
+      <c r="K962">
+        <v>0</v>
+      </c>
+      <c r="L962">
+        <v>0</v>
+      </c>
+      <c r="M962" s="1">
+        <v>13940</v>
+      </c>
+      <c r="N962" s="1">
+        <v>13940</v>
+      </c>
+      <c r="O962">
+        <v>24</v>
+      </c>
+      <c r="P962">
+        <v>12</v>
+      </c>
+      <c r="Q962">
+        <v>4</v>
+      </c>
+      <c r="R962">
+        <v>1</v>
+      </c>
+      <c r="S962" t="s">
+        <v>23</v>
+      </c>
+      <c r="T962" t="s">
+        <v>31</v>
+      </c>
+      <c r="U962">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="963" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A963" t="s">
+        <v>579</v>
+      </c>
+      <c r="B963" t="s">
+        <v>204</v>
+      </c>
+      <c r="C963">
+        <v>1</v>
+      </c>
+      <c r="D963">
+        <v>1</v>
+      </c>
+      <c r="E963">
+        <v>3.2</v>
+      </c>
+      <c r="F963">
+        <v>0</v>
+      </c>
+      <c r="G963">
+        <v>25</v>
+      </c>
+      <c r="H963">
+        <v>2</v>
+      </c>
+      <c r="I963">
+        <v>12.5</v>
+      </c>
+      <c r="J963">
+        <v>7.5</v>
+      </c>
+      <c r="K963">
+        <v>0</v>
+      </c>
+      <c r="L963">
+        <v>0</v>
+      </c>
+      <c r="M963" s="1">
+        <v>45689</v>
+      </c>
+      <c r="N963" s="1">
+        <v>45689</v>
+      </c>
+      <c r="O963">
+        <v>20</v>
+      </c>
+      <c r="P963">
+        <v>9</v>
+      </c>
+      <c r="Q963">
+        <v>3</v>
+      </c>
+      <c r="R963">
+        <v>0</v>
+      </c>
+      <c r="S963" t="s">
+        <v>31</v>
+      </c>
+      <c r="T963" t="s">
+        <v>24</v>
+      </c>
+      <c r="U963">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="964" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A964" t="s">
+        <v>579</v>
+      </c>
+      <c r="B964" t="s">
+        <v>580</v>
+      </c>
+      <c r="C964">
+        <v>1</v>
+      </c>
+      <c r="D964">
+        <v>1</v>
+      </c>
+      <c r="E964">
+        <v>3</v>
+      </c>
+      <c r="F964">
+        <v>0</v>
+      </c>
+      <c r="G964">
+        <v>28</v>
+      </c>
+      <c r="H964">
+        <v>1</v>
+      </c>
+      <c r="I964">
+        <v>28</v>
+      </c>
+      <c r="J964">
+        <v>9.33</v>
+      </c>
+      <c r="K964">
+        <v>0</v>
+      </c>
+      <c r="L964">
+        <v>0</v>
+      </c>
+      <c r="M964" s="1">
+        <v>46753</v>
+      </c>
+      <c r="N964" s="1">
+        <v>46753</v>
+      </c>
+      <c r="O964">
+        <v>18</v>
+      </c>
+      <c r="P964">
+        <v>7</v>
+      </c>
+      <c r="Q964">
+        <v>3</v>
+      </c>
+      <c r="R964">
+        <v>0</v>
+      </c>
+      <c r="S964" t="s">
+        <v>40</v>
+      </c>
+      <c r="T964" t="s">
+        <v>24</v>
+      </c>
+      <c r="U964">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="965" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A965" t="s">
+        <v>579</v>
+      </c>
+      <c r="B965" t="s">
+        <v>302</v>
+      </c>
+      <c r="C965">
+        <v>1</v>
+      </c>
+      <c r="D965">
+        <v>1</v>
+      </c>
+      <c r="E965">
+        <v>4</v>
+      </c>
+      <c r="F965">
+        <v>0</v>
+      </c>
+      <c r="G965">
+        <v>32</v>
+      </c>
+      <c r="H965">
+        <v>2</v>
+      </c>
+      <c r="I965">
+        <v>16</v>
+      </c>
+      <c r="J965">
+        <v>8</v>
+      </c>
+      <c r="K965">
+        <v>0</v>
+      </c>
+      <c r="L965">
+        <v>0</v>
+      </c>
+      <c r="M965" s="1">
+        <v>11720</v>
+      </c>
+      <c r="N965" s="1">
+        <v>11720</v>
+      </c>
+      <c r="O965">
+        <v>24</v>
+      </c>
+      <c r="P965">
+        <v>10</v>
+      </c>
+      <c r="Q965">
+        <v>5</v>
+      </c>
+      <c r="R965">
+        <v>0</v>
+      </c>
+      <c r="S965" t="s">
+        <v>38</v>
+      </c>
+      <c r="T965" t="s">
+        <v>24</v>
+      </c>
+      <c r="U965">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="966" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A966" t="s">
+        <v>579</v>
+      </c>
+      <c r="B966" t="s">
+        <v>475</v>
+      </c>
+      <c r="C966">
+        <v>1</v>
+      </c>
+      <c r="D966">
+        <v>1</v>
+      </c>
+      <c r="E966">
+        <v>4</v>
+      </c>
+      <c r="F966">
+        <v>0</v>
+      </c>
+      <c r="G966">
+        <v>30</v>
+      </c>
+      <c r="H966">
+        <v>0</v>
+      </c>
+      <c r="J966">
+        <v>7.5</v>
+      </c>
+      <c r="K966">
+        <v>0</v>
+      </c>
+      <c r="L966">
+        <v>0</v>
+      </c>
+      <c r="M966" t="s">
+        <v>177</v>
+      </c>
+      <c r="N966" t="s">
+        <v>177</v>
+      </c>
+      <c r="O966">
+        <v>24</v>
+      </c>
+      <c r="P966">
+        <v>9</v>
+      </c>
+      <c r="Q966">
+        <v>4</v>
+      </c>
+      <c r="R966">
+        <v>0</v>
+      </c>
+      <c r="S966" t="s">
+        <v>40</v>
+      </c>
+      <c r="T966" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="967" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A967" t="s">
+        <v>579</v>
+      </c>
+      <c r="B967" t="s">
+        <v>208</v>
+      </c>
+      <c r="C967">
+        <v>1</v>
+      </c>
+      <c r="D967">
+        <v>1</v>
+      </c>
+      <c r="E967">
+        <v>4</v>
+      </c>
+      <c r="F967">
+        <v>0</v>
+      </c>
+      <c r="G967">
+        <v>25</v>
+      </c>
+      <c r="H967">
+        <v>3</v>
+      </c>
+      <c r="I967">
+        <v>8.33</v>
+      </c>
+      <c r="J967">
+        <v>6.25</v>
+      </c>
+      <c r="K967">
+        <v>0</v>
+      </c>
+      <c r="L967">
+        <v>0</v>
+      </c>
+      <c r="M967" s="1">
+        <v>45717</v>
+      </c>
+      <c r="N967" s="1">
+        <v>45717</v>
+      </c>
+      <c r="O967">
+        <v>24</v>
+      </c>
+      <c r="P967">
+        <v>12</v>
+      </c>
+      <c r="Q967">
+        <v>4</v>
+      </c>
+      <c r="R967">
+        <v>0</v>
+      </c>
+      <c r="S967" t="s">
+        <v>31</v>
+      </c>
+      <c r="T967" t="s">
+        <v>24</v>
+      </c>
+      <c r="U967">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="968" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A968" t="s">
+        <v>579</v>
+      </c>
+      <c r="B968" t="s">
+        <v>212</v>
+      </c>
+      <c r="C968">
+        <v>1</v>
+      </c>
+      <c r="D968">
+        <v>1</v>
+      </c>
+      <c r="E968">
+        <v>4</v>
+      </c>
+      <c r="F968">
+        <v>0</v>
+      </c>
+      <c r="G968">
+        <v>27</v>
+      </c>
+      <c r="H968">
+        <v>1</v>
+      </c>
+      <c r="I968">
+        <v>27</v>
+      </c>
+      <c r="J968">
+        <v>6.75</v>
+      </c>
+      <c r="K968">
+        <v>0</v>
+      </c>
+      <c r="L968">
+        <v>0</v>
+      </c>
+      <c r="M968" s="1">
+        <v>46388</v>
+      </c>
+      <c r="N968" s="1">
+        <v>46388</v>
+      </c>
+      <c r="O968">
+        <v>24</v>
+      </c>
+      <c r="P968">
+        <v>11</v>
+      </c>
+      <c r="Q968">
+        <v>3</v>
+      </c>
+      <c r="R968">
+        <v>0</v>
+      </c>
+      <c r="S968" t="s">
+        <v>109</v>
+      </c>
+      <c r="T968" t="s">
+        <v>24</v>
+      </c>
+      <c r="U968">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="969" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A969" t="s">
+        <v>579</v>
+      </c>
+      <c r="B969" t="s">
+        <v>351</v>
+      </c>
+      <c r="C969">
+        <v>1</v>
+      </c>
+      <c r="D969">
+        <v>1</v>
+      </c>
+      <c r="E969">
+        <v>1</v>
+      </c>
+      <c r="F969">
+        <v>0</v>
+      </c>
+      <c r="G969">
+        <v>9</v>
+      </c>
+      <c r="H969">
+        <v>0</v>
+      </c>
+      <c r="J969">
+        <v>9</v>
+      </c>
+      <c r="K969">
+        <v>0</v>
+      </c>
+      <c r="L969">
+        <v>0</v>
+      </c>
+      <c r="M969" t="s">
+        <v>58</v>
+      </c>
+      <c r="N969" t="s">
+        <v>58</v>
+      </c>
+      <c r="O969">
+        <v>6</v>
+      </c>
+      <c r="P969">
+        <v>2</v>
+      </c>
+      <c r="Q969">
+        <v>0</v>
+      </c>
+      <c r="R969">
+        <v>1</v>
+      </c>
+      <c r="S969" t="s">
+        <v>24</v>
+      </c>
+      <c r="T969" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="970" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A970" t="s">
+        <v>579</v>
+      </c>
+      <c r="B970" t="s">
+        <v>215</v>
+      </c>
+      <c r="C970">
+        <v>1</v>
+      </c>
+      <c r="D970">
+        <v>1</v>
+      </c>
+      <c r="E970">
+        <v>4</v>
+      </c>
+      <c r="F970">
+        <v>0</v>
+      </c>
+      <c r="G970">
+        <v>17</v>
+      </c>
+      <c r="H970">
+        <v>1</v>
+      </c>
+      <c r="I970">
+        <v>17</v>
+      </c>
+      <c r="J970">
+        <v>4.25</v>
+      </c>
+      <c r="K970">
+        <v>0</v>
+      </c>
+      <c r="L970">
+        <v>0</v>
+      </c>
+      <c r="M970" s="1">
+        <v>42736</v>
+      </c>
+      <c r="N970" s="1">
+        <v>42736</v>
+      </c>
+      <c r="O970">
+        <v>24</v>
+      </c>
+      <c r="P970">
+        <v>13</v>
+      </c>
+      <c r="Q970">
+        <v>1</v>
+      </c>
+      <c r="R970">
+        <v>0</v>
+      </c>
+      <c r="S970" t="s">
+        <v>24</v>
+      </c>
+      <c r="T970" t="s">
+        <v>24</v>
+      </c>
+      <c r="U970">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="971" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A971" t="s">
+        <v>581</v>
+      </c>
+      <c r="B971" t="s">
+        <v>422</v>
+      </c>
+      <c r="C971">
+        <v>1</v>
+      </c>
+      <c r="D971">
+        <v>1</v>
+      </c>
+      <c r="E971">
+        <v>4</v>
+      </c>
+      <c r="F971">
+        <v>0</v>
+      </c>
+      <c r="G971">
+        <v>38</v>
+      </c>
+      <c r="H971">
+        <v>2</v>
+      </c>
+      <c r="I971">
+        <v>19</v>
+      </c>
+      <c r="J971">
+        <v>9.5</v>
+      </c>
+      <c r="K971">
+        <v>0</v>
+      </c>
+      <c r="L971">
+        <v>0</v>
+      </c>
+      <c r="M971" s="1">
+        <v>13912</v>
+      </c>
+      <c r="N971" s="1">
+        <v>13912</v>
+      </c>
+      <c r="O971">
+        <v>24</v>
+      </c>
+      <c r="P971">
+        <v>15</v>
+      </c>
+      <c r="Q971">
+        <v>4</v>
+      </c>
+      <c r="R971">
+        <v>2</v>
+      </c>
+      <c r="S971" t="s">
+        <v>85</v>
+      </c>
+      <c r="T971" t="s">
+        <v>24</v>
+      </c>
+      <c r="U971">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="972" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A972" t="s">
+        <v>581</v>
+      </c>
+      <c r="B972" t="s">
+        <v>114</v>
+      </c>
+      <c r="C972">
+        <v>1</v>
+      </c>
+      <c r="D972">
+        <v>1</v>
+      </c>
+      <c r="E972">
+        <v>4</v>
+      </c>
+      <c r="F972">
+        <v>0</v>
+      </c>
+      <c r="G972">
+        <v>26</v>
+      </c>
+      <c r="H972">
+        <v>1</v>
+      </c>
+      <c r="I972">
+        <v>26</v>
+      </c>
+      <c r="J972">
+        <v>6.5</v>
+      </c>
+      <c r="K972">
+        <v>0</v>
+      </c>
+      <c r="L972">
+        <v>0</v>
+      </c>
+      <c r="M972" s="1">
+        <v>46023</v>
+      </c>
+      <c r="N972" s="1">
+        <v>46023</v>
+      </c>
+      <c r="O972">
+        <v>24</v>
+      </c>
+      <c r="P972">
+        <v>13</v>
+      </c>
+      <c r="Q972">
+        <v>2</v>
+      </c>
+      <c r="R972">
+        <v>1</v>
+      </c>
+      <c r="S972" t="s">
+        <v>107</v>
+      </c>
+      <c r="T972" t="s">
+        <v>24</v>
+      </c>
+      <c r="U972">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="973" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A973" t="s">
+        <v>581</v>
+      </c>
+      <c r="B973" t="s">
+        <v>223</v>
+      </c>
+      <c r="C973">
+        <v>1</v>
+      </c>
+      <c r="D973">
+        <v>1</v>
+      </c>
+      <c r="E973">
+        <v>1.2</v>
+      </c>
+      <c r="F973">
+        <v>0</v>
+      </c>
+      <c r="G973">
+        <v>8</v>
+      </c>
+      <c r="H973">
+        <v>1</v>
+      </c>
+      <c r="I973">
+        <v>8</v>
+      </c>
+      <c r="J973">
+        <v>6</v>
+      </c>
+      <c r="K973">
+        <v>0</v>
+      </c>
+      <c r="L973">
+        <v>0</v>
+      </c>
+      <c r="M973" s="2">
+        <v>46235</v>
+      </c>
+      <c r="N973" s="2">
+        <v>46235</v>
+      </c>
+      <c r="O973">
+        <v>8</v>
+      </c>
+      <c r="P973">
+        <v>7</v>
+      </c>
+      <c r="Q973">
+        <v>0</v>
+      </c>
+      <c r="R973">
+        <v>1</v>
+      </c>
+      <c r="S973" t="s">
+        <v>29</v>
+      </c>
+      <c r="T973" t="s">
+        <v>24</v>
+      </c>
+      <c r="U973">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="974" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A974" t="s">
+        <v>581</v>
+      </c>
+      <c r="B974" t="s">
+        <v>582</v>
+      </c>
+      <c r="C974">
+        <v>1</v>
+      </c>
+      <c r="D974">
+        <v>1</v>
+      </c>
+      <c r="E974">
+        <v>4</v>
+      </c>
+      <c r="F974">
+        <v>0</v>
+      </c>
+      <c r="G974">
+        <v>19</v>
+      </c>
+      <c r="H974">
+        <v>1</v>
+      </c>
+      <c r="I974">
+        <v>19</v>
+      </c>
+      <c r="J974">
+        <v>4.75</v>
+      </c>
+      <c r="K974">
+        <v>0</v>
+      </c>
+      <c r="L974">
+        <v>0</v>
+      </c>
+      <c r="M974" s="1">
+        <v>43466</v>
+      </c>
+      <c r="N974" s="1">
+        <v>43466</v>
+      </c>
+      <c r="O974">
+        <v>24</v>
+      </c>
+      <c r="P974">
+        <v>14</v>
+      </c>
+      <c r="Q974">
+        <v>0</v>
+      </c>
+      <c r="R974">
+        <v>1</v>
+      </c>
+      <c r="S974" t="s">
+        <v>31</v>
+      </c>
+      <c r="T974" t="s">
+        <v>31</v>
+      </c>
+      <c r="U974">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="975" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A975" t="s">
+        <v>581</v>
+      </c>
+      <c r="B975" t="s">
+        <v>271</v>
+      </c>
+      <c r="C975">
+        <v>1</v>
+      </c>
+      <c r="D975">
+        <v>1</v>
+      </c>
+      <c r="E975">
+        <v>2</v>
+      </c>
+      <c r="F975">
+        <v>0</v>
+      </c>
+      <c r="G975">
+        <v>5</v>
+      </c>
+      <c r="H975">
+        <v>0</v>
+      </c>
+      <c r="J975">
+        <v>2.5</v>
+      </c>
+      <c r="K975">
+        <v>0</v>
+      </c>
+      <c r="L975">
+        <v>0</v>
+      </c>
+      <c r="M975" t="s">
+        <v>254</v>
+      </c>
+      <c r="N975" t="s">
+        <v>254</v>
+      </c>
+      <c r="O975">
+        <v>12</v>
+      </c>
+      <c r="P975">
+        <v>9</v>
+      </c>
+      <c r="Q975">
+        <v>0</v>
+      </c>
+      <c r="R975">
+        <v>0</v>
+      </c>
+      <c r="S975" t="s">
+        <v>24</v>
+      </c>
+      <c r="T975" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="976" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A976" t="s">
+        <v>581</v>
+      </c>
+      <c r="B976" t="s">
+        <v>341</v>
+      </c>
+      <c r="C976">
+        <v>1</v>
+      </c>
+      <c r="D976">
+        <v>1</v>
+      </c>
+      <c r="E976">
+        <v>1</v>
+      </c>
+      <c r="F976">
+        <v>0</v>
+      </c>
+      <c r="G976">
+        <v>13</v>
+      </c>
+      <c r="H976">
+        <v>0</v>
+      </c>
+      <c r="J976">
+        <v>13</v>
+      </c>
+      <c r="K976">
+        <v>0</v>
+      </c>
+      <c r="L976">
+        <v>0</v>
+      </c>
+      <c r="M976" t="s">
+        <v>50</v>
+      </c>
+      <c r="N976" t="s">
+        <v>50</v>
+      </c>
+      <c r="O976">
+        <v>6</v>
+      </c>
+      <c r="P976">
+        <v>3</v>
+      </c>
+      <c r="Q976">
+        <v>1</v>
+      </c>
+      <c r="R976">
+        <v>0</v>
+      </c>
+      <c r="S976" t="s">
+        <v>61</v>
+      </c>
+      <c r="T976" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="977" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A977" t="s">
+        <v>581</v>
+      </c>
+      <c r="B977" t="s">
+        <v>338</v>
+      </c>
+      <c r="C977">
+        <v>1</v>
+      </c>
+      <c r="D977">
+        <v>1</v>
+      </c>
+      <c r="E977">
+        <v>3</v>
+      </c>
+      <c r="F977">
+        <v>0</v>
+      </c>
+      <c r="G977">
+        <v>28</v>
+      </c>
+      <c r="H977">
+        <v>0</v>
+      </c>
+      <c r="J977">
+        <v>9.33</v>
+      </c>
+      <c r="K977">
+        <v>0</v>
+      </c>
+      <c r="L977">
+        <v>0</v>
+      </c>
+      <c r="M977" t="s">
+        <v>100</v>
+      </c>
+      <c r="N977" t="s">
+        <v>100</v>
+      </c>
+      <c r="O977">
+        <v>18</v>
+      </c>
+      <c r="P977">
+        <v>8</v>
+      </c>
+      <c r="Q977">
+        <v>3</v>
+      </c>
+      <c r="R977">
+        <v>0</v>
+      </c>
+      <c r="S977" t="s">
+        <v>308</v>
+      </c>
+      <c r="T977" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="978" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A978" t="s">
+        <v>581</v>
+      </c>
+      <c r="B978" t="s">
+        <v>121</v>
+      </c>
+      <c r="C978">
+        <v>1</v>
+      </c>
+      <c r="D978">
+        <v>1</v>
+      </c>
+      <c r="E978">
+        <v>2</v>
+      </c>
+      <c r="F978">
+        <v>0</v>
+      </c>
+      <c r="G978">
+        <v>7</v>
+      </c>
+      <c r="H978">
+        <v>1</v>
+      </c>
+      <c r="I978">
+        <v>7</v>
+      </c>
+      <c r="J978">
+        <v>3.5</v>
+      </c>
+      <c r="K978">
+        <v>0</v>
+      </c>
+      <c r="L978">
+        <v>0</v>
+      </c>
+      <c r="M978" s="2">
+        <v>46204</v>
+      </c>
+      <c r="N978" s="2">
+        <v>46204</v>
+      </c>
+      <c r="O978">
+        <v>12</v>
+      </c>
+      <c r="P978">
+        <v>8</v>
+      </c>
+      <c r="Q978">
+        <v>0</v>
+      </c>
+      <c r="R978">
+        <v>0</v>
+      </c>
+      <c r="S978" t="s">
+        <v>40</v>
+      </c>
+      <c r="T978" t="s">
+        <v>24</v>
+      </c>
+      <c r="U978">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="979" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A979" t="s">
+        <v>581</v>
+      </c>
+      <c r="B979" t="s">
+        <v>225</v>
+      </c>
+      <c r="C979">
+        <v>1</v>
+      </c>
+      <c r="D979">
+        <v>1</v>
+      </c>
+      <c r="E979">
+        <v>4</v>
+      </c>
+      <c r="F979">
+        <v>0</v>
+      </c>
+      <c r="G979">
+        <v>22</v>
+      </c>
+      <c r="H979">
+        <v>3</v>
+      </c>
+      <c r="I979">
+        <v>7.33</v>
+      </c>
+      <c r="J979">
+        <v>5.5</v>
+      </c>
+      <c r="K979">
+        <v>0</v>
+      </c>
+      <c r="L979">
+        <v>0</v>
+      </c>
+      <c r="M979" s="1">
+        <v>44621</v>
+      </c>
+      <c r="N979" s="1">
+        <v>44621</v>
+      </c>
+      <c r="O979">
+        <v>24</v>
+      </c>
+      <c r="P979">
+        <v>16</v>
+      </c>
+      <c r="Q979">
+        <v>4</v>
+      </c>
+      <c r="R979">
+        <v>0</v>
+      </c>
+      <c r="S979" t="s">
+        <v>29</v>
+      </c>
+      <c r="T979" t="s">
+        <v>24</v>
+      </c>
+      <c r="U979">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="980" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A980" t="s">
+        <v>581</v>
+      </c>
+      <c r="B980" t="s">
+        <v>122</v>
+      </c>
+      <c r="C980">
+        <v>1</v>
+      </c>
+      <c r="D980">
+        <v>1</v>
+      </c>
+      <c r="E980">
+        <v>3</v>
+      </c>
+      <c r="F980">
+        <v>0</v>
+      </c>
+      <c r="G980">
+        <v>21</v>
+      </c>
+      <c r="H980">
+        <v>1</v>
+      </c>
+      <c r="I980">
+        <v>21</v>
+      </c>
+      <c r="J980">
+        <v>7</v>
+      </c>
+      <c r="K980">
+        <v>0</v>
+      </c>
+      <c r="L980">
+        <v>0</v>
+      </c>
+      <c r="M980" s="1">
+        <v>44197</v>
+      </c>
+      <c r="N980" s="1">
+        <v>44197</v>
+      </c>
+      <c r="O980">
+        <v>18</v>
+      </c>
+      <c r="P980">
+        <v>9</v>
+      </c>
+      <c r="Q980">
+        <v>1</v>
+      </c>
+      <c r="R980">
+        <v>0</v>
+      </c>
+      <c r="S980" t="s">
+        <v>123</v>
+      </c>
+      <c r="T980" t="s">
+        <v>24</v>
+      </c>
+      <c r="U980">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="981" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A981" t="s">
+        <v>581</v>
+      </c>
+      <c r="B981" t="s">
+        <v>124</v>
+      </c>
+      <c r="C981">
+        <v>1</v>
+      </c>
+      <c r="D981">
+        <v>1</v>
+      </c>
+      <c r="E981">
+        <v>4</v>
+      </c>
+      <c r="F981">
+        <v>0</v>
+      </c>
+      <c r="G981">
+        <v>21</v>
+      </c>
+      <c r="H981">
+        <v>4</v>
+      </c>
+      <c r="I981">
+        <v>5.25</v>
+      </c>
+      <c r="J981">
+        <v>5.25</v>
+      </c>
+      <c r="K981">
+        <v>0</v>
+      </c>
+      <c r="L981">
+        <v>0</v>
+      </c>
+      <c r="M981" s="1">
+        <v>44287</v>
+      </c>
+      <c r="N981" s="1">
+        <v>44287</v>
+      </c>
+      <c r="O981">
+        <v>24</v>
+      </c>
+      <c r="P981">
+        <v>16</v>
+      </c>
+      <c r="Q981">
+        <v>2</v>
+      </c>
+      <c r="R981">
+        <v>0</v>
+      </c>
+      <c r="S981" t="s">
+        <v>40</v>
+      </c>
+      <c r="T981" t="s">
+        <v>42</v>
+      </c>
+      <c r="U981">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="982" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A982" t="s">
+        <v>581</v>
+      </c>
+      <c r="B982" t="s">
+        <v>59</v>
+      </c>
+      <c r="C982">
+        <v>1</v>
+      </c>
+      <c r="D982">
+        <v>1</v>
+      </c>
+      <c r="E982">
+        <v>2</v>
+      </c>
+      <c r="F982">
+        <v>0</v>
+      </c>
+      <c r="G982">
+        <v>10</v>
+      </c>
+      <c r="H982">
+        <v>0</v>
+      </c>
+      <c r="J982">
+        <v>5</v>
+      </c>
+      <c r="K982">
+        <v>0</v>
+      </c>
+      <c r="L982">
+        <v>0</v>
+      </c>
+      <c r="M982" t="s">
+        <v>48</v>
+      </c>
+      <c r="N982" t="s">
+        <v>48</v>
+      </c>
+      <c r="O982">
+        <v>12</v>
+      </c>
+      <c r="P982">
+        <v>6</v>
+      </c>
+      <c r="Q982">
+        <v>1</v>
+      </c>
+      <c r="R982">
+        <v>0</v>
+      </c>
+      <c r="S982" t="s">
+        <v>24</v>
+      </c>
+      <c r="T982" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="983" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A983" t="s">
+        <v>581</v>
+      </c>
+      <c r="B983" t="s">
+        <v>551</v>
+      </c>
+      <c r="C983">
+        <v>1</v>
+      </c>
+      <c r="D983">
+        <v>1</v>
+      </c>
+      <c r="E983">
+        <v>2</v>
+      </c>
+      <c r="F983">
+        <v>1</v>
+      </c>
+      <c r="G983">
+        <v>9</v>
+      </c>
+      <c r="H983">
+        <v>1</v>
+      </c>
+      <c r="I983">
+        <v>9</v>
+      </c>
+      <c r="J983">
+        <v>4.5</v>
+      </c>
+      <c r="K983">
+        <v>0</v>
+      </c>
+      <c r="L983">
+        <v>0</v>
+      </c>
+      <c r="M983" s="2">
+        <v>46266</v>
+      </c>
+      <c r="N983" s="2">
+        <v>46266</v>
+      </c>
+      <c r="O983">
+        <v>12</v>
+      </c>
+      <c r="P983">
+        <v>7</v>
+      </c>
+      <c r="Q983">
+        <v>1</v>
+      </c>
+      <c r="R983">
+        <v>0</v>
+      </c>
+      <c r="S983" t="s">
+        <v>31</v>
+      </c>
+      <c r="T983" t="s">
+        <v>24</v>
+      </c>
+      <c r="U983">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="984" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A984" t="s">
+        <v>583</v>
+      </c>
+      <c r="B984" t="s">
+        <v>498</v>
+      </c>
+      <c r="C984">
+        <v>1</v>
+      </c>
+      <c r="D984">
+        <v>1</v>
+      </c>
+      <c r="E984">
+        <v>1</v>
+      </c>
+      <c r="F984">
+        <v>0</v>
+      </c>
+      <c r="G984">
+        <v>6</v>
+      </c>
+      <c r="H984">
+        <v>0</v>
+      </c>
+      <c r="J984">
+        <v>6</v>
+      </c>
+      <c r="K984">
+        <v>0</v>
+      </c>
+      <c r="L984">
+        <v>0</v>
+      </c>
+      <c r="M984" t="s">
+        <v>192</v>
+      </c>
+      <c r="N984" t="s">
+        <v>192</v>
+      </c>
+      <c r="O984">
+        <v>6</v>
+      </c>
+      <c r="P984">
+        <v>3</v>
+      </c>
+      <c r="Q984">
+        <v>0</v>
+      </c>
+      <c r="R984">
+        <v>0</v>
+      </c>
+      <c r="S984" t="s">
+        <v>29</v>
+      </c>
+      <c r="T984" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="985" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A985" t="s">
+        <v>583</v>
+      </c>
+      <c r="B985" t="s">
+        <v>103</v>
+      </c>
+      <c r="C985">
+        <v>1</v>
+      </c>
+      <c r="D985">
+        <v>1</v>
+      </c>
+      <c r="E985">
+        <v>3</v>
+      </c>
+      <c r="F985">
+        <v>0</v>
+      </c>
+      <c r="G985">
+        <v>26</v>
+      </c>
+      <c r="H985">
+        <v>0</v>
+      </c>
+      <c r="J985">
+        <v>8.67</v>
+      </c>
+      <c r="K985">
+        <v>0</v>
+      </c>
+      <c r="L985">
+        <v>0</v>
+      </c>
+      <c r="M985" t="s">
+        <v>90</v>
+      </c>
+      <c r="N985" t="s">
+        <v>90</v>
+      </c>
+      <c r="O985">
+        <v>18</v>
+      </c>
+      <c r="P985">
+        <v>6</v>
+      </c>
+      <c r="Q985">
+        <v>3</v>
+      </c>
+      <c r="R985">
+        <v>0</v>
+      </c>
+      <c r="S985" t="s">
+        <v>109</v>
+      </c>
+      <c r="T985" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="986" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A986" t="s">
+        <v>583</v>
+      </c>
+      <c r="B986" t="s">
+        <v>180</v>
+      </c>
+      <c r="C986">
+        <v>1</v>
+      </c>
+      <c r="D986">
+        <v>1</v>
+      </c>
+      <c r="E986">
+        <v>4</v>
+      </c>
+      <c r="F986">
+        <v>0</v>
+      </c>
+      <c r="G986">
+        <v>28</v>
+      </c>
+      <c r="H986">
+        <v>3</v>
+      </c>
+      <c r="I986">
+        <v>9.33</v>
+      </c>
+      <c r="J986">
+        <v>7</v>
+      </c>
+      <c r="K986">
+        <v>0</v>
+      </c>
+      <c r="L986">
+        <v>0</v>
+      </c>
+      <c r="M986" s="1">
+        <v>46813</v>
+      </c>
+      <c r="N986" s="1">
+        <v>46813</v>
+      </c>
+      <c r="O986">
+        <v>24</v>
+      </c>
+      <c r="P986">
+        <v>12</v>
+      </c>
+      <c r="Q986">
+        <v>5</v>
+      </c>
+      <c r="R986">
+        <v>0</v>
+      </c>
+      <c r="S986" t="s">
+        <v>31</v>
+      </c>
+      <c r="T986" t="s">
+        <v>24</v>
+      </c>
+      <c r="U986">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="987" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A987" t="s">
+        <v>583</v>
+      </c>
+      <c r="B987" t="s">
+        <v>584</v>
+      </c>
+      <c r="C987">
+        <v>1</v>
+      </c>
+      <c r="D987">
+        <v>1</v>
+      </c>
+      <c r="E987">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F987">
+        <v>0</v>
+      </c>
+      <c r="G987">
+        <v>11</v>
+      </c>
+      <c r="H987">
+        <v>4</v>
+      </c>
+      <c r="I987">
+        <v>2.75</v>
+      </c>
+      <c r="J987">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="K987">
+        <v>0</v>
+      </c>
+      <c r="L987">
+        <v>0</v>
+      </c>
+      <c r="M987" s="2">
+        <v>46330</v>
+      </c>
+      <c r="N987" s="2">
+        <v>46330</v>
+      </c>
+      <c r="O987">
+        <v>15</v>
+      </c>
+      <c r="P987">
+        <v>9</v>
+      </c>
+      <c r="Q987">
+        <v>1</v>
+      </c>
+      <c r="R987">
+        <v>0</v>
+      </c>
+      <c r="S987" t="s">
+        <v>24</v>
+      </c>
+      <c r="T987" t="s">
+        <v>24</v>
+      </c>
+      <c r="U987">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="988" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A988" t="s">
+        <v>583</v>
+      </c>
+      <c r="B988" t="s">
+        <v>184</v>
+      </c>
+      <c r="C988">
+        <v>1</v>
+      </c>
+      <c r="D988">
+        <v>1</v>
+      </c>
+      <c r="E988">
+        <v>4</v>
+      </c>
+      <c r="F988">
+        <v>0</v>
+      </c>
+      <c r="G988">
+        <v>29</v>
+      </c>
+      <c r="H988">
+        <v>1</v>
+      </c>
+      <c r="I988">
+        <v>29</v>
+      </c>
+      <c r="J988">
+        <v>7.25</v>
+      </c>
+      <c r="K988">
+        <v>0</v>
+      </c>
+      <c r="L988">
+        <v>0</v>
+      </c>
+      <c r="M988" s="1">
+        <v>47119</v>
+      </c>
+      <c r="N988" s="1">
+        <v>47119</v>
+      </c>
+      <c r="O988">
+        <v>24</v>
+      </c>
+      <c r="P988">
+        <v>15</v>
+      </c>
+      <c r="Q988">
+        <v>1</v>
+      </c>
+      <c r="R988">
+        <v>2</v>
+      </c>
+      <c r="S988" t="s">
+        <v>34</v>
+      </c>
+      <c r="T988" t="s">
+        <v>24</v>
+      </c>
+      <c r="U988">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="989" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A989" t="s">
+        <v>583</v>
+      </c>
+      <c r="B989" t="s">
+        <v>185</v>
+      </c>
+      <c r="C989">
+        <v>1</v>
+      </c>
+      <c r="D989">
+        <v>1</v>
+      </c>
+      <c r="E989">
+        <v>4</v>
+      </c>
+      <c r="F989">
+        <v>0</v>
+      </c>
+      <c r="G989">
+        <v>24</v>
+      </c>
+      <c r="H989">
+        <v>0</v>
+      </c>
+      <c r="J989">
+        <v>6</v>
+      </c>
+      <c r="K989">
+        <v>0</v>
+      </c>
+      <c r="L989">
+        <v>0</v>
+      </c>
+      <c r="M989" t="s">
+        <v>162</v>
+      </c>
+      <c r="N989" t="s">
+        <v>162</v>
+      </c>
+      <c r="O989">
+        <v>24</v>
+      </c>
+      <c r="P989">
+        <v>14</v>
+      </c>
+      <c r="Q989">
+        <v>4</v>
+      </c>
+      <c r="R989">
+        <v>0</v>
+      </c>
+      <c r="S989" t="s">
+        <v>31</v>
+      </c>
+      <c r="T989" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="990" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A990" t="s">
+        <v>583</v>
+      </c>
+      <c r="B990" t="s">
+        <v>434</v>
+      </c>
+      <c r="C990">
+        <v>1</v>
+      </c>
+      <c r="D990">
+        <v>1</v>
+      </c>
+      <c r="E990">
+        <v>4</v>
+      </c>
+      <c r="F990">
+        <v>0</v>
+      </c>
+      <c r="G990">
+        <v>28</v>
+      </c>
+      <c r="H990">
+        <v>0</v>
+      </c>
+      <c r="J990">
+        <v>7</v>
+      </c>
+      <c r="K990">
+        <v>0</v>
+      </c>
+      <c r="L990">
+        <v>0</v>
+      </c>
+      <c r="M990" t="s">
+        <v>100</v>
+      </c>
+      <c r="N990" t="s">
+        <v>100</v>
+      </c>
+      <c r="O990">
+        <v>24</v>
+      </c>
+      <c r="P990">
+        <v>9</v>
+      </c>
+      <c r="Q990">
+        <v>3</v>
+      </c>
+      <c r="R990">
+        <v>0</v>
+      </c>
+      <c r="S990" t="s">
+        <v>40</v>
+      </c>
+      <c r="T990" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="991" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A991" t="s">
+        <v>583</v>
+      </c>
+      <c r="B991" t="s">
+        <v>546</v>
+      </c>
+      <c r="C991">
+        <v>1</v>
+      </c>
+      <c r="D991">
+        <v>1</v>
+      </c>
+      <c r="E991">
+        <v>1.2</v>
+      </c>
+      <c r="F991">
+        <v>0</v>
+      </c>
+      <c r="G991">
+        <v>5</v>
+      </c>
+      <c r="H991">
+        <v>0</v>
+      </c>
+      <c r="J991">
+        <v>3.75</v>
+      </c>
+      <c r="K991">
+        <v>0</v>
+      </c>
+      <c r="L991">
+        <v>0</v>
+      </c>
+      <c r="M991" t="s">
+        <v>254</v>
+      </c>
+      <c r="N991" t="s">
+        <v>254</v>
+      </c>
+      <c r="O991">
+        <v>8</v>
+      </c>
+      <c r="P991">
+        <v>6</v>
+      </c>
+      <c r="Q991">
+        <v>0</v>
+      </c>
+      <c r="R991">
+        <v>0</v>
+      </c>
+      <c r="S991" t="s">
+        <v>38</v>
+      </c>
+      <c r="T991" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="992" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A992" t="s">
+        <v>583</v>
+      </c>
+      <c r="B992" t="s">
+        <v>585</v>
+      </c>
+      <c r="C992">
+        <v>1</v>
+      </c>
+      <c r="D992">
+        <v>1</v>
+      </c>
+      <c r="E992">
+        <v>1</v>
+      </c>
+      <c r="F992">
+        <v>0</v>
+      </c>
+      <c r="G992">
+        <v>23</v>
+      </c>
+      <c r="H992">
+        <v>1</v>
+      </c>
+      <c r="I992">
+        <v>23</v>
+      </c>
+      <c r="J992">
+        <v>23</v>
+      </c>
+      <c r="K992">
+        <v>0</v>
+      </c>
+      <c r="L992">
+        <v>0</v>
+      </c>
+      <c r="M992" s="1">
+        <v>44927</v>
+      </c>
+      <c r="N992" s="1">
+        <v>44927</v>
+      </c>
+      <c r="O992">
+        <v>6</v>
+      </c>
+      <c r="P992">
+        <v>3</v>
+      </c>
+      <c r="Q992">
+        <v>1</v>
+      </c>
+      <c r="R992">
+        <v>1</v>
+      </c>
+      <c r="S992" t="s">
+        <v>586</v>
+      </c>
+      <c r="T992" t="s">
+        <v>24</v>
+      </c>
+      <c r="U992">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="993" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A993" t="s">
+        <v>583</v>
+      </c>
+      <c r="B993" t="s">
+        <v>549</v>
+      </c>
+      <c r="C993">
+        <v>1</v>
+      </c>
+      <c r="D993">
+        <v>1</v>
+      </c>
+      <c r="E993">
+        <v>4</v>
+      </c>
+      <c r="F993">
+        <v>0</v>
+      </c>
+      <c r="G993">
+        <v>21</v>
+      </c>
+      <c r="H993">
+        <v>2</v>
+      </c>
+      <c r="I993">
+        <v>10.5</v>
+      </c>
+      <c r="J993">
+        <v>5.25</v>
+      </c>
+      <c r="K993">
+        <v>0</v>
+      </c>
+      <c r="L993">
+        <v>0</v>
+      </c>
+      <c r="M993" s="1">
+        <v>44228</v>
+      </c>
+      <c r="N993" s="1">
+        <v>44228</v>
+      </c>
+      <c r="O993">
+        <v>24</v>
+      </c>
+      <c r="P993">
+        <v>16</v>
+      </c>
+      <c r="Q993">
+        <v>0</v>
+      </c>
+      <c r="R993">
+        <v>0</v>
+      </c>
+      <c r="S993" t="s">
+        <v>155</v>
+      </c>
+      <c r="T993" t="s">
+        <v>24</v>
+      </c>
+      <c r="U993">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="994" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A994" t="s">
+        <v>583</v>
+      </c>
+      <c r="B994" t="s">
+        <v>461</v>
+      </c>
+      <c r="C994">
+        <v>1</v>
+      </c>
+      <c r="D994">
+        <v>1</v>
+      </c>
+      <c r="E994">
+        <v>2</v>
+      </c>
+      <c r="F994">
+        <v>0</v>
+      </c>
+      <c r="G994">
+        <v>23</v>
+      </c>
+      <c r="H994">
+        <v>1</v>
+      </c>
+      <c r="I994">
+        <v>23</v>
+      </c>
+      <c r="J994">
+        <v>11.5</v>
+      </c>
+      <c r="K994">
+        <v>0</v>
+      </c>
+      <c r="L994">
+        <v>0</v>
+      </c>
+      <c r="M994" s="1">
+        <v>44927</v>
+      </c>
+      <c r="N994" s="1">
+        <v>44927</v>
+      </c>
+      <c r="O994">
+        <v>12</v>
+      </c>
+      <c r="P994">
+        <v>7</v>
+      </c>
+      <c r="Q994">
+        <v>2</v>
+      </c>
+      <c r="R994">
+        <v>0</v>
+      </c>
+      <c r="S994" t="s">
+        <v>587</v>
+      </c>
+      <c r="T994" t="s">
+        <v>42</v>
+      </c>
+      <c r="U994">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="995" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A995" t="s">
+        <v>583</v>
+      </c>
+      <c r="B995" t="s">
+        <v>111</v>
+      </c>
+      <c r="C995">
+        <v>1</v>
+      </c>
+      <c r="D995">
+        <v>1</v>
+      </c>
+      <c r="E995">
+        <v>4</v>
+      </c>
+      <c r="F995">
+        <v>0</v>
+      </c>
+      <c r="G995">
+        <v>15</v>
+      </c>
+      <c r="H995">
+        <v>2</v>
+      </c>
+      <c r="I995">
+        <v>7.5</v>
+      </c>
+      <c r="J995">
+        <v>3.75</v>
+      </c>
+      <c r="K995">
+        <v>0</v>
+      </c>
+      <c r="L995">
+        <v>0</v>
+      </c>
+      <c r="M995" s="1">
+        <v>42036</v>
+      </c>
+      <c r="N995" s="1">
+        <v>42036</v>
+      </c>
+      <c r="O995">
+        <v>24</v>
+      </c>
+      <c r="P995">
+        <v>16</v>
+      </c>
+      <c r="Q995">
+        <v>1</v>
+      </c>
+      <c r="R995">
+        <v>0</v>
+      </c>
+      <c r="S995" t="s">
+        <v>31</v>
+      </c>
+      <c r="T995" t="s">
+        <v>24</v>
+      </c>
+      <c r="U995">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="996" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A996" t="s">
+        <v>588</v>
+      </c>
+      <c r="B996" t="s">
+        <v>538</v>
+      </c>
+      <c r="C996">
+        <v>1</v>
+      </c>
+      <c r="D996">
+        <v>1</v>
+      </c>
+      <c r="E996">
+        <v>1</v>
+      </c>
+      <c r="F996">
+        <v>0</v>
+      </c>
+      <c r="G996">
+        <v>1</v>
+      </c>
+      <c r="H996">
+        <v>0</v>
+      </c>
+      <c r="J996">
+        <v>1</v>
+      </c>
+      <c r="K996">
+        <v>0</v>
+      </c>
+      <c r="L996">
+        <v>0</v>
+      </c>
+      <c r="M996" t="s">
+        <v>316</v>
+      </c>
+      <c r="N996" t="s">
+        <v>316</v>
+      </c>
+      <c r="O996">
+        <v>6</v>
+      </c>
+      <c r="P996">
+        <v>5</v>
+      </c>
+      <c r="Q996">
+        <v>0</v>
+      </c>
+      <c r="R996">
+        <v>0</v>
+      </c>
+      <c r="S996" t="s">
+        <v>24</v>
+      </c>
+      <c r="T996" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="997" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A997" t="s">
+        <v>588</v>
+      </c>
+      <c r="B997" t="s">
+        <v>589</v>
+      </c>
+      <c r="C997">
+        <v>1</v>
+      </c>
+      <c r="D997">
+        <v>1</v>
+      </c>
+      <c r="E997">
+        <v>2</v>
+      </c>
+      <c r="F997">
+        <v>0</v>
+      </c>
+      <c r="G997">
+        <v>18</v>
+      </c>
+      <c r="H997">
+        <v>1</v>
+      </c>
+      <c r="I997">
+        <v>18</v>
+      </c>
+      <c r="J997">
+        <v>9</v>
+      </c>
+      <c r="K997">
+        <v>0</v>
+      </c>
+      <c r="L997">
+        <v>0</v>
+      </c>
+      <c r="M997" s="1">
+        <v>43101</v>
+      </c>
+      <c r="N997" s="1">
+        <v>43101</v>
+      </c>
+      <c r="O997">
+        <v>12</v>
+      </c>
+      <c r="P997">
+        <v>4</v>
+      </c>
+      <c r="Q997">
+        <v>1</v>
+      </c>
+      <c r="R997">
+        <v>0</v>
+      </c>
+      <c r="S997" t="s">
+        <v>109</v>
+      </c>
+      <c r="T997" t="s">
+        <v>129</v>
+      </c>
+      <c r="U997">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="998" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A998" t="s">
+        <v>588</v>
+      </c>
+      <c r="B998" t="s">
+        <v>104</v>
+      </c>
+      <c r="C998">
+        <v>1</v>
+      </c>
+      <c r="D998">
+        <v>1</v>
+      </c>
+      <c r="E998">
+        <v>3</v>
+      </c>
+      <c r="F998">
+        <v>0</v>
+      </c>
+      <c r="G998">
+        <v>16</v>
+      </c>
+      <c r="H998">
+        <v>2</v>
+      </c>
+      <c r="I998">
+        <v>8</v>
+      </c>
+      <c r="J998">
+        <v>5.33</v>
+      </c>
+      <c r="K998">
+        <v>0</v>
+      </c>
+      <c r="L998">
+        <v>0</v>
+      </c>
+      <c r="M998" s="1">
+        <v>42401</v>
+      </c>
+      <c r="N998" s="1">
+        <v>42401</v>
+      </c>
+      <c r="O998">
+        <v>18</v>
+      </c>
+      <c r="P998">
+        <v>10</v>
+      </c>
+      <c r="Q998">
+        <v>2</v>
+      </c>
+      <c r="R998">
+        <v>0</v>
+      </c>
+      <c r="S998" t="s">
+        <v>31</v>
+      </c>
+      <c r="T998" t="s">
+        <v>24</v>
+      </c>
+      <c r="U998">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="999" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A999" t="s">
+        <v>588</v>
+      </c>
+      <c r="B999" t="s">
+        <v>398</v>
+      </c>
+      <c r="C999">
+        <v>1</v>
+      </c>
+      <c r="D999">
+        <v>1</v>
+      </c>
+      <c r="E999">
+        <v>4</v>
+      </c>
+      <c r="F999">
+        <v>1</v>
+      </c>
+      <c r="G999">
+        <v>11</v>
+      </c>
+      <c r="H999">
+        <v>1</v>
+      </c>
+      <c r="I999">
+        <v>11</v>
+      </c>
+      <c r="J999">
+        <v>2.75</v>
+      </c>
+      <c r="K999">
+        <v>0</v>
+      </c>
+      <c r="L999">
+        <v>0</v>
+      </c>
+      <c r="M999" s="2">
+        <v>46327</v>
+      </c>
+      <c r="N999" s="2">
+        <v>46327</v>
+      </c>
+      <c r="O999">
+        <v>24</v>
+      </c>
+      <c r="P999">
+        <v>18</v>
+      </c>
+      <c r="Q999">
+        <v>1</v>
+      </c>
+      <c r="R999">
+        <v>0</v>
+      </c>
+      <c r="S999" t="s">
+        <v>29</v>
+      </c>
+      <c r="T999" t="s">
+        <v>24</v>
+      </c>
+      <c r="U999">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1000" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1000">
+        <v>1</v>
+      </c>
+      <c r="D1000">
+        <v>1</v>
+      </c>
+      <c r="E1000">
+        <v>2</v>
+      </c>
+      <c r="F1000">
+        <v>0</v>
+      </c>
+      <c r="G1000">
+        <v>19</v>
+      </c>
+      <c r="H1000">
+        <v>0</v>
+      </c>
+      <c r="J1000">
+        <v>9.5</v>
+      </c>
+      <c r="K1000">
+        <v>0</v>
+      </c>
+      <c r="L1000">
+        <v>0</v>
+      </c>
+      <c r="M1000" t="s">
+        <v>72</v>
+      </c>
+      <c r="N1000" t="s">
+        <v>72</v>
+      </c>
+      <c r="O1000">
+        <v>12</v>
+      </c>
+      <c r="P1000">
+        <v>5</v>
+      </c>
+      <c r="Q1000">
+        <v>4</v>
+      </c>
+      <c r="R1000">
+        <v>0</v>
+      </c>
+      <c r="S1000" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1000" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1001" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1001" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1001">
+        <v>1</v>
+      </c>
+      <c r="D1001">
+        <v>1</v>
+      </c>
+      <c r="E1001">
+        <v>2</v>
+      </c>
+      <c r="F1001">
+        <v>0</v>
+      </c>
+      <c r="G1001">
+        <v>20</v>
+      </c>
+      <c r="H1001">
+        <v>0</v>
+      </c>
+      <c r="J1001">
+        <v>10</v>
+      </c>
+      <c r="K1001">
+        <v>0</v>
+      </c>
+      <c r="L1001">
+        <v>0</v>
+      </c>
+      <c r="M1001" t="s">
+        <v>135</v>
+      </c>
+      <c r="N1001" t="s">
+        <v>135</v>
+      </c>
+      <c r="O1001">
+        <v>12</v>
+      </c>
+      <c r="P1001">
+        <v>5</v>
+      </c>
+      <c r="Q1001">
+        <v>4</v>
+      </c>
+      <c r="R1001">
+        <v>0</v>
+      </c>
+      <c r="S1001" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1001" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1002" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1002" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1002">
+        <v>1</v>
+      </c>
+      <c r="D1002">
+        <v>1</v>
+      </c>
+      <c r="E1002">
+        <v>2</v>
+      </c>
+      <c r="F1002">
+        <v>0</v>
+      </c>
+      <c r="G1002">
+        <v>12</v>
+      </c>
+      <c r="H1002">
+        <v>1</v>
+      </c>
+      <c r="I1002">
+        <v>12</v>
+      </c>
+      <c r="J1002">
+        <v>6</v>
+      </c>
+      <c r="K1002">
+        <v>0</v>
+      </c>
+      <c r="L1002">
+        <v>0</v>
+      </c>
+      <c r="M1002" s="2">
+        <v>46357</v>
+      </c>
+      <c r="N1002" s="2">
+        <v>46357</v>
+      </c>
+      <c r="O1002">
+        <v>12</v>
+      </c>
+      <c r="P1002">
+        <v>6</v>
+      </c>
+      <c r="Q1002">
+        <v>1</v>
+      </c>
+      <c r="R1002">
+        <v>0</v>
+      </c>
+      <c r="S1002" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1002" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1002">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1003" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1003" t="s">
+        <v>442</v>
+      </c>
+      <c r="C1003">
+        <v>1</v>
+      </c>
+      <c r="D1003">
+        <v>1</v>
+      </c>
+      <c r="E1003">
+        <v>2.4</v>
+      </c>
+      <c r="F1003">
+        <v>0</v>
+      </c>
+      <c r="G1003">
+        <v>30</v>
+      </c>
+      <c r="H1003">
+        <v>1</v>
+      </c>
+      <c r="I1003">
+        <v>30</v>
+      </c>
+      <c r="J1003">
+        <v>11.25</v>
+      </c>
+      <c r="K1003">
+        <v>0</v>
+      </c>
+      <c r="L1003">
+        <v>0</v>
+      </c>
+      <c r="M1003" s="1">
+        <v>10959</v>
+      </c>
+      <c r="N1003" s="1">
+        <v>10959</v>
+      </c>
+      <c r="O1003">
+        <v>16</v>
+      </c>
+      <c r="P1003">
+        <v>8</v>
+      </c>
+      <c r="Q1003">
+        <v>1</v>
+      </c>
+      <c r="R1003">
+        <v>0</v>
+      </c>
+      <c r="S1003" t="s">
+        <v>590</v>
+      </c>
+      <c r="T1003" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1003">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1004" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1004" t="s">
+        <v>591</v>
+      </c>
+      <c r="C1004">
+        <v>1</v>
+      </c>
+      <c r="D1004">
+        <v>1</v>
+      </c>
+      <c r="E1004">
+        <v>3</v>
+      </c>
+      <c r="F1004">
+        <v>0</v>
+      </c>
+      <c r="G1004">
+        <v>13</v>
+      </c>
+      <c r="H1004">
+        <v>4</v>
+      </c>
+      <c r="I1004">
+        <v>3.25</v>
+      </c>
+      <c r="J1004">
+        <v>4.33</v>
+      </c>
+      <c r="K1004">
+        <v>0</v>
+      </c>
+      <c r="L1004">
+        <v>0</v>
+      </c>
+      <c r="M1004" s="1">
+        <v>41365</v>
+      </c>
+      <c r="N1004" s="1">
+        <v>41365</v>
+      </c>
+      <c r="O1004">
+        <v>18</v>
+      </c>
+      <c r="P1004">
+        <v>15</v>
+      </c>
+      <c r="Q1004">
+        <v>1</v>
+      </c>
+      <c r="R1004">
+        <v>0</v>
+      </c>
+      <c r="S1004" t="s">
+        <v>238</v>
+      </c>
+      <c r="T1004" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1004">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1005" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1005" t="s">
+        <v>592</v>
+      </c>
+      <c r="C1005">
+        <v>1</v>
+      </c>
+      <c r="D1005">
+        <v>1</v>
+      </c>
+      <c r="E1005">
+        <v>3</v>
+      </c>
+      <c r="F1005">
+        <v>0</v>
+      </c>
+      <c r="G1005">
+        <v>11</v>
+      </c>
+      <c r="H1005">
+        <v>1</v>
+      </c>
+      <c r="I1005">
+        <v>11</v>
+      </c>
+      <c r="J1005">
+        <v>3.67</v>
+      </c>
+      <c r="K1005">
+        <v>0</v>
+      </c>
+      <c r="L1005">
+        <v>0</v>
+      </c>
+      <c r="M1005" s="2">
+        <v>46327</v>
+      </c>
+      <c r="N1005" s="2">
+        <v>46327</v>
+      </c>
+      <c r="O1005">
+        <v>18</v>
+      </c>
+      <c r="P1005">
+        <v>12</v>
+      </c>
+      <c r="Q1005">
+        <v>1</v>
+      </c>
+      <c r="R1005">
+        <v>0</v>
+      </c>
+      <c r="S1005" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1005" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1005">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1006" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1006" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1006">
+        <v>1</v>
+      </c>
+      <c r="D1006">
+        <v>1</v>
+      </c>
+      <c r="E1006">
+        <v>4</v>
+      </c>
+      <c r="F1006">
+        <v>0</v>
+      </c>
+      <c r="G1006">
+        <v>33</v>
+      </c>
+      <c r="H1006">
+        <v>0</v>
+      </c>
+      <c r="J1006">
+        <v>8.25</v>
+      </c>
+      <c r="K1006">
+        <v>0</v>
+      </c>
+      <c r="L1006">
+        <v>0</v>
+      </c>
+      <c r="M1006" t="s">
+        <v>297</v>
+      </c>
+      <c r="N1006" t="s">
+        <v>297</v>
+      </c>
+      <c r="O1006">
+        <v>24</v>
+      </c>
+      <c r="P1006">
+        <v>9</v>
+      </c>
+      <c r="Q1006">
+        <v>2</v>
+      </c>
+      <c r="R1006">
+        <v>1</v>
+      </c>
+      <c r="S1006" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1006" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1007" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1007" t="s">
+        <v>364</v>
+      </c>
+      <c r="C1007">
+        <v>1</v>
+      </c>
+      <c r="D1007">
+        <v>1</v>
+      </c>
+      <c r="E1007">
+        <v>3</v>
+      </c>
+      <c r="F1007">
+        <v>0</v>
+      </c>
+      <c r="G1007">
+        <v>15</v>
+      </c>
+      <c r="H1007">
+        <v>0</v>
+      </c>
+      <c r="J1007">
+        <v>5</v>
+      </c>
+      <c r="K1007">
+        <v>0</v>
+      </c>
+      <c r="L1007">
+        <v>0</v>
+      </c>
+      <c r="M1007" t="s">
+        <v>145</v>
+      </c>
+      <c r="N1007" t="s">
+        <v>145</v>
+      </c>
+      <c r="O1007">
+        <v>18</v>
+      </c>
+      <c r="P1007">
+        <v>6</v>
+      </c>
+      <c r="Q1007">
+        <v>0</v>
+      </c>
+      <c r="R1007">
+        <v>0</v>
+      </c>
+      <c r="S1007" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1007" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1008" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>267</v>
+      </c>
+      <c r="C1008">
+        <v>1</v>
+      </c>
+      <c r="D1008">
+        <v>1</v>
+      </c>
+      <c r="E1008">
+        <v>3</v>
+      </c>
+      <c r="F1008">
+        <v>0</v>
+      </c>
+      <c r="G1008">
+        <v>27</v>
+      </c>
+      <c r="H1008">
+        <v>1</v>
+      </c>
+      <c r="I1008">
+        <v>27</v>
+      </c>
+      <c r="J1008">
+        <v>9</v>
+      </c>
+      <c r="K1008">
+        <v>0</v>
+      </c>
+      <c r="L1008">
+        <v>0</v>
+      </c>
+      <c r="M1008" s="1">
+        <v>46388</v>
+      </c>
+      <c r="N1008" s="1">
+        <v>46388</v>
+      </c>
+      <c r="O1008">
+        <v>18</v>
+      </c>
+      <c r="P1008">
+        <v>5</v>
+      </c>
+      <c r="Q1008">
+        <v>4</v>
+      </c>
+      <c r="R1008">
+        <v>0</v>
+      </c>
+      <c r="S1008" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1008" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1008">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1009" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1009" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1009">
+        <v>1</v>
+      </c>
+      <c r="D1009">
+        <v>1</v>
+      </c>
+      <c r="E1009">
+        <v>3</v>
+      </c>
+      <c r="F1009">
+        <v>0</v>
+      </c>
+      <c r="G1009">
+        <v>24</v>
+      </c>
+      <c r="H1009">
+        <v>0</v>
+      </c>
+      <c r="J1009">
+        <v>8</v>
+      </c>
+      <c r="K1009">
+        <v>0</v>
+      </c>
+      <c r="L1009">
+        <v>0</v>
+      </c>
+      <c r="M1009" t="s">
+        <v>162</v>
+      </c>
+      <c r="N1009" t="s">
+        <v>162</v>
+      </c>
+      <c r="O1009">
+        <v>18</v>
+      </c>
+      <c r="P1009">
+        <v>7</v>
+      </c>
+      <c r="Q1009">
+        <v>2</v>
+      </c>
+      <c r="R1009">
+        <v>0</v>
+      </c>
+      <c r="S1009" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1009" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1010" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>432</v>
+      </c>
+      <c r="C1010">
+        <v>1</v>
+      </c>
+      <c r="D1010">
+        <v>1</v>
+      </c>
+      <c r="E1010">
+        <v>1</v>
+      </c>
+      <c r="F1010">
+        <v>0</v>
+      </c>
+      <c r="G1010">
+        <v>11</v>
+      </c>
+      <c r="H1010">
+        <v>0</v>
+      </c>
+      <c r="J1010">
+        <v>11</v>
+      </c>
+      <c r="K1010">
+        <v>0</v>
+      </c>
+      <c r="L1010">
+        <v>0</v>
+      </c>
+      <c r="M1010" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1010" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1010">
+        <v>6</v>
+      </c>
+      <c r="P1010">
+        <v>0</v>
+      </c>
+      <c r="Q1010">
+        <v>1</v>
+      </c>
+      <c r="R1010">
+        <v>0</v>
+      </c>
+      <c r="S1010" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1010" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1011" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1011" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1011">
+        <v>1</v>
+      </c>
+      <c r="D1011">
+        <v>1</v>
+      </c>
+      <c r="E1011">
+        <v>4</v>
+      </c>
+      <c r="F1011">
+        <v>0</v>
+      </c>
+      <c r="G1011">
+        <v>28</v>
+      </c>
+      <c r="H1011">
+        <v>0</v>
+      </c>
+      <c r="J1011">
+        <v>7</v>
+      </c>
+      <c r="K1011">
+        <v>0</v>
+      </c>
+      <c r="L1011">
+        <v>0</v>
+      </c>
+      <c r="M1011" t="s">
+        <v>100</v>
+      </c>
+      <c r="N1011" t="s">
+        <v>100</v>
+      </c>
+      <c r="O1011">
+        <v>24</v>
+      </c>
+      <c r="P1011">
+        <v>7</v>
+      </c>
+      <c r="Q1011">
+        <v>1</v>
+      </c>
+      <c r="R1011">
+        <v>1</v>
+      </c>
+      <c r="S1011" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1011" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1012" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1012" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1012">
+        <v>1</v>
+      </c>
+      <c r="D1012">
+        <v>1</v>
+      </c>
+      <c r="E1012">
+        <v>4</v>
+      </c>
+      <c r="F1012">
+        <v>0</v>
+      </c>
+      <c r="G1012">
+        <v>27</v>
+      </c>
+      <c r="H1012">
+        <v>0</v>
+      </c>
+      <c r="J1012">
+        <v>6.75</v>
+      </c>
+      <c r="K1012">
+        <v>0</v>
+      </c>
+      <c r="L1012">
+        <v>0</v>
+      </c>
+      <c r="M1012" t="s">
+        <v>93</v>
+      </c>
+      <c r="N1012" t="s">
+        <v>93</v>
+      </c>
+      <c r="O1012">
+        <v>24</v>
+      </c>
+      <c r="P1012">
+        <v>7</v>
+      </c>
+      <c r="Q1012">
+        <v>2</v>
+      </c>
+      <c r="R1012">
+        <v>0</v>
+      </c>
+      <c r="S1012" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1012" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1013" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1013" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1013">
+        <v>1</v>
+      </c>
+      <c r="D1013">
+        <v>1</v>
+      </c>
+      <c r="E1013">
+        <v>4</v>
+      </c>
+      <c r="F1013">
+        <v>0</v>
+      </c>
+      <c r="G1013">
+        <v>24</v>
+      </c>
+      <c r="H1013">
+        <v>3</v>
+      </c>
+      <c r="I1013">
+        <v>8</v>
+      </c>
+      <c r="J1013">
+        <v>6</v>
+      </c>
+      <c r="K1013">
+        <v>0</v>
+      </c>
+      <c r="L1013">
+        <v>0</v>
+      </c>
+      <c r="M1013" s="1">
+        <v>45352</v>
+      </c>
+      <c r="N1013" s="1">
+        <v>45352</v>
+      </c>
+      <c r="O1013">
+        <v>24</v>
+      </c>
+      <c r="P1013">
+        <v>13</v>
+      </c>
+      <c r="Q1013">
+        <v>3</v>
+      </c>
+      <c r="R1013">
+        <v>0</v>
+      </c>
+      <c r="S1013" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1013" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1013">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1014" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1014" t="s">
+        <v>393</v>
+      </c>
+      <c r="C1014">
+        <v>1</v>
+      </c>
+      <c r="D1014">
+        <v>1</v>
+      </c>
+      <c r="E1014">
+        <v>4</v>
+      </c>
+      <c r="F1014">
+        <v>0</v>
+      </c>
+      <c r="G1014">
+        <v>36</v>
+      </c>
+      <c r="H1014">
+        <v>1</v>
+      </c>
+      <c r="I1014">
+        <v>36</v>
+      </c>
+      <c r="J1014">
+        <v>9</v>
+      </c>
+      <c r="K1014">
+        <v>0</v>
+      </c>
+      <c r="L1014">
+        <v>0</v>
+      </c>
+      <c r="M1014" s="1">
+        <v>13150</v>
+      </c>
+      <c r="N1014" s="1">
+        <v>13150</v>
+      </c>
+      <c r="O1014">
+        <v>24</v>
+      </c>
+      <c r="P1014">
+        <v>11</v>
+      </c>
+      <c r="Q1014">
+        <v>3</v>
+      </c>
+      <c r="R1014">
+        <v>1</v>
+      </c>
+      <c r="S1014" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1014" t="s">
+        <v>129</v>
+      </c>
+      <c r="U1014">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1015" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1015" t="s">
+        <v>512</v>
+      </c>
+      <c r="C1015">
+        <v>1</v>
+      </c>
+      <c r="D1015">
+        <v>1</v>
+      </c>
+      <c r="E1015">
+        <v>2</v>
+      </c>
+      <c r="F1015">
+        <v>0</v>
+      </c>
+      <c r="G1015">
+        <v>21</v>
+      </c>
+      <c r="H1015">
+        <v>0</v>
+      </c>
+      <c r="J1015">
+        <v>10.5</v>
+      </c>
+      <c r="K1015">
+        <v>0</v>
+      </c>
+      <c r="L1015">
+        <v>0</v>
+      </c>
+      <c r="M1015" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1015" t="s">
+        <v>84</v>
+      </c>
+      <c r="O1015">
+        <v>12</v>
+      </c>
+      <c r="P1015">
+        <v>6</v>
+      </c>
+      <c r="Q1015">
+        <v>2</v>
+      </c>
+      <c r="R1015">
+        <v>1</v>
+      </c>
+      <c r="S1015" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1015" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1016" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1016" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1016">
+        <v>1</v>
+      </c>
+      <c r="D1016">
+        <v>1</v>
+      </c>
+      <c r="E1016">
+        <v>3</v>
+      </c>
+      <c r="F1016">
+        <v>0</v>
+      </c>
+      <c r="G1016">
+        <v>32</v>
+      </c>
+      <c r="H1016">
+        <v>0</v>
+      </c>
+      <c r="J1016">
+        <v>10.67</v>
+      </c>
+      <c r="K1016">
+        <v>0</v>
+      </c>
+      <c r="L1016">
+        <v>0</v>
+      </c>
+      <c r="M1016" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1016" t="s">
+        <v>65</v>
+      </c>
+      <c r="O1016">
+        <v>18</v>
+      </c>
+      <c r="P1016">
+        <v>3</v>
+      </c>
+      <c r="Q1016">
+        <v>2</v>
+      </c>
+      <c r="R1016">
+        <v>1</v>
+      </c>
+      <c r="S1016" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1016" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1017" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1017" t="s">
+        <v>594</v>
+      </c>
+      <c r="C1017">
+        <v>1</v>
+      </c>
+      <c r="D1017">
+        <v>1</v>
+      </c>
+      <c r="E1017">
+        <v>1</v>
+      </c>
+      <c r="F1017">
+        <v>0</v>
+      </c>
+      <c r="G1017">
+        <v>9</v>
+      </c>
+      <c r="H1017">
+        <v>0</v>
+      </c>
+      <c r="J1017">
+        <v>9</v>
+      </c>
+      <c r="K1017">
+        <v>0</v>
+      </c>
+      <c r="L1017">
+        <v>0</v>
+      </c>
+      <c r="M1017" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1017" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1017">
+        <v>6</v>
+      </c>
+      <c r="P1017">
+        <v>1</v>
+      </c>
+      <c r="Q1017">
+        <v>0</v>
+      </c>
+      <c r="R1017">
+        <v>0</v>
+      </c>
+      <c r="S1017" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1017" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1018" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1018" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1018">
+        <v>1</v>
+      </c>
+      <c r="D1018">
+        <v>1</v>
+      </c>
+      <c r="E1018">
+        <v>3</v>
+      </c>
+      <c r="F1018">
+        <v>0</v>
+      </c>
+      <c r="G1018">
+        <v>21</v>
+      </c>
+      <c r="H1018">
+        <v>0</v>
+      </c>
+      <c r="J1018">
+        <v>7</v>
+      </c>
+      <c r="K1018">
+        <v>0</v>
+      </c>
+      <c r="L1018">
+        <v>0</v>
+      </c>
+      <c r="M1018" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1018" t="s">
+        <v>84</v>
+      </c>
+      <c r="O1018">
+        <v>18</v>
+      </c>
+      <c r="P1018">
+        <v>8</v>
+      </c>
+      <c r="Q1018">
+        <v>2</v>
+      </c>
+      <c r="R1018">
+        <v>0</v>
+      </c>
+      <c r="S1018" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1018" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1019" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1019" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1019">
+        <v>1</v>
+      </c>
+      <c r="D1019">
+        <v>1</v>
+      </c>
+      <c r="E1019">
+        <v>4</v>
+      </c>
+      <c r="F1019">
+        <v>0</v>
+      </c>
+      <c r="G1019">
+        <v>26</v>
+      </c>
+      <c r="H1019">
+        <v>4</v>
+      </c>
+      <c r="I1019">
+        <v>6.5</v>
+      </c>
+      <c r="J1019">
+        <v>6.5</v>
+      </c>
+      <c r="K1019">
+        <v>0</v>
+      </c>
+      <c r="L1019">
+        <v>0</v>
+      </c>
+      <c r="M1019" s="1">
+        <v>46113</v>
+      </c>
+      <c r="N1019" s="1">
+        <v>46113</v>
+      </c>
+      <c r="O1019">
+        <v>24</v>
+      </c>
+      <c r="P1019">
+        <v>15</v>
+      </c>
+      <c r="Q1019">
+        <v>2</v>
+      </c>
+      <c r="R1019">
+        <v>1</v>
+      </c>
+      <c r="S1019" t="s">
+        <v>56</v>
+      </c>
+      <c r="T1019" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1019">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1020" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>595</v>
+      </c>
+      <c r="C1020">
+        <v>1</v>
+      </c>
+      <c r="D1020">
+        <v>1</v>
+      </c>
+      <c r="E1020">
+        <v>3</v>
+      </c>
+      <c r="F1020">
+        <v>0</v>
+      </c>
+      <c r="G1020">
+        <v>25</v>
+      </c>
+      <c r="H1020">
+        <v>1</v>
+      </c>
+      <c r="I1020">
+        <v>25</v>
+      </c>
+      <c r="J1020">
+        <v>8.33</v>
+      </c>
+      <c r="K1020">
+        <v>0</v>
+      </c>
+      <c r="L1020">
+        <v>0</v>
+      </c>
+      <c r="M1020" s="1">
+        <v>45658</v>
+      </c>
+      <c r="N1020" s="1">
+        <v>45658</v>
+      </c>
+      <c r="O1020">
+        <v>18</v>
+      </c>
+      <c r="P1020">
+        <v>7</v>
+      </c>
+      <c r="Q1020">
+        <v>2</v>
+      </c>
+      <c r="R1020">
+        <v>0</v>
+      </c>
+      <c r="S1020" t="s">
+        <v>109</v>
+      </c>
+      <c r="T1020" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1020">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1021" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>438</v>
+      </c>
+      <c r="C1021">
+        <v>1</v>
+      </c>
+      <c r="D1021">
+        <v>1</v>
+      </c>
+      <c r="E1021">
+        <v>2.4</v>
+      </c>
+      <c r="F1021">
+        <v>0</v>
+      </c>
+      <c r="G1021">
+        <v>23</v>
+      </c>
+      <c r="H1021">
+        <v>0</v>
+      </c>
+      <c r="J1021">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="K1021">
+        <v>0</v>
+      </c>
+      <c r="L1021">
+        <v>0</v>
+      </c>
+      <c r="M1021" t="s">
+        <v>216</v>
+      </c>
+      <c r="N1021" t="s">
+        <v>216</v>
+      </c>
+      <c r="O1021">
+        <v>16</v>
+      </c>
+      <c r="P1021">
+        <v>7</v>
+      </c>
+      <c r="Q1021">
+        <v>2</v>
+      </c>
+      <c r="R1021">
+        <v>0</v>
+      </c>
+      <c r="S1021" t="s">
+        <v>109</v>
+      </c>
+      <c r="T1021" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1022" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1022" t="s">
+        <v>395</v>
+      </c>
+      <c r="C1022">
+        <v>1</v>
+      </c>
+      <c r="D1022">
+        <v>1</v>
+      </c>
+      <c r="E1022">
+        <v>4</v>
+      </c>
+      <c r="F1022">
+        <v>0</v>
+      </c>
+      <c r="G1022">
+        <v>20</v>
+      </c>
+      <c r="H1022">
+        <v>2</v>
+      </c>
+      <c r="I1022">
+        <v>10</v>
+      </c>
+      <c r="J1022">
+        <v>5</v>
+      </c>
+      <c r="K1022">
+        <v>0</v>
+      </c>
+      <c r="L1022">
+        <v>0</v>
+      </c>
+      <c r="M1022" s="1">
+        <v>43862</v>
+      </c>
+      <c r="N1022" s="1">
+        <v>43862</v>
+      </c>
+      <c r="O1022">
+        <v>24</v>
+      </c>
+      <c r="P1022">
+        <v>13</v>
+      </c>
+      <c r="Q1022">
+        <v>1</v>
+      </c>
+      <c r="R1022">
+        <v>1</v>
+      </c>
+      <c r="S1022" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1022" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1022">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Midweek League bowling stats for season.xlsx
+++ b/NV Play Midweek League bowling stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4969" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5029" uniqueCount="600">
   <si>
     <t>Group</t>
   </si>
@@ -1808,6 +1808,18 @@
   <si>
     <t>Byjo Varghese</t>
   </si>
+  <si>
+    <t>Belfast Superkings MW XI v Ardent Blues MW1 XI, TBC - 23 July 2026</t>
+  </si>
+  <si>
+    <t>Muralee Krishnan</t>
+  </si>
+  <si>
+    <t>Rijo George</t>
+  </si>
+  <si>
+    <t>6 (11)</t>
+  </si>
 </sst>
 </file>
 
@@ -2615,7 +2627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U1022"/>
+  <dimension ref="A1:U1034"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="69.28515625" bestFit="1" customWidth="1"/>
@@ -66383,6 +66395,750 @@
         <v>12</v>
       </c>
     </row>
+    <row r="1023" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1023" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1023" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1023">
+        <v>1</v>
+      </c>
+      <c r="D1023">
+        <v>1</v>
+      </c>
+      <c r="E1023">
+        <v>1</v>
+      </c>
+      <c r="F1023">
+        <v>0</v>
+      </c>
+      <c r="G1023">
+        <v>13</v>
+      </c>
+      <c r="H1023">
+        <v>0</v>
+      </c>
+      <c r="J1023">
+        <v>13</v>
+      </c>
+      <c r="K1023">
+        <v>0</v>
+      </c>
+      <c r="L1023">
+        <v>0</v>
+      </c>
+      <c r="M1023" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1023" t="s">
+        <v>50</v>
+      </c>
+      <c r="O1023">
+        <v>6</v>
+      </c>
+      <c r="P1023">
+        <v>3</v>
+      </c>
+      <c r="Q1023">
+        <v>1</v>
+      </c>
+      <c r="R1023">
+        <v>1</v>
+      </c>
+      <c r="S1023" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1023" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1024" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1024" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1024">
+        <v>1</v>
+      </c>
+      <c r="D1024">
+        <v>1</v>
+      </c>
+      <c r="E1024">
+        <v>4</v>
+      </c>
+      <c r="F1024">
+        <v>0</v>
+      </c>
+      <c r="G1024">
+        <v>25</v>
+      </c>
+      <c r="H1024">
+        <v>2</v>
+      </c>
+      <c r="I1024">
+        <v>12.5</v>
+      </c>
+      <c r="J1024">
+        <v>6.25</v>
+      </c>
+      <c r="K1024">
+        <v>0</v>
+      </c>
+      <c r="L1024">
+        <v>0</v>
+      </c>
+      <c r="M1024" s="1">
+        <v>45689</v>
+      </c>
+      <c r="N1024" s="1">
+        <v>45689</v>
+      </c>
+      <c r="O1024">
+        <v>24</v>
+      </c>
+      <c r="P1024">
+        <v>12</v>
+      </c>
+      <c r="Q1024">
+        <v>3</v>
+      </c>
+      <c r="R1024">
+        <v>0</v>
+      </c>
+      <c r="S1024" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1024" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1024">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1025" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1025" t="s">
+        <v>539</v>
+      </c>
+      <c r="C1025">
+        <v>1</v>
+      </c>
+      <c r="D1025">
+        <v>1</v>
+      </c>
+      <c r="E1025">
+        <v>4</v>
+      </c>
+      <c r="F1025">
+        <v>0</v>
+      </c>
+      <c r="G1025">
+        <v>20</v>
+      </c>
+      <c r="H1025">
+        <v>2</v>
+      </c>
+      <c r="I1025">
+        <v>10</v>
+      </c>
+      <c r="J1025">
+        <v>5</v>
+      </c>
+      <c r="K1025">
+        <v>0</v>
+      </c>
+      <c r="L1025">
+        <v>0</v>
+      </c>
+      <c r="M1025" s="1">
+        <v>43862</v>
+      </c>
+      <c r="N1025" s="1">
+        <v>43862</v>
+      </c>
+      <c r="O1025">
+        <v>24</v>
+      </c>
+      <c r="P1025">
+        <v>14</v>
+      </c>
+      <c r="Q1025">
+        <v>3</v>
+      </c>
+      <c r="R1025">
+        <v>0</v>
+      </c>
+      <c r="S1025" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1025" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1025">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1026" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1026" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1026">
+        <v>1</v>
+      </c>
+      <c r="D1026">
+        <v>1</v>
+      </c>
+      <c r="E1026">
+        <v>4</v>
+      </c>
+      <c r="F1026">
+        <v>0</v>
+      </c>
+      <c r="G1026">
+        <v>47</v>
+      </c>
+      <c r="H1026">
+        <v>1</v>
+      </c>
+      <c r="I1026">
+        <v>47</v>
+      </c>
+      <c r="J1026">
+        <v>11.75</v>
+      </c>
+      <c r="K1026">
+        <v>0</v>
+      </c>
+      <c r="L1026">
+        <v>0</v>
+      </c>
+      <c r="M1026" s="1">
+        <v>17168</v>
+      </c>
+      <c r="N1026" s="1">
+        <v>17168</v>
+      </c>
+      <c r="O1026">
+        <v>24</v>
+      </c>
+      <c r="P1026">
+        <v>8</v>
+      </c>
+      <c r="Q1026">
+        <v>4</v>
+      </c>
+      <c r="R1026">
+        <v>2</v>
+      </c>
+      <c r="S1026" t="s">
+        <v>34</v>
+      </c>
+      <c r="T1026" t="s">
+        <v>42</v>
+      </c>
+      <c r="U1026">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1027" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1027" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1027">
+        <v>1</v>
+      </c>
+      <c r="D1027">
+        <v>1</v>
+      </c>
+      <c r="E1027">
+        <v>4</v>
+      </c>
+      <c r="F1027">
+        <v>0</v>
+      </c>
+      <c r="G1027">
+        <v>57</v>
+      </c>
+      <c r="H1027">
+        <v>1</v>
+      </c>
+      <c r="I1027">
+        <v>57</v>
+      </c>
+      <c r="J1027">
+        <v>14.25</v>
+      </c>
+      <c r="K1027">
+        <v>0</v>
+      </c>
+      <c r="L1027">
+        <v>0</v>
+      </c>
+      <c r="M1027" s="1">
+        <v>20821</v>
+      </c>
+      <c r="N1027" s="1">
+        <v>20821</v>
+      </c>
+      <c r="O1027">
+        <v>24</v>
+      </c>
+      <c r="P1027">
+        <v>6</v>
+      </c>
+      <c r="Q1027">
+        <v>7</v>
+      </c>
+      <c r="R1027">
+        <v>3</v>
+      </c>
+      <c r="S1027" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1027" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1027">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1028" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1028" t="s">
+        <v>597</v>
+      </c>
+      <c r="C1028">
+        <v>1</v>
+      </c>
+      <c r="D1028">
+        <v>1</v>
+      </c>
+      <c r="E1028">
+        <v>1</v>
+      </c>
+      <c r="F1028">
+        <v>0</v>
+      </c>
+      <c r="G1028">
+        <v>17</v>
+      </c>
+      <c r="H1028">
+        <v>0</v>
+      </c>
+      <c r="J1028">
+        <v>17</v>
+      </c>
+      <c r="K1028">
+        <v>0</v>
+      </c>
+      <c r="L1028">
+        <v>0</v>
+      </c>
+      <c r="M1028" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1028" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1028">
+        <v>6</v>
+      </c>
+      <c r="P1028">
+        <v>1</v>
+      </c>
+      <c r="Q1028">
+        <v>2</v>
+      </c>
+      <c r="R1028">
+        <v>1</v>
+      </c>
+      <c r="S1028" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1028" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1029" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1029" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1029">
+        <v>1</v>
+      </c>
+      <c r="D1029">
+        <v>1</v>
+      </c>
+      <c r="E1029">
+        <v>1</v>
+      </c>
+      <c r="F1029">
+        <v>0</v>
+      </c>
+      <c r="G1029">
+        <v>14</v>
+      </c>
+      <c r="H1029">
+        <v>0</v>
+      </c>
+      <c r="J1029">
+        <v>14</v>
+      </c>
+      <c r="K1029">
+        <v>0</v>
+      </c>
+      <c r="L1029">
+        <v>0</v>
+      </c>
+      <c r="M1029" t="s">
+        <v>193</v>
+      </c>
+      <c r="N1029" t="s">
+        <v>193</v>
+      </c>
+      <c r="O1029">
+        <v>6</v>
+      </c>
+      <c r="P1029">
+        <v>2</v>
+      </c>
+      <c r="Q1029">
+        <v>0</v>
+      </c>
+      <c r="R1029">
+        <v>2</v>
+      </c>
+      <c r="S1029" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1029" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1030" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1030" t="s">
+        <v>598</v>
+      </c>
+      <c r="C1030">
+        <v>1</v>
+      </c>
+      <c r="D1030">
+        <v>1</v>
+      </c>
+      <c r="E1030">
+        <v>3.4</v>
+      </c>
+      <c r="F1030">
+        <v>0</v>
+      </c>
+      <c r="G1030">
+        <v>35</v>
+      </c>
+      <c r="H1030">
+        <v>1</v>
+      </c>
+      <c r="I1030">
+        <v>35</v>
+      </c>
+      <c r="J1030">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="K1030">
+        <v>0</v>
+      </c>
+      <c r="L1030">
+        <v>0</v>
+      </c>
+      <c r="M1030" s="1">
+        <v>12785</v>
+      </c>
+      <c r="N1030" s="1">
+        <v>12785</v>
+      </c>
+      <c r="O1030">
+        <v>22</v>
+      </c>
+      <c r="P1030">
+        <v>12</v>
+      </c>
+      <c r="Q1030">
+        <v>3</v>
+      </c>
+      <c r="R1030">
+        <v>1</v>
+      </c>
+      <c r="S1030" t="s">
+        <v>599</v>
+      </c>
+      <c r="T1030" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1030">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1031" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1031" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1031">
+        <v>1</v>
+      </c>
+      <c r="D1031">
+        <v>1</v>
+      </c>
+      <c r="E1031">
+        <v>3</v>
+      </c>
+      <c r="F1031">
+        <v>0</v>
+      </c>
+      <c r="G1031">
+        <v>28</v>
+      </c>
+      <c r="H1031">
+        <v>0</v>
+      </c>
+      <c r="J1031">
+        <v>9.33</v>
+      </c>
+      <c r="K1031">
+        <v>0</v>
+      </c>
+      <c r="L1031">
+        <v>0</v>
+      </c>
+      <c r="M1031" t="s">
+        <v>100</v>
+      </c>
+      <c r="N1031" t="s">
+        <v>100</v>
+      </c>
+      <c r="O1031">
+        <v>18</v>
+      </c>
+      <c r="P1031">
+        <v>6</v>
+      </c>
+      <c r="Q1031">
+        <v>4</v>
+      </c>
+      <c r="R1031">
+        <v>0</v>
+      </c>
+      <c r="S1031" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1031" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1032" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1032" t="s">
+        <v>441</v>
+      </c>
+      <c r="C1032">
+        <v>1</v>
+      </c>
+      <c r="D1032">
+        <v>1</v>
+      </c>
+      <c r="E1032">
+        <v>4</v>
+      </c>
+      <c r="F1032">
+        <v>0</v>
+      </c>
+      <c r="G1032">
+        <v>40</v>
+      </c>
+      <c r="H1032">
+        <v>0</v>
+      </c>
+      <c r="J1032">
+        <v>10</v>
+      </c>
+      <c r="K1032">
+        <v>0</v>
+      </c>
+      <c r="L1032">
+        <v>0</v>
+      </c>
+      <c r="M1032" t="s">
+        <v>345</v>
+      </c>
+      <c r="N1032" t="s">
+        <v>345</v>
+      </c>
+      <c r="O1032">
+        <v>24</v>
+      </c>
+      <c r="P1032">
+        <v>9</v>
+      </c>
+      <c r="Q1032">
+        <v>4</v>
+      </c>
+      <c r="R1032">
+        <v>1</v>
+      </c>
+      <c r="S1032" t="s">
+        <v>34</v>
+      </c>
+      <c r="T1032" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1033" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1033" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1033">
+        <v>1</v>
+      </c>
+      <c r="D1033">
+        <v>1</v>
+      </c>
+      <c r="E1033">
+        <v>4</v>
+      </c>
+      <c r="F1033">
+        <v>0</v>
+      </c>
+      <c r="G1033">
+        <v>45</v>
+      </c>
+      <c r="H1033">
+        <v>1</v>
+      </c>
+      <c r="I1033">
+        <v>45</v>
+      </c>
+      <c r="J1033">
+        <v>11.25</v>
+      </c>
+      <c r="K1033">
+        <v>0</v>
+      </c>
+      <c r="L1033">
+        <v>0</v>
+      </c>
+      <c r="M1033" s="1">
+        <v>16438</v>
+      </c>
+      <c r="N1033" s="1">
+        <v>16438</v>
+      </c>
+      <c r="O1033">
+        <v>24</v>
+      </c>
+      <c r="P1033">
+        <v>10</v>
+      </c>
+      <c r="Q1033">
+        <v>6</v>
+      </c>
+      <c r="R1033">
+        <v>1</v>
+      </c>
+      <c r="S1033" t="s">
+        <v>155</v>
+      </c>
+      <c r="T1033" t="s">
+        <v>31</v>
+      </c>
+      <c r="U1033">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1034" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1034" t="s">
+        <v>458</v>
+      </c>
+      <c r="C1034">
+        <v>1</v>
+      </c>
+      <c r="D1034">
+        <v>1</v>
+      </c>
+      <c r="E1034">
+        <v>4</v>
+      </c>
+      <c r="F1034">
+        <v>0</v>
+      </c>
+      <c r="G1034">
+        <v>25</v>
+      </c>
+      <c r="H1034">
+        <v>0</v>
+      </c>
+      <c r="J1034">
+        <v>6.25</v>
+      </c>
+      <c r="K1034">
+        <v>0</v>
+      </c>
+      <c r="L1034">
+        <v>0</v>
+      </c>
+      <c r="M1034" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1034" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1034">
+        <v>24</v>
+      </c>
+      <c r="P1034">
+        <v>10</v>
+      </c>
+      <c r="Q1034">
+        <v>1</v>
+      </c>
+      <c r="R1034">
+        <v>1</v>
+      </c>
+      <c r="S1034" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1034" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Midweek League bowling stats for season.xlsx
+++ b/NV Play Midweek League bowling stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5029" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5149" uniqueCount="605">
   <si>
     <t>Group</t>
   </si>
@@ -1820,6 +1820,21 @@
   <si>
     <t>6 (11)</t>
   </si>
+  <si>
+    <t>Downpatrick MW XI v Dunmurry MW2 XI, The Meadow - 29 July 2026</t>
+  </si>
+  <si>
+    <t>Onkar Jadhav</t>
+  </si>
+  <si>
+    <t>Sidharth Kumar</t>
+  </si>
+  <si>
+    <t>Muckamore MW1 XI v Arches MW XI, Moylena - 29 July 2026</t>
+  </si>
+  <si>
+    <t>Bradley Hodge</t>
+  </si>
 </sst>
 </file>
 
@@ -2627,7 +2642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U1034"/>
+  <dimension ref="A1:U1059"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="69.28515625" bestFit="1" customWidth="1"/>
@@ -67139,6 +67154,1571 @@
         <v>24</v>
       </c>
     </row>
+    <row r="1035" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1035" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1035" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1035">
+        <v>1</v>
+      </c>
+      <c r="D1035">
+        <v>1</v>
+      </c>
+      <c r="E1035">
+        <v>2</v>
+      </c>
+      <c r="F1035">
+        <v>0</v>
+      </c>
+      <c r="G1035">
+        <v>19</v>
+      </c>
+      <c r="H1035">
+        <v>1</v>
+      </c>
+      <c r="I1035">
+        <v>19</v>
+      </c>
+      <c r="J1035">
+        <v>9.5</v>
+      </c>
+      <c r="K1035">
+        <v>0</v>
+      </c>
+      <c r="L1035">
+        <v>0</v>
+      </c>
+      <c r="M1035" s="1">
+        <v>43466</v>
+      </c>
+      <c r="N1035" s="1">
+        <v>43466</v>
+      </c>
+      <c r="O1035">
+        <v>12</v>
+      </c>
+      <c r="P1035">
+        <v>6</v>
+      </c>
+      <c r="Q1035">
+        <v>1</v>
+      </c>
+      <c r="R1035">
+        <v>2</v>
+      </c>
+      <c r="S1035" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1035" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1035">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1036" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1036" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1036">
+        <v>1</v>
+      </c>
+      <c r="D1036">
+        <v>1</v>
+      </c>
+      <c r="E1036">
+        <v>2</v>
+      </c>
+      <c r="F1036">
+        <v>0</v>
+      </c>
+      <c r="G1036">
+        <v>9</v>
+      </c>
+      <c r="H1036">
+        <v>0</v>
+      </c>
+      <c r="J1036">
+        <v>4.5</v>
+      </c>
+      <c r="K1036">
+        <v>0</v>
+      </c>
+      <c r="L1036">
+        <v>0</v>
+      </c>
+      <c r="M1036" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1036" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1036">
+        <v>12</v>
+      </c>
+      <c r="P1036">
+        <v>6</v>
+      </c>
+      <c r="Q1036">
+        <v>1</v>
+      </c>
+      <c r="R1036">
+        <v>0</v>
+      </c>
+      <c r="S1036" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1036" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1037" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1037" t="s">
+        <v>404</v>
+      </c>
+      <c r="C1037">
+        <v>1</v>
+      </c>
+      <c r="D1037">
+        <v>1</v>
+      </c>
+      <c r="E1037">
+        <v>3</v>
+      </c>
+      <c r="F1037">
+        <v>0</v>
+      </c>
+      <c r="G1037">
+        <v>23</v>
+      </c>
+      <c r="H1037">
+        <v>0</v>
+      </c>
+      <c r="J1037">
+        <v>7.67</v>
+      </c>
+      <c r="K1037">
+        <v>0</v>
+      </c>
+      <c r="L1037">
+        <v>0</v>
+      </c>
+      <c r="M1037" t="s">
+        <v>216</v>
+      </c>
+      <c r="N1037" t="s">
+        <v>216</v>
+      </c>
+      <c r="O1037">
+        <v>18</v>
+      </c>
+      <c r="P1037">
+        <v>9</v>
+      </c>
+      <c r="Q1037">
+        <v>1</v>
+      </c>
+      <c r="R1037">
+        <v>0</v>
+      </c>
+      <c r="S1037" t="s">
+        <v>372</v>
+      </c>
+      <c r="T1037" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1038" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1038" t="s">
+        <v>601</v>
+      </c>
+      <c r="C1038">
+        <v>1</v>
+      </c>
+      <c r="D1038">
+        <v>1</v>
+      </c>
+      <c r="E1038">
+        <v>3</v>
+      </c>
+      <c r="F1038">
+        <v>0</v>
+      </c>
+      <c r="G1038">
+        <v>29</v>
+      </c>
+      <c r="H1038">
+        <v>0</v>
+      </c>
+      <c r="J1038">
+        <v>9.67</v>
+      </c>
+      <c r="K1038">
+        <v>0</v>
+      </c>
+      <c r="L1038">
+        <v>0</v>
+      </c>
+      <c r="M1038" t="s">
+        <v>263</v>
+      </c>
+      <c r="N1038" t="s">
+        <v>263</v>
+      </c>
+      <c r="O1038">
+        <v>18</v>
+      </c>
+      <c r="P1038">
+        <v>5</v>
+      </c>
+      <c r="Q1038">
+        <v>4</v>
+      </c>
+      <c r="R1038">
+        <v>0</v>
+      </c>
+      <c r="S1038" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1038" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1039" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1039" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1039">
+        <v>1</v>
+      </c>
+      <c r="D1039">
+        <v>1</v>
+      </c>
+      <c r="E1039">
+        <v>1</v>
+      </c>
+      <c r="F1039">
+        <v>0</v>
+      </c>
+      <c r="G1039">
+        <v>16</v>
+      </c>
+      <c r="H1039">
+        <v>0</v>
+      </c>
+      <c r="J1039">
+        <v>16</v>
+      </c>
+      <c r="K1039">
+        <v>0</v>
+      </c>
+      <c r="L1039">
+        <v>0</v>
+      </c>
+      <c r="M1039" t="s">
+        <v>70</v>
+      </c>
+      <c r="N1039" t="s">
+        <v>70</v>
+      </c>
+      <c r="O1039">
+        <v>6</v>
+      </c>
+      <c r="P1039">
+        <v>1</v>
+      </c>
+      <c r="Q1039">
+        <v>1</v>
+      </c>
+      <c r="R1039">
+        <v>1</v>
+      </c>
+      <c r="S1039" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1039" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1040" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1040" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1040">
+        <v>1</v>
+      </c>
+      <c r="D1040">
+        <v>1</v>
+      </c>
+      <c r="E1040">
+        <v>1</v>
+      </c>
+      <c r="F1040">
+        <v>0</v>
+      </c>
+      <c r="G1040">
+        <v>11</v>
+      </c>
+      <c r="H1040">
+        <v>0</v>
+      </c>
+      <c r="J1040">
+        <v>11</v>
+      </c>
+      <c r="K1040">
+        <v>0</v>
+      </c>
+      <c r="L1040">
+        <v>0</v>
+      </c>
+      <c r="M1040" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1040" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1040">
+        <v>6</v>
+      </c>
+      <c r="P1040">
+        <v>2</v>
+      </c>
+      <c r="Q1040">
+        <v>2</v>
+      </c>
+      <c r="R1040">
+        <v>0</v>
+      </c>
+      <c r="S1040" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1040" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1041" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1041" t="s">
+        <v>358</v>
+      </c>
+      <c r="C1041">
+        <v>1</v>
+      </c>
+      <c r="D1041">
+        <v>1</v>
+      </c>
+      <c r="E1041">
+        <v>1</v>
+      </c>
+      <c r="F1041">
+        <v>0</v>
+      </c>
+      <c r="G1041">
+        <v>10</v>
+      </c>
+      <c r="H1041">
+        <v>0</v>
+      </c>
+      <c r="J1041">
+        <v>10</v>
+      </c>
+      <c r="K1041">
+        <v>0</v>
+      </c>
+      <c r="L1041">
+        <v>0</v>
+      </c>
+      <c r="M1041" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1041" t="s">
+        <v>48</v>
+      </c>
+      <c r="O1041">
+        <v>6</v>
+      </c>
+      <c r="P1041">
+        <v>3</v>
+      </c>
+      <c r="Q1041">
+        <v>1</v>
+      </c>
+      <c r="R1041">
+        <v>0</v>
+      </c>
+      <c r="S1041" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1041" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1042" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1042" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1042">
+        <v>1</v>
+      </c>
+      <c r="D1042">
+        <v>1</v>
+      </c>
+      <c r="E1042">
+        <v>3</v>
+      </c>
+      <c r="F1042">
+        <v>1</v>
+      </c>
+      <c r="G1042">
+        <v>35</v>
+      </c>
+      <c r="H1042">
+        <v>2</v>
+      </c>
+      <c r="I1042">
+        <v>17.5</v>
+      </c>
+      <c r="J1042">
+        <v>11.67</v>
+      </c>
+      <c r="K1042">
+        <v>0</v>
+      </c>
+      <c r="L1042">
+        <v>0</v>
+      </c>
+      <c r="M1042" s="1">
+        <v>12816</v>
+      </c>
+      <c r="N1042" s="1">
+        <v>12816</v>
+      </c>
+      <c r="O1042">
+        <v>18</v>
+      </c>
+      <c r="P1042">
+        <v>9</v>
+      </c>
+      <c r="Q1042">
+        <v>5</v>
+      </c>
+      <c r="R1042">
+        <v>1</v>
+      </c>
+      <c r="S1042" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1042" t="s">
+        <v>129</v>
+      </c>
+      <c r="U1042">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1043" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1043" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1043">
+        <v>1</v>
+      </c>
+      <c r="D1043">
+        <v>1</v>
+      </c>
+      <c r="E1043">
+        <v>4</v>
+      </c>
+      <c r="F1043">
+        <v>0</v>
+      </c>
+      <c r="G1043">
+        <v>30</v>
+      </c>
+      <c r="H1043">
+        <v>3</v>
+      </c>
+      <c r="I1043">
+        <v>10</v>
+      </c>
+      <c r="J1043">
+        <v>7.5</v>
+      </c>
+      <c r="K1043">
+        <v>0</v>
+      </c>
+      <c r="L1043">
+        <v>0</v>
+      </c>
+      <c r="M1043" s="1">
+        <v>11018</v>
+      </c>
+      <c r="N1043" s="1">
+        <v>11018</v>
+      </c>
+      <c r="O1043">
+        <v>24</v>
+      </c>
+      <c r="P1043">
+        <v>11</v>
+      </c>
+      <c r="Q1043">
+        <v>2</v>
+      </c>
+      <c r="R1043">
+        <v>1</v>
+      </c>
+      <c r="S1043" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1043" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1043">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1044" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1044" t="s">
+        <v>602</v>
+      </c>
+      <c r="C1044">
+        <v>1</v>
+      </c>
+      <c r="D1044">
+        <v>1</v>
+      </c>
+      <c r="E1044">
+        <v>4</v>
+      </c>
+      <c r="F1044">
+        <v>0</v>
+      </c>
+      <c r="G1044">
+        <v>32</v>
+      </c>
+      <c r="H1044">
+        <v>2</v>
+      </c>
+      <c r="I1044">
+        <v>16</v>
+      </c>
+      <c r="J1044">
+        <v>8</v>
+      </c>
+      <c r="K1044">
+        <v>0</v>
+      </c>
+      <c r="L1044">
+        <v>0</v>
+      </c>
+      <c r="M1044" s="1">
+        <v>11720</v>
+      </c>
+      <c r="N1044" s="1">
+        <v>11720</v>
+      </c>
+      <c r="O1044">
+        <v>24</v>
+      </c>
+      <c r="P1044">
+        <v>12</v>
+      </c>
+      <c r="Q1044">
+        <v>1</v>
+      </c>
+      <c r="R1044">
+        <v>3</v>
+      </c>
+      <c r="S1044" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1044" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1044">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1045" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1045" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1045">
+        <v>1</v>
+      </c>
+      <c r="D1045">
+        <v>1</v>
+      </c>
+      <c r="E1045">
+        <v>3</v>
+      </c>
+      <c r="F1045">
+        <v>0</v>
+      </c>
+      <c r="G1045">
+        <v>23</v>
+      </c>
+      <c r="H1045">
+        <v>1</v>
+      </c>
+      <c r="I1045">
+        <v>23</v>
+      </c>
+      <c r="J1045">
+        <v>7.67</v>
+      </c>
+      <c r="K1045">
+        <v>0</v>
+      </c>
+      <c r="L1045">
+        <v>0</v>
+      </c>
+      <c r="M1045" s="1">
+        <v>44927</v>
+      </c>
+      <c r="N1045" s="1">
+        <v>44927</v>
+      </c>
+      <c r="O1045">
+        <v>18</v>
+      </c>
+      <c r="P1045">
+        <v>6</v>
+      </c>
+      <c r="Q1045">
+        <v>2</v>
+      </c>
+      <c r="R1045">
+        <v>0</v>
+      </c>
+      <c r="S1045" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1045" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1045">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1046" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1046">
+        <v>1</v>
+      </c>
+      <c r="D1046">
+        <v>1</v>
+      </c>
+      <c r="E1046">
+        <v>3</v>
+      </c>
+      <c r="F1046">
+        <v>0</v>
+      </c>
+      <c r="G1046">
+        <v>20</v>
+      </c>
+      <c r="H1046">
+        <v>1</v>
+      </c>
+      <c r="I1046">
+        <v>20</v>
+      </c>
+      <c r="J1046">
+        <v>6.67</v>
+      </c>
+      <c r="K1046">
+        <v>0</v>
+      </c>
+      <c r="L1046">
+        <v>0</v>
+      </c>
+      <c r="M1046" s="1">
+        <v>43831</v>
+      </c>
+      <c r="N1046" s="1">
+        <v>43831</v>
+      </c>
+      <c r="O1046">
+        <v>18</v>
+      </c>
+      <c r="P1046">
+        <v>6</v>
+      </c>
+      <c r="Q1046">
+        <v>2</v>
+      </c>
+      <c r="R1046">
+        <v>0</v>
+      </c>
+      <c r="S1046" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1046" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1046">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1047" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1047" t="s">
+        <v>471</v>
+      </c>
+      <c r="C1047">
+        <v>1</v>
+      </c>
+      <c r="D1047">
+        <v>1</v>
+      </c>
+      <c r="E1047">
+        <v>3.4</v>
+      </c>
+      <c r="F1047">
+        <v>0</v>
+      </c>
+      <c r="G1047">
+        <v>13</v>
+      </c>
+      <c r="H1047">
+        <v>0</v>
+      </c>
+      <c r="J1047">
+        <v>3.55</v>
+      </c>
+      <c r="K1047">
+        <v>0</v>
+      </c>
+      <c r="L1047">
+        <v>0</v>
+      </c>
+      <c r="M1047" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1047" t="s">
+        <v>50</v>
+      </c>
+      <c r="O1047">
+        <v>22</v>
+      </c>
+      <c r="P1047">
+        <v>13</v>
+      </c>
+      <c r="Q1047">
+        <v>1</v>
+      </c>
+      <c r="R1047">
+        <v>0</v>
+      </c>
+      <c r="S1047" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1047" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1048" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1048" t="s">
+        <v>551</v>
+      </c>
+      <c r="C1048">
+        <v>1</v>
+      </c>
+      <c r="D1048">
+        <v>1</v>
+      </c>
+      <c r="E1048">
+        <v>4</v>
+      </c>
+      <c r="F1048">
+        <v>0</v>
+      </c>
+      <c r="G1048">
+        <v>24</v>
+      </c>
+      <c r="H1048">
+        <v>1</v>
+      </c>
+      <c r="I1048">
+        <v>24</v>
+      </c>
+      <c r="J1048">
+        <v>6</v>
+      </c>
+      <c r="K1048">
+        <v>0</v>
+      </c>
+      <c r="L1048">
+        <v>0</v>
+      </c>
+      <c r="M1048" s="1">
+        <v>45292</v>
+      </c>
+      <c r="N1048" s="1">
+        <v>45292</v>
+      </c>
+      <c r="O1048">
+        <v>24</v>
+      </c>
+      <c r="P1048">
+        <v>13</v>
+      </c>
+      <c r="Q1048">
+        <v>1</v>
+      </c>
+      <c r="R1048">
+        <v>1</v>
+      </c>
+      <c r="S1048" t="s">
+        <v>34</v>
+      </c>
+      <c r="T1048" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1048">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1049" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1049" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1049">
+        <v>1</v>
+      </c>
+      <c r="D1049">
+        <v>1</v>
+      </c>
+      <c r="E1049">
+        <v>3</v>
+      </c>
+      <c r="F1049">
+        <v>0</v>
+      </c>
+      <c r="G1049">
+        <v>25</v>
+      </c>
+      <c r="H1049">
+        <v>0</v>
+      </c>
+      <c r="J1049">
+        <v>8.33</v>
+      </c>
+      <c r="K1049">
+        <v>0</v>
+      </c>
+      <c r="L1049">
+        <v>0</v>
+      </c>
+      <c r="M1049" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1049" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1049">
+        <v>18</v>
+      </c>
+      <c r="P1049">
+        <v>7</v>
+      </c>
+      <c r="Q1049">
+        <v>2</v>
+      </c>
+      <c r="R1049">
+        <v>0</v>
+      </c>
+      <c r="S1049" t="s">
+        <v>155</v>
+      </c>
+      <c r="T1049" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1050" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1050" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1050">
+        <v>1</v>
+      </c>
+      <c r="D1050">
+        <v>1</v>
+      </c>
+      <c r="E1050">
+        <v>4</v>
+      </c>
+      <c r="F1050">
+        <v>0</v>
+      </c>
+      <c r="G1050">
+        <v>35</v>
+      </c>
+      <c r="H1050">
+        <v>1</v>
+      </c>
+      <c r="I1050">
+        <v>35</v>
+      </c>
+      <c r="J1050">
+        <v>8.75</v>
+      </c>
+      <c r="K1050">
+        <v>0</v>
+      </c>
+      <c r="L1050">
+        <v>0</v>
+      </c>
+      <c r="M1050" s="1">
+        <v>12785</v>
+      </c>
+      <c r="N1050" s="1">
+        <v>12785</v>
+      </c>
+      <c r="O1050">
+        <v>24</v>
+      </c>
+      <c r="P1050">
+        <v>8</v>
+      </c>
+      <c r="Q1050">
+        <v>1</v>
+      </c>
+      <c r="R1050">
+        <v>2</v>
+      </c>
+      <c r="S1050" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1050" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1050">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1051" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1051" t="s">
+        <v>604</v>
+      </c>
+      <c r="C1051">
+        <v>1</v>
+      </c>
+      <c r="D1051">
+        <v>1</v>
+      </c>
+      <c r="E1051">
+        <v>4</v>
+      </c>
+      <c r="F1051">
+        <v>0</v>
+      </c>
+      <c r="G1051">
+        <v>43</v>
+      </c>
+      <c r="H1051">
+        <v>2</v>
+      </c>
+      <c r="I1051">
+        <v>21.5</v>
+      </c>
+      <c r="J1051">
+        <v>10.75</v>
+      </c>
+      <c r="K1051">
+        <v>0</v>
+      </c>
+      <c r="L1051">
+        <v>0</v>
+      </c>
+      <c r="M1051" s="1">
+        <v>15738</v>
+      </c>
+      <c r="N1051" s="1">
+        <v>15738</v>
+      </c>
+      <c r="O1051">
+        <v>24</v>
+      </c>
+      <c r="P1051">
+        <v>6</v>
+      </c>
+      <c r="Q1051">
+        <v>2</v>
+      </c>
+      <c r="R1051">
+        <v>3</v>
+      </c>
+      <c r="S1051" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1051" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1051">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1052" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1052" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1052">
+        <v>1</v>
+      </c>
+      <c r="D1052">
+        <v>1</v>
+      </c>
+      <c r="E1052">
+        <v>4</v>
+      </c>
+      <c r="F1052">
+        <v>0</v>
+      </c>
+      <c r="G1052">
+        <v>25</v>
+      </c>
+      <c r="H1052">
+        <v>1</v>
+      </c>
+      <c r="I1052">
+        <v>25</v>
+      </c>
+      <c r="J1052">
+        <v>6.25</v>
+      </c>
+      <c r="K1052">
+        <v>0</v>
+      </c>
+      <c r="L1052">
+        <v>0</v>
+      </c>
+      <c r="M1052" s="1">
+        <v>45658</v>
+      </c>
+      <c r="N1052" s="1">
+        <v>45658</v>
+      </c>
+      <c r="O1052">
+        <v>24</v>
+      </c>
+      <c r="P1052">
+        <v>12</v>
+      </c>
+      <c r="Q1052">
+        <v>2</v>
+      </c>
+      <c r="R1052">
+        <v>1</v>
+      </c>
+      <c r="S1052" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1052" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1052">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1053" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1053" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1053">
+        <v>1</v>
+      </c>
+      <c r="D1053">
+        <v>1</v>
+      </c>
+      <c r="E1053">
+        <v>4</v>
+      </c>
+      <c r="F1053">
+        <v>0</v>
+      </c>
+      <c r="G1053">
+        <v>35</v>
+      </c>
+      <c r="H1053">
+        <v>1</v>
+      </c>
+      <c r="I1053">
+        <v>35</v>
+      </c>
+      <c r="J1053">
+        <v>8.75</v>
+      </c>
+      <c r="K1053">
+        <v>0</v>
+      </c>
+      <c r="L1053">
+        <v>0</v>
+      </c>
+      <c r="M1053" s="1">
+        <v>12785</v>
+      </c>
+      <c r="N1053" s="1">
+        <v>12785</v>
+      </c>
+      <c r="O1053">
+        <v>24</v>
+      </c>
+      <c r="P1053">
+        <v>11</v>
+      </c>
+      <c r="Q1053">
+        <v>2</v>
+      </c>
+      <c r="R1053">
+        <v>2</v>
+      </c>
+      <c r="S1053" t="s">
+        <v>109</v>
+      </c>
+      <c r="T1053" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1053">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1054" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1054" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1054">
+        <v>1</v>
+      </c>
+      <c r="D1054">
+        <v>1</v>
+      </c>
+      <c r="E1054">
+        <v>1</v>
+      </c>
+      <c r="F1054">
+        <v>0</v>
+      </c>
+      <c r="G1054">
+        <v>15</v>
+      </c>
+      <c r="H1054">
+        <v>0</v>
+      </c>
+      <c r="J1054">
+        <v>15</v>
+      </c>
+      <c r="K1054">
+        <v>0</v>
+      </c>
+      <c r="L1054">
+        <v>0</v>
+      </c>
+      <c r="M1054" t="s">
+        <v>145</v>
+      </c>
+      <c r="N1054" t="s">
+        <v>145</v>
+      </c>
+      <c r="O1054">
+        <v>6</v>
+      </c>
+      <c r="P1054">
+        <v>1</v>
+      </c>
+      <c r="Q1054">
+        <v>1</v>
+      </c>
+      <c r="R1054">
+        <v>1</v>
+      </c>
+      <c r="S1054" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1054" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1055" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1055">
+        <v>1</v>
+      </c>
+      <c r="D1055">
+        <v>1</v>
+      </c>
+      <c r="E1055">
+        <v>4</v>
+      </c>
+      <c r="F1055">
+        <v>0</v>
+      </c>
+      <c r="G1055">
+        <v>24</v>
+      </c>
+      <c r="H1055">
+        <v>2</v>
+      </c>
+      <c r="I1055">
+        <v>12</v>
+      </c>
+      <c r="J1055">
+        <v>6</v>
+      </c>
+      <c r="K1055">
+        <v>0</v>
+      </c>
+      <c r="L1055">
+        <v>0</v>
+      </c>
+      <c r="M1055" s="1">
+        <v>45323</v>
+      </c>
+      <c r="N1055" s="1">
+        <v>45323</v>
+      </c>
+      <c r="O1055">
+        <v>24</v>
+      </c>
+      <c r="P1055">
+        <v>15</v>
+      </c>
+      <c r="Q1055">
+        <v>0</v>
+      </c>
+      <c r="R1055">
+        <v>2</v>
+      </c>
+      <c r="S1055" t="s">
+        <v>107</v>
+      </c>
+      <c r="T1055" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1055">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1056" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1056">
+        <v>1</v>
+      </c>
+      <c r="D1056">
+        <v>1</v>
+      </c>
+      <c r="E1056">
+        <v>4</v>
+      </c>
+      <c r="F1056">
+        <v>0</v>
+      </c>
+      <c r="G1056">
+        <v>29</v>
+      </c>
+      <c r="H1056">
+        <v>1</v>
+      </c>
+      <c r="I1056">
+        <v>29</v>
+      </c>
+      <c r="J1056">
+        <v>7.25</v>
+      </c>
+      <c r="K1056">
+        <v>0</v>
+      </c>
+      <c r="L1056">
+        <v>0</v>
+      </c>
+      <c r="M1056" s="1">
+        <v>47119</v>
+      </c>
+      <c r="N1056" s="1">
+        <v>47119</v>
+      </c>
+      <c r="O1056">
+        <v>24</v>
+      </c>
+      <c r="P1056">
+        <v>10</v>
+      </c>
+      <c r="Q1056">
+        <v>2</v>
+      </c>
+      <c r="R1056">
+        <v>1</v>
+      </c>
+      <c r="S1056" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1056" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1056">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1057" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1057">
+        <v>1</v>
+      </c>
+      <c r="D1057">
+        <v>1</v>
+      </c>
+      <c r="E1057">
+        <v>4</v>
+      </c>
+      <c r="F1057">
+        <v>0</v>
+      </c>
+      <c r="G1057">
+        <v>34</v>
+      </c>
+      <c r="H1057">
+        <v>2</v>
+      </c>
+      <c r="I1057">
+        <v>17</v>
+      </c>
+      <c r="J1057">
+        <v>8.5</v>
+      </c>
+      <c r="K1057">
+        <v>0</v>
+      </c>
+      <c r="L1057">
+        <v>0</v>
+      </c>
+      <c r="M1057" s="1">
+        <v>12451</v>
+      </c>
+      <c r="N1057" s="1">
+        <v>12451</v>
+      </c>
+      <c r="O1057">
+        <v>24</v>
+      </c>
+      <c r="P1057">
+        <v>12</v>
+      </c>
+      <c r="Q1057">
+        <v>2</v>
+      </c>
+      <c r="R1057">
+        <v>2</v>
+      </c>
+      <c r="S1057" t="s">
+        <v>85</v>
+      </c>
+      <c r="T1057" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1057">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1058" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1058">
+        <v>1</v>
+      </c>
+      <c r="D1058">
+        <v>1</v>
+      </c>
+      <c r="E1058">
+        <v>4</v>
+      </c>
+      <c r="F1058">
+        <v>0</v>
+      </c>
+      <c r="G1058">
+        <v>32</v>
+      </c>
+      <c r="H1058">
+        <v>0</v>
+      </c>
+      <c r="J1058">
+        <v>8</v>
+      </c>
+      <c r="K1058">
+        <v>0</v>
+      </c>
+      <c r="L1058">
+        <v>0</v>
+      </c>
+      <c r="M1058" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1058" t="s">
+        <v>65</v>
+      </c>
+      <c r="O1058">
+        <v>24</v>
+      </c>
+      <c r="P1058">
+        <v>12</v>
+      </c>
+      <c r="Q1058">
+        <v>2</v>
+      </c>
+      <c r="R1058">
+        <v>2</v>
+      </c>
+      <c r="S1058" t="s">
+        <v>38</v>
+      </c>
+      <c r="T1058" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1059" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1059">
+        <v>1</v>
+      </c>
+      <c r="D1059">
+        <v>1</v>
+      </c>
+      <c r="E1059">
+        <v>4</v>
+      </c>
+      <c r="F1059">
+        <v>0</v>
+      </c>
+      <c r="G1059">
+        <v>17</v>
+      </c>
+      <c r="H1059">
+        <v>1</v>
+      </c>
+      <c r="I1059">
+        <v>17</v>
+      </c>
+      <c r="J1059">
+        <v>4.25</v>
+      </c>
+      <c r="K1059">
+        <v>0</v>
+      </c>
+      <c r="L1059">
+        <v>0</v>
+      </c>
+      <c r="M1059" s="1">
+        <v>42736</v>
+      </c>
+      <c r="N1059" s="1">
+        <v>42736</v>
+      </c>
+      <c r="O1059">
+        <v>24</v>
+      </c>
+      <c r="P1059">
+        <v>15</v>
+      </c>
+      <c r="Q1059">
+        <v>2</v>
+      </c>
+      <c r="R1059">
+        <v>0</v>
+      </c>
+      <c r="S1059" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1059" t="s">
+        <v>31</v>
+      </c>
+      <c r="U1059">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Midweek League bowling stats for season.xlsx
+++ b/NV Play Midweek League bowling stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5149" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5207" uniqueCount="608">
   <si>
     <t>Group</t>
   </si>
@@ -1835,6 +1835,15 @@
   <si>
     <t>Bradley Hodge</t>
   </si>
+  <si>
+    <t>Arches MW XI v Dunmurry MW2 XI, City of Belfast Playing Fields (Dunmurry) - 6 August 2026</t>
+  </si>
+  <si>
+    <t>0-47</t>
+  </si>
+  <si>
+    <t>Purvik Prasad</t>
+  </si>
 </sst>
 </file>
 
@@ -2642,7 +2651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U1059"/>
+  <dimension ref="A1:U1071"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="69.28515625" bestFit="1" customWidth="1"/>
@@ -68719,6 +68728,756 @@
         <v>24</v>
       </c>
     </row>
+    <row r="1060" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1060" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1060">
+        <v>1</v>
+      </c>
+      <c r="D1060">
+        <v>1</v>
+      </c>
+      <c r="E1060">
+        <v>2</v>
+      </c>
+      <c r="F1060">
+        <v>0</v>
+      </c>
+      <c r="G1060">
+        <v>17</v>
+      </c>
+      <c r="H1060">
+        <v>1</v>
+      </c>
+      <c r="I1060">
+        <v>17</v>
+      </c>
+      <c r="J1060">
+        <v>8.5</v>
+      </c>
+      <c r="K1060">
+        <v>0</v>
+      </c>
+      <c r="L1060">
+        <v>0</v>
+      </c>
+      <c r="M1060" s="1">
+        <v>42736</v>
+      </c>
+      <c r="N1060" s="1">
+        <v>42736</v>
+      </c>
+      <c r="O1060">
+        <v>12</v>
+      </c>
+      <c r="P1060">
+        <v>6</v>
+      </c>
+      <c r="Q1060">
+        <v>2</v>
+      </c>
+      <c r="R1060">
+        <v>1</v>
+      </c>
+      <c r="S1060" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1060" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1060">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1061" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1061">
+        <v>1</v>
+      </c>
+      <c r="D1061">
+        <v>1</v>
+      </c>
+      <c r="E1061">
+        <v>3</v>
+      </c>
+      <c r="F1061">
+        <v>0</v>
+      </c>
+      <c r="G1061">
+        <v>27</v>
+      </c>
+      <c r="H1061">
+        <v>1</v>
+      </c>
+      <c r="I1061">
+        <v>27</v>
+      </c>
+      <c r="J1061">
+        <v>9</v>
+      </c>
+      <c r="K1061">
+        <v>0</v>
+      </c>
+      <c r="L1061">
+        <v>0</v>
+      </c>
+      <c r="M1061" s="1">
+        <v>46388</v>
+      </c>
+      <c r="N1061" s="1">
+        <v>46388</v>
+      </c>
+      <c r="O1061">
+        <v>18</v>
+      </c>
+      <c r="P1061">
+        <v>8</v>
+      </c>
+      <c r="Q1061">
+        <v>3</v>
+      </c>
+      <c r="R1061">
+        <v>0</v>
+      </c>
+      <c r="S1061" t="s">
+        <v>155</v>
+      </c>
+      <c r="T1061" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1061">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1062" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1062" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1062">
+        <v>1</v>
+      </c>
+      <c r="D1062">
+        <v>1</v>
+      </c>
+      <c r="E1062">
+        <v>2</v>
+      </c>
+      <c r="F1062">
+        <v>0</v>
+      </c>
+      <c r="G1062">
+        <v>26</v>
+      </c>
+      <c r="H1062">
+        <v>0</v>
+      </c>
+      <c r="J1062">
+        <v>13</v>
+      </c>
+      <c r="K1062">
+        <v>0</v>
+      </c>
+      <c r="L1062">
+        <v>0</v>
+      </c>
+      <c r="M1062" t="s">
+        <v>90</v>
+      </c>
+      <c r="N1062" t="s">
+        <v>90</v>
+      </c>
+      <c r="O1062">
+        <v>12</v>
+      </c>
+      <c r="P1062">
+        <v>3</v>
+      </c>
+      <c r="Q1062">
+        <v>1</v>
+      </c>
+      <c r="R1062">
+        <v>2</v>
+      </c>
+      <c r="S1062" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1062" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1063" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1063" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1063">
+        <v>1</v>
+      </c>
+      <c r="D1063">
+        <v>1</v>
+      </c>
+      <c r="E1063">
+        <v>1.5</v>
+      </c>
+      <c r="F1063">
+        <v>0</v>
+      </c>
+      <c r="G1063">
+        <v>19</v>
+      </c>
+      <c r="H1063">
+        <v>2</v>
+      </c>
+      <c r="I1063">
+        <v>9.5</v>
+      </c>
+      <c r="J1063">
+        <v>10.36</v>
+      </c>
+      <c r="K1063">
+        <v>0</v>
+      </c>
+      <c r="L1063">
+        <v>0</v>
+      </c>
+      <c r="M1063" s="1">
+        <v>43497</v>
+      </c>
+      <c r="N1063" s="1">
+        <v>43497</v>
+      </c>
+      <c r="O1063">
+        <v>11</v>
+      </c>
+      <c r="P1063">
+        <v>6</v>
+      </c>
+      <c r="Q1063">
+        <v>1</v>
+      </c>
+      <c r="R1063">
+        <v>2</v>
+      </c>
+      <c r="S1063" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1063" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1063">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1064" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1064" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1064">
+        <v>1</v>
+      </c>
+      <c r="D1064">
+        <v>1</v>
+      </c>
+      <c r="E1064">
+        <v>4</v>
+      </c>
+      <c r="F1064">
+        <v>0</v>
+      </c>
+      <c r="G1064">
+        <v>47</v>
+      </c>
+      <c r="H1064">
+        <v>0</v>
+      </c>
+      <c r="J1064">
+        <v>11.75</v>
+      </c>
+      <c r="K1064">
+        <v>0</v>
+      </c>
+      <c r="L1064">
+        <v>0</v>
+      </c>
+      <c r="M1064" t="s">
+        <v>606</v>
+      </c>
+      <c r="N1064" t="s">
+        <v>606</v>
+      </c>
+      <c r="O1064">
+        <v>24</v>
+      </c>
+      <c r="P1064">
+        <v>3</v>
+      </c>
+      <c r="Q1064">
+        <v>5</v>
+      </c>
+      <c r="R1064">
+        <v>1</v>
+      </c>
+      <c r="S1064" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1064" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1065" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1065" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1065">
+        <v>1</v>
+      </c>
+      <c r="D1065">
+        <v>1</v>
+      </c>
+      <c r="E1065">
+        <v>1</v>
+      </c>
+      <c r="F1065">
+        <v>0</v>
+      </c>
+      <c r="G1065">
+        <v>17</v>
+      </c>
+      <c r="H1065">
+        <v>0</v>
+      </c>
+      <c r="J1065">
+        <v>17</v>
+      </c>
+      <c r="K1065">
+        <v>0</v>
+      </c>
+      <c r="L1065">
+        <v>0</v>
+      </c>
+      <c r="M1065" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1065" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1065">
+        <v>6</v>
+      </c>
+      <c r="P1065">
+        <v>2</v>
+      </c>
+      <c r="Q1065">
+        <v>1</v>
+      </c>
+      <c r="R1065">
+        <v>2</v>
+      </c>
+      <c r="S1065" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1065" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1066" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1066" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1066">
+        <v>1</v>
+      </c>
+      <c r="D1066">
+        <v>1</v>
+      </c>
+      <c r="E1066">
+        <v>3</v>
+      </c>
+      <c r="F1066">
+        <v>0</v>
+      </c>
+      <c r="G1066">
+        <v>12</v>
+      </c>
+      <c r="H1066">
+        <v>2</v>
+      </c>
+      <c r="I1066">
+        <v>6</v>
+      </c>
+      <c r="J1066">
+        <v>4</v>
+      </c>
+      <c r="K1066">
+        <v>0</v>
+      </c>
+      <c r="L1066">
+        <v>0</v>
+      </c>
+      <c r="M1066" s="2">
+        <v>46358</v>
+      </c>
+      <c r="N1066" s="2">
+        <v>46358</v>
+      </c>
+      <c r="O1066">
+        <v>18</v>
+      </c>
+      <c r="P1066">
+        <v>12</v>
+      </c>
+      <c r="Q1066">
+        <v>1</v>
+      </c>
+      <c r="R1066">
+        <v>0</v>
+      </c>
+      <c r="S1066" t="s">
+        <v>31</v>
+      </c>
+      <c r="T1066" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1066">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1067" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1067" t="s">
+        <v>607</v>
+      </c>
+      <c r="C1067">
+        <v>1</v>
+      </c>
+      <c r="D1067">
+        <v>1</v>
+      </c>
+      <c r="E1067">
+        <v>3</v>
+      </c>
+      <c r="F1067">
+        <v>0</v>
+      </c>
+      <c r="G1067">
+        <v>31</v>
+      </c>
+      <c r="H1067">
+        <v>0</v>
+      </c>
+      <c r="J1067">
+        <v>10.33</v>
+      </c>
+      <c r="K1067">
+        <v>0</v>
+      </c>
+      <c r="L1067">
+        <v>0</v>
+      </c>
+      <c r="M1067" t="s">
+        <v>283</v>
+      </c>
+      <c r="N1067" t="s">
+        <v>283</v>
+      </c>
+      <c r="O1067">
+        <v>18</v>
+      </c>
+      <c r="P1067">
+        <v>4</v>
+      </c>
+      <c r="Q1067">
+        <v>3</v>
+      </c>
+      <c r="R1067">
+        <v>1</v>
+      </c>
+      <c r="S1067" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1067" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1068" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1068" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1068">
+        <v>1</v>
+      </c>
+      <c r="D1068">
+        <v>1</v>
+      </c>
+      <c r="E1068">
+        <v>4</v>
+      </c>
+      <c r="F1068">
+        <v>3</v>
+      </c>
+      <c r="G1068">
+        <v>3</v>
+      </c>
+      <c r="H1068">
+        <v>1</v>
+      </c>
+      <c r="I1068">
+        <v>3</v>
+      </c>
+      <c r="J1068">
+        <v>0.75</v>
+      </c>
+      <c r="K1068">
+        <v>0</v>
+      </c>
+      <c r="L1068">
+        <v>0</v>
+      </c>
+      <c r="M1068" s="2">
+        <v>46082</v>
+      </c>
+      <c r="N1068" s="2">
+        <v>46082</v>
+      </c>
+      <c r="O1068">
+        <v>24</v>
+      </c>
+      <c r="P1068">
+        <v>21</v>
+      </c>
+      <c r="Q1068">
+        <v>0</v>
+      </c>
+      <c r="R1068">
+        <v>0</v>
+      </c>
+      <c r="S1068" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1068" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1068">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1069" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1069" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1069">
+        <v>1</v>
+      </c>
+      <c r="D1069">
+        <v>1</v>
+      </c>
+      <c r="E1069">
+        <v>4</v>
+      </c>
+      <c r="F1069">
+        <v>0</v>
+      </c>
+      <c r="G1069">
+        <v>25</v>
+      </c>
+      <c r="H1069">
+        <v>1</v>
+      </c>
+      <c r="I1069">
+        <v>25</v>
+      </c>
+      <c r="J1069">
+        <v>6.25</v>
+      </c>
+      <c r="K1069">
+        <v>0</v>
+      </c>
+      <c r="L1069">
+        <v>0</v>
+      </c>
+      <c r="M1069" s="1">
+        <v>45658</v>
+      </c>
+      <c r="N1069" s="1">
+        <v>45658</v>
+      </c>
+      <c r="O1069">
+        <v>24</v>
+      </c>
+      <c r="P1069">
+        <v>12</v>
+      </c>
+      <c r="Q1069">
+        <v>2</v>
+      </c>
+      <c r="R1069">
+        <v>0</v>
+      </c>
+      <c r="S1069" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1069" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1069">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1070" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1070" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1070">
+        <v>1</v>
+      </c>
+      <c r="D1070">
+        <v>1</v>
+      </c>
+      <c r="E1070">
+        <v>4</v>
+      </c>
+      <c r="F1070">
+        <v>0</v>
+      </c>
+      <c r="G1070">
+        <v>33</v>
+      </c>
+      <c r="H1070">
+        <v>0</v>
+      </c>
+      <c r="J1070">
+        <v>8.25</v>
+      </c>
+      <c r="K1070">
+        <v>0</v>
+      </c>
+      <c r="L1070">
+        <v>0</v>
+      </c>
+      <c r="M1070" t="s">
+        <v>297</v>
+      </c>
+      <c r="N1070" t="s">
+        <v>297</v>
+      </c>
+      <c r="O1070">
+        <v>24</v>
+      </c>
+      <c r="P1070">
+        <v>12</v>
+      </c>
+      <c r="Q1070">
+        <v>4</v>
+      </c>
+      <c r="R1070">
+        <v>1</v>
+      </c>
+      <c r="S1070" t="s">
+        <v>29</v>
+      </c>
+      <c r="T1070" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1071" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1071" t="s">
+        <v>551</v>
+      </c>
+      <c r="C1071">
+        <v>1</v>
+      </c>
+      <c r="D1071">
+        <v>1</v>
+      </c>
+      <c r="E1071">
+        <v>4</v>
+      </c>
+      <c r="F1071">
+        <v>0</v>
+      </c>
+      <c r="G1071">
+        <v>19</v>
+      </c>
+      <c r="H1071">
+        <v>2</v>
+      </c>
+      <c r="I1071">
+        <v>9.5</v>
+      </c>
+      <c r="J1071">
+        <v>4.75</v>
+      </c>
+      <c r="K1071">
+        <v>0</v>
+      </c>
+      <c r="L1071">
+        <v>0</v>
+      </c>
+      <c r="M1071" s="1">
+        <v>43497</v>
+      </c>
+      <c r="N1071" s="1">
+        <v>43497</v>
+      </c>
+      <c r="O1071">
+        <v>24</v>
+      </c>
+      <c r="P1071">
+        <v>12</v>
+      </c>
+      <c r="Q1071">
+        <v>1</v>
+      </c>
+      <c r="R1071">
+        <v>0</v>
+      </c>
+      <c r="S1071" t="s">
+        <v>109</v>
+      </c>
+      <c r="T1071" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1071">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Midweek League bowling stats for season.xlsx
+++ b/NV Play Midweek League bowling stats for season.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\-Midweek League-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03D3655-06A8-4E92-8B3F-51568E2FA94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634BB9A6-0CA8-4BCB-95AA-1FA8AB2D9191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="1725" windowWidth="30255" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20260529-000142-bowling-stats-g" sheetId="1" r:id="rId1"/>
@@ -1289,9 +1289,6 @@
     <t>Shah Ata</t>
   </si>
   <si>
-    <t>Alec Stuart</t>
-  </si>
-  <si>
     <t>Aaditya Sundaram</t>
   </si>
   <si>
@@ -1854,6 +1851,9 @@
   </si>
   <si>
     <t>Purvik Prasad</t>
+  </si>
+  <si>
+    <t>Alex Stuart</t>
   </si>
 </sst>
 </file>
@@ -3195,7 +3195,7 @@
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -3520,7 +3520,7 @@
         <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -4341,7 +4341,7 @@
         <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -5091,7 +5091,7 @@
         <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -5404,7 +5404,7 @@
         <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -6219,7 +6219,7 @@
         <v>101</v>
       </c>
       <c r="B57" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -6284,7 +6284,7 @@
         <v>101</v>
       </c>
       <c r="B58" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -7170,7 +7170,7 @@
         <v>141</v>
       </c>
       <c r="B72" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -7365,7 +7365,7 @@
         <v>141</v>
       </c>
       <c r="B75" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -7873,7 +7873,7 @@
         <v>141</v>
       </c>
       <c r="B83" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -7991,7 +7991,7 @@
         <v>127</v>
       </c>
       <c r="B85" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -8298,7 +8298,7 @@
         <v>127</v>
       </c>
       <c r="B90" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -9089,7 +9089,7 @@
         <v>157</v>
       </c>
       <c r="B103" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -9573,7 +9573,7 @@
         <v>157</v>
       </c>
       <c r="B111" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -10683,7 +10683,7 @@
         <v>191</v>
       </c>
       <c r="B129" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -10813,7 +10813,7 @@
         <v>191</v>
       </c>
       <c r="B131" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -10878,7 +10878,7 @@
         <v>191</v>
       </c>
       <c r="B132" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -11002,7 +11002,7 @@
         <v>191</v>
       </c>
       <c r="B134" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -11120,7 +11120,7 @@
         <v>191</v>
       </c>
       <c r="B136" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -12295,7 +12295,7 @@
         <v>217</v>
       </c>
       <c r="B155" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -12360,7 +12360,7 @@
         <v>217</v>
       </c>
       <c r="B156" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -12614,7 +12614,7 @@
         <v>217</v>
       </c>
       <c r="B160" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -12803,7 +12803,7 @@
         <v>217</v>
       </c>
       <c r="B163" t="s">
-        <v>418</v>
+        <v>606</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -12868,7 +12868,7 @@
         <v>217</v>
       </c>
       <c r="B164" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -12986,7 +12986,7 @@
         <v>217</v>
       </c>
       <c r="B166" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -13051,7 +13051,7 @@
         <v>217</v>
       </c>
       <c r="B167" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -13110,7 +13110,7 @@
         <v>218</v>
       </c>
       <c r="B168" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -14374,7 +14374,7 @@
         <v>228</v>
       </c>
       <c r="B188" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -15189,7 +15189,7 @@
         <v>236</v>
       </c>
       <c r="B201" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -15254,7 +15254,7 @@
         <v>236</v>
       </c>
       <c r="B202" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -16196,7 +16196,7 @@
     </row>
     <row r="217" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B217" t="s">
         <v>253</v>
@@ -16261,10 +16261,10 @@
     </row>
     <row r="218" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B218" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -16320,10 +16320,10 @@
     </row>
     <row r="219" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B219" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -16379,7 +16379,7 @@
     </row>
     <row r="220" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B220" t="s">
         <v>150</v>
@@ -16438,7 +16438,7 @@
     </row>
     <row r="221" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B221" t="s">
         <v>255</v>
@@ -16503,7 +16503,7 @@
     </row>
     <row r="222" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B222" t="s">
         <v>152</v>
@@ -16562,7 +16562,7 @@
     </row>
     <row r="223" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B223" t="s">
         <v>256</v>
@@ -16627,7 +16627,7 @@
     </row>
     <row r="224" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B224" t="s">
         <v>257</v>
@@ -16692,7 +16692,7 @@
     </row>
     <row r="225" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B225" t="s">
         <v>258</v>
@@ -16751,7 +16751,7 @@
     </row>
     <row r="226" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B226" t="s">
         <v>259</v>
@@ -16816,7 +16816,7 @@
     </row>
     <row r="227" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B227" t="s">
         <v>260</v>
@@ -16881,7 +16881,7 @@
     </row>
     <row r="228" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B228" t="s">
         <v>156</v>
@@ -16946,7 +16946,7 @@
     </row>
     <row r="229" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B229" t="s">
         <v>261</v>
@@ -17504,7 +17504,7 @@
         <v>262</v>
       </c>
       <c r="B238" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -17823,7 +17823,7 @@
         <v>268</v>
       </c>
       <c r="B243" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -18585,7 +18585,7 @@
         <v>274</v>
       </c>
       <c r="B255" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -19524,7 +19524,7 @@
         <v>280</v>
       </c>
       <c r="B270" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -19589,7 +19589,7 @@
         <v>280</v>
       </c>
       <c r="B271" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -19831,7 +19831,7 @@
         <v>280</v>
       </c>
       <c r="B275" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -19955,7 +19955,7 @@
         <v>280</v>
       </c>
       <c r="B277" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -20014,7 +20014,7 @@
         <v>280</v>
       </c>
       <c r="B278" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -20073,7 +20073,7 @@
         <v>280</v>
       </c>
       <c r="B279" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -20451,7 +20451,7 @@
         <v>290</v>
       </c>
       <c r="B285" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -20575,7 +20575,7 @@
         <v>290</v>
       </c>
       <c r="B287" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -20758,7 +20758,7 @@
         <v>290</v>
       </c>
       <c r="B290" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -20817,7 +20817,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -20882,7 +20882,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -20947,7 +20947,7 @@
         <v>290</v>
       </c>
       <c r="B293" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -21006,7 +21006,7 @@
         <v>295</v>
       </c>
       <c r="B294" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -22175,7 +22175,7 @@
         <v>305</v>
       </c>
       <c r="B313" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -22423,7 +22423,7 @@
         <v>305</v>
       </c>
       <c r="B317" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -22541,7 +22541,7 @@
         <v>305</v>
       </c>
       <c r="B319" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -22662,7 +22662,7 @@
     </row>
     <row r="321" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B321" t="s">
         <v>253</v>
@@ -22721,7 +22721,7 @@
     </row>
     <row r="322" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B322" t="s">
         <v>311</v>
@@ -22786,10 +22786,10 @@
     </row>
     <row r="323" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B323" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -22851,7 +22851,7 @@
     </row>
     <row r="324" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B324" t="s">
         <v>312</v>
@@ -22916,10 +22916,10 @@
     </row>
     <row r="325" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B325" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -22981,10 +22981,10 @@
     </row>
     <row r="326" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B326" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -23046,7 +23046,7 @@
     </row>
     <row r="327" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B327" t="s">
         <v>313</v>
@@ -23105,10 +23105,10 @@
     </row>
     <row r="328" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B328" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -23164,7 +23164,7 @@
     </row>
     <row r="329" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B329" t="s">
         <v>314</v>
@@ -23229,7 +23229,7 @@
     </row>
     <row r="330" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B330" t="s">
         <v>256</v>
@@ -23294,7 +23294,7 @@
     </row>
     <row r="331" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B331" t="s">
         <v>257</v>
@@ -23353,10 +23353,10 @@
     </row>
     <row r="332" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B332" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -23412,7 +23412,7 @@
     </row>
     <row r="333" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B333" t="s">
         <v>316</v>
@@ -23471,7 +23471,7 @@
     </row>
     <row r="334" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B334" t="s">
         <v>317</v>
@@ -23536,7 +23536,7 @@
     </row>
     <row r="335" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B335" t="s">
         <v>318</v>
@@ -23595,7 +23595,7 @@
     </row>
     <row r="336" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B336" t="s">
         <v>289</v>
@@ -24206,7 +24206,7 @@
         <v>319</v>
       </c>
       <c r="B346" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -24572,7 +24572,7 @@
         <v>326</v>
       </c>
       <c r="B352" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -24755,7 +24755,7 @@
         <v>326</v>
       </c>
       <c r="B355" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C355">
         <v>1</v>
@@ -25499,7 +25499,7 @@
         <v>334</v>
       </c>
       <c r="B367" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C367">
         <v>1</v>
@@ -26184,7 +26184,7 @@
         <v>338</v>
       </c>
       <c r="B378" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C378">
         <v>1</v>
@@ -26497,7 +26497,7 @@
         <v>338</v>
       </c>
       <c r="B383" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C383">
         <v>1</v>
@@ -26692,7 +26692,7 @@
         <v>338</v>
       </c>
       <c r="B386" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C386">
         <v>1</v>
@@ -26757,7 +26757,7 @@
         <v>338</v>
       </c>
       <c r="B387" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C387">
         <v>1</v>
@@ -27749,7 +27749,7 @@
         <v>346</v>
       </c>
       <c r="B403" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C403">
         <v>1</v>
@@ -29090,7 +29090,7 @@
         <v>360</v>
       </c>
       <c r="B424" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C424">
         <v>1</v>
@@ -29409,7 +29409,7 @@
         <v>360</v>
       </c>
       <c r="B429" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C429">
         <v>1</v>
@@ -29474,7 +29474,7 @@
         <v>360</v>
       </c>
       <c r="B430" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C430">
         <v>1</v>
@@ -29846,7 +29846,7 @@
         <v>360</v>
       </c>
       <c r="B436" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C436">
         <v>1</v>
@@ -29970,7 +29970,7 @@
         <v>366</v>
       </c>
       <c r="B438" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C438">
         <v>1</v>
@@ -30705,10 +30705,10 @@
     </row>
     <row r="450" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
+        <v>495</v>
+      </c>
+      <c r="B450" t="s">
         <v>496</v>
-      </c>
-      <c r="B450" t="s">
-        <v>497</v>
       </c>
       <c r="C450">
         <v>1</v>
@@ -30770,7 +30770,7 @@
     </row>
     <row r="451" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B451" t="s">
         <v>413</v>
@@ -30829,7 +30829,7 @@
     </row>
     <row r="452" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B452" t="s">
         <v>180</v>
@@ -30888,7 +30888,7 @@
     </row>
     <row r="453" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B453" t="s">
         <v>164</v>
@@ -30953,7 +30953,7 @@
     </row>
     <row r="454" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B454" t="s">
         <v>308</v>
@@ -31018,7 +31018,7 @@
     </row>
     <row r="455" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B455" t="s">
         <v>240</v>
@@ -31083,7 +31083,7 @@
     </row>
     <row r="456" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B456" t="s">
         <v>415</v>
@@ -31142,7 +31142,7 @@
     </row>
     <row r="457" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B457" t="s">
         <v>184</v>
@@ -31207,10 +31207,10 @@
     </row>
     <row r="458" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B458" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C458">
         <v>1</v>
@@ -31266,7 +31266,7 @@
     </row>
     <row r="459" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B459" t="s">
         <v>185</v>
@@ -31325,10 +31325,10 @@
     </row>
     <row r="460" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B460" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C460">
         <v>1</v>
@@ -31384,7 +31384,7 @@
     </row>
     <row r="461" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B461" t="s">
         <v>266</v>
@@ -31443,10 +31443,10 @@
     </row>
     <row r="462" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B462" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C462">
         <v>1</v>
@@ -31576,7 +31576,7 @@
         <v>372</v>
       </c>
       <c r="B464" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C464">
         <v>1</v>
@@ -31700,7 +31700,7 @@
         <v>372</v>
       </c>
       <c r="B466" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C466">
         <v>1</v>
@@ -33194,7 +33194,7 @@
         <v>375</v>
       </c>
       <c r="B490" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C490">
         <v>1</v>
@@ -33962,7 +33962,7 @@
         <v>382</v>
       </c>
       <c r="B502" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C502">
         <v>1</v>
@@ -34086,7 +34086,7 @@
         <v>382</v>
       </c>
       <c r="B504" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C504">
         <v>1</v>
@@ -34346,7 +34346,7 @@
         <v>390</v>
       </c>
       <c r="B508" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C508">
         <v>1</v>
@@ -34777,7 +34777,7 @@
         <v>390</v>
       </c>
       <c r="B515" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C515">
         <v>1</v>
@@ -34901,7 +34901,7 @@
         <v>390</v>
       </c>
       <c r="B517" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C517">
         <v>1</v>
@@ -35787,7 +35787,7 @@
         <v>402</v>
       </c>
       <c r="B531" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C531">
         <v>1</v>
@@ -35911,7 +35911,7 @@
         <v>402</v>
       </c>
       <c r="B533" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C533">
         <v>1</v>
@@ -36159,7 +36159,7 @@
         <v>402</v>
       </c>
       <c r="B537" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C537">
         <v>1</v>
@@ -36224,7 +36224,7 @@
         <v>402</v>
       </c>
       <c r="B538" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C538">
         <v>1</v>
@@ -36472,7 +36472,7 @@
         <v>404</v>
       </c>
       <c r="B542" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C542">
         <v>1</v>
@@ -36732,7 +36732,7 @@
         <v>404</v>
       </c>
       <c r="B546" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C546">
         <v>1</v>
@@ -37110,7 +37110,7 @@
         <v>404</v>
       </c>
       <c r="B552" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C552">
         <v>1</v>
@@ -37748,7 +37748,7 @@
         <v>408</v>
       </c>
       <c r="B562" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C562">
         <v>1</v>
@@ -37872,7 +37872,7 @@
         <v>408</v>
       </c>
       <c r="B564" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C564">
         <v>1</v>
@@ -38486,7 +38486,7 @@
         <v>411</v>
       </c>
       <c r="B574" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C574">
         <v>1</v>
@@ -38551,7 +38551,7 @@
         <v>411</v>
       </c>
       <c r="B575" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C575">
         <v>1</v>
@@ -38681,7 +38681,7 @@
         <v>411</v>
       </c>
       <c r="B577" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C577">
         <v>1</v>
@@ -39224,7 +39224,7 @@
         <v>412</v>
       </c>
       <c r="B586" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C586">
         <v>1</v>
@@ -39587,7 +39587,7 @@
     </row>
     <row r="592" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B592" t="s">
         <v>202</v>
@@ -39652,7 +39652,7 @@
     </row>
     <row r="593" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B593" t="s">
         <v>230</v>
@@ -39711,7 +39711,7 @@
     </row>
     <row r="594" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B594" t="s">
         <v>204</v>
@@ -39770,7 +39770,7 @@
     </row>
     <row r="595" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B595" t="s">
         <v>301</v>
@@ -39835,10 +39835,10 @@
     </row>
     <row r="596" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
+        <v>462</v>
+      </c>
+      <c r="B596" t="s">
         <v>463</v>
-      </c>
-      <c r="B596" t="s">
-        <v>464</v>
       </c>
       <c r="C596">
         <v>1</v>
@@ -39894,7 +39894,7 @@
     </row>
     <row r="597" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B597" t="s">
         <v>208</v>
@@ -39959,7 +39959,7 @@
     </row>
     <row r="598" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B598" t="s">
         <v>368</v>
@@ -40018,7 +40018,7 @@
     </row>
     <row r="599" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B599" t="s">
         <v>212</v>
@@ -40083,7 +40083,7 @@
     </row>
     <row r="600" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B600" t="s">
         <v>215</v>
@@ -40142,10 +40142,10 @@
     </row>
     <row r="601" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B601" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C601">
         <v>1</v>
@@ -40201,7 +40201,7 @@
     </row>
     <row r="602" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B602" t="s">
         <v>80</v>
@@ -40266,10 +40266,10 @@
     </row>
     <row r="603" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B603" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C603">
         <v>1</v>
@@ -40331,7 +40331,7 @@
     </row>
     <row r="604" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B604" t="s">
         <v>235</v>
@@ -40390,7 +40390,7 @@
     </row>
     <row r="605" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B605" t="s">
         <v>45</v>
@@ -40449,10 +40449,10 @@
     </row>
     <row r="606" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B606" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C606">
         <v>1</v>
@@ -40508,7 +40508,7 @@
     </row>
     <row r="607" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B607" t="s">
         <v>291</v>
@@ -40573,7 +40573,7 @@
     </row>
     <row r="608" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B608" t="s">
         <v>246</v>
@@ -40638,10 +40638,10 @@
     </row>
     <row r="609" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B609" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C609">
         <v>1</v>
@@ -40697,10 +40697,10 @@
     </row>
     <row r="610" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
+        <v>466</v>
+      </c>
+      <c r="B610" t="s">
         <v>467</v>
-      </c>
-      <c r="B610" t="s">
-        <v>468</v>
       </c>
       <c r="C610">
         <v>1</v>
@@ -40762,10 +40762,10 @@
     </row>
     <row r="611" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B611" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C611">
         <v>1</v>
@@ -40821,7 +40821,7 @@
     </row>
     <row r="612" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B612" t="s">
         <v>294</v>
@@ -40886,7 +40886,7 @@
     </row>
     <row r="613" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B613" t="s">
         <v>60</v>
@@ -40951,10 +40951,10 @@
     </row>
     <row r="614" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B614" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C614">
         <v>1</v>
@@ -41010,10 +41010,10 @@
     </row>
     <row r="615" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B615" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C615">
         <v>1</v>
@@ -41069,7 +41069,7 @@
     </row>
     <row r="616" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B616" t="s">
         <v>394</v>
@@ -41134,10 +41134,10 @@
     </row>
     <row r="617" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B617" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C617">
         <v>1</v>
@@ -41199,7 +41199,7 @@
     </row>
     <row r="618" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B618" t="s">
         <v>22</v>
@@ -41258,7 +41258,7 @@
     </row>
     <row r="619" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B619" t="s">
         <v>201</v>
@@ -41323,7 +41323,7 @@
     </row>
     <row r="620" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B620" t="s">
         <v>87</v>
@@ -41382,7 +41382,7 @@
     </row>
     <row r="621" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B621" t="s">
         <v>347</v>
@@ -41447,7 +41447,7 @@
     </row>
     <row r="622" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B622" t="s">
         <v>407</v>
@@ -41506,10 +41506,10 @@
     </row>
     <row r="623" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
+        <v>470</v>
+      </c>
+      <c r="B623" t="s">
         <v>471</v>
-      </c>
-      <c r="B623" t="s">
-        <v>472</v>
       </c>
       <c r="C623">
         <v>1</v>
@@ -41565,10 +41565,10 @@
     </row>
     <row r="624" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B624" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C624">
         <v>1</v>
@@ -41630,10 +41630,10 @@
     </row>
     <row r="625" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B625" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C625">
         <v>1</v>
@@ -41695,7 +41695,7 @@
     </row>
     <row r="626" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B626" t="s">
         <v>399</v>
@@ -41760,7 +41760,7 @@
     </row>
     <row r="627" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B627" t="s">
         <v>401</v>
@@ -41819,10 +41819,10 @@
     </row>
     <row r="628" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B628" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C628">
         <v>1</v>
@@ -41884,7 +41884,7 @@
     </row>
     <row r="629" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B629" t="s">
         <v>125</v>
@@ -41949,7 +41949,7 @@
     </row>
     <row r="630" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B630" t="s">
         <v>41</v>
@@ -42014,10 +42014,10 @@
     </row>
     <row r="631" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B631" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C631">
         <v>1</v>
@@ -42073,7 +42073,7 @@
     </row>
     <row r="632" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B632" t="s">
         <v>27</v>
@@ -42132,7 +42132,7 @@
     </row>
     <row r="633" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B633" t="s">
         <v>342</v>
@@ -42191,7 +42191,7 @@
     </row>
     <row r="634" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B634" t="s">
         <v>278</v>
@@ -42250,10 +42250,10 @@
     </row>
     <row r="635" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
+        <v>500</v>
+      </c>
+      <c r="B635" t="s">
         <v>501</v>
-      </c>
-      <c r="B635" t="s">
-        <v>502</v>
       </c>
       <c r="C635">
         <v>1</v>
@@ -42309,7 +42309,7 @@
     </row>
     <row r="636" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B636" t="s">
         <v>384</v>
@@ -42368,7 +42368,7 @@
     </row>
     <row r="637" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B637" t="s">
         <v>32</v>
@@ -42427,7 +42427,7 @@
     </row>
     <row r="638" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B638" t="s">
         <v>37</v>
@@ -42486,7 +42486,7 @@
     </row>
     <row r="639" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B639" t="s">
         <v>385</v>
@@ -42545,10 +42545,10 @@
     </row>
     <row r="640" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B640" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C640">
         <v>1</v>
@@ -42610,10 +42610,10 @@
     </row>
     <row r="641" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B641" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C641">
         <v>1</v>
@@ -42675,7 +42675,7 @@
     </row>
     <row r="642" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B642" t="s">
         <v>388</v>
@@ -42740,10 +42740,10 @@
     </row>
     <row r="643" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B643" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C643">
         <v>1</v>
@@ -42805,10 +42805,10 @@
     </row>
     <row r="644" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
+        <v>475</v>
+      </c>
+      <c r="B644" t="s">
         <v>476</v>
-      </c>
-      <c r="B644" t="s">
-        <v>477</v>
       </c>
       <c r="C644">
         <v>1</v>
@@ -42864,10 +42864,10 @@
     </row>
     <row r="645" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B645" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C645">
         <v>1</v>
@@ -42929,7 +42929,7 @@
     </row>
     <row r="646" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B646" t="s">
         <v>151</v>
@@ -42994,10 +42994,10 @@
     </row>
     <row r="647" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B647" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C647">
         <v>1</v>
@@ -43053,10 +43053,10 @@
     </row>
     <row r="648" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B648" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C648">
         <v>1</v>
@@ -43118,10 +43118,10 @@
     </row>
     <row r="649" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B649" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C649">
         <v>1</v>
@@ -43177,7 +43177,7 @@
     </row>
     <row r="650" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B650" t="s">
         <v>248</v>
@@ -43236,7 +43236,7 @@
     </row>
     <row r="651" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B651" t="s">
         <v>249</v>
@@ -43301,7 +43301,7 @@
     </row>
     <row r="652" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B652" t="s">
         <v>250</v>
@@ -43360,7 +43360,7 @@
     </row>
     <row r="653" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B653" t="s">
         <v>332</v>
@@ -43419,10 +43419,10 @@
     </row>
     <row r="654" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B654" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C654">
         <v>1</v>
@@ -43484,10 +43484,10 @@
     </row>
     <row r="655" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B655" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C655">
         <v>1</v>
@@ -43543,7 +43543,7 @@
     </row>
     <row r="656" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B656" t="s">
         <v>47</v>
@@ -43608,10 +43608,10 @@
     </row>
     <row r="657" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B657" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C657">
         <v>1</v>
@@ -43673,10 +43673,10 @@
     </row>
     <row r="658" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B658" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C658">
         <v>1</v>
@@ -43732,7 +43732,7 @@
     </row>
     <row r="659" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B659" t="s">
         <v>285</v>
@@ -43797,7 +43797,7 @@
     </row>
     <row r="660" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B660" t="s">
         <v>286</v>
@@ -43856,7 +43856,7 @@
     </row>
     <row r="661" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B661" t="s">
         <v>340</v>
@@ -43889,10 +43889,10 @@
         <v>0</v>
       </c>
       <c r="M661" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="N661" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="O661">
         <v>4</v>
@@ -43915,7 +43915,7 @@
     </row>
     <row r="662" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B662" t="s">
         <v>52</v>
@@ -43980,7 +43980,7 @@
     </row>
     <row r="663" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B663" t="s">
         <v>54</v>
@@ -44039,7 +44039,7 @@
     </row>
     <row r="664" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B664" t="s">
         <v>121</v>
@@ -44104,10 +44104,10 @@
     </row>
     <row r="665" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
+        <v>482</v>
+      </c>
+      <c r="B665" t="s">
         <v>483</v>
-      </c>
-      <c r="B665" t="s">
-        <v>484</v>
       </c>
       <c r="C665">
         <v>1</v>
@@ -44163,7 +44163,7 @@
     </row>
     <row r="666" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B666" t="s">
         <v>316</v>
@@ -44228,7 +44228,7 @@
     </row>
     <row r="667" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B667" t="s">
         <v>59</v>
@@ -44293,7 +44293,7 @@
     </row>
     <row r="668" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B668" t="s">
         <v>318</v>
@@ -44352,7 +44352,7 @@
     </row>
     <row r="669" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B669" t="s">
         <v>289</v>
@@ -44417,10 +44417,10 @@
     </row>
     <row r="670" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B670" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C670">
         <v>1</v>
@@ -44482,10 +44482,10 @@
     </row>
     <row r="671" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B671" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C671">
         <v>1</v>
@@ -44547,7 +44547,7 @@
     </row>
     <row r="672" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B672" t="s">
         <v>83</v>
@@ -44606,7 +44606,7 @@
     </row>
     <row r="673" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B673" t="s">
         <v>64</v>
@@ -44671,10 +44671,10 @@
     </row>
     <row r="674" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B674" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C674">
         <v>1</v>
@@ -44736,7 +44736,7 @@
     </row>
     <row r="675" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B675" t="s">
         <v>232</v>
@@ -44795,10 +44795,10 @@
     </row>
     <row r="676" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B676" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C676">
         <v>1</v>
@@ -44854,7 +44854,7 @@
     </row>
     <row r="677" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B677" t="s">
         <v>89</v>
@@ -44913,7 +44913,7 @@
     </row>
     <row r="678" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B678" t="s">
         <v>379</v>
@@ -44978,10 +44978,10 @@
     </row>
     <row r="679" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B679" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C679">
         <v>1</v>
@@ -45037,7 +45037,7 @@
     </row>
     <row r="680" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B680" t="s">
         <v>67</v>
@@ -45102,10 +45102,10 @@
     </row>
     <row r="681" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B681" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C681">
         <v>1</v>
@@ -45167,7 +45167,7 @@
     </row>
     <row r="682" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B682" t="s">
         <v>337</v>
@@ -45226,7 +45226,7 @@
     </row>
     <row r="683" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B683" t="s">
         <v>226</v>
@@ -45285,7 +45285,7 @@
     </row>
     <row r="684" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B684" t="s">
         <v>79</v>
@@ -45350,7 +45350,7 @@
     </row>
     <row r="685" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B685" t="s">
         <v>114</v>
@@ -45415,7 +45415,7 @@
     </row>
     <row r="686" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B686" t="s">
         <v>377</v>
@@ -45474,7 +45474,7 @@
     </row>
     <row r="687" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B687" t="s">
         <v>54</v>
@@ -45533,10 +45533,10 @@
     </row>
     <row r="688" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B688" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C688">
         <v>1</v>
@@ -45598,7 +45598,7 @@
     </row>
     <row r="689" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B689" t="s">
         <v>329</v>
@@ -45663,7 +45663,7 @@
     </row>
     <row r="690" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B690" t="s">
         <v>393</v>
@@ -45728,11 +45728,11 @@
     </row>
     <row r="691" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
+        <v>504</v>
+      </c>
+      <c r="B691" t="s">
         <v>505</v>
       </c>
-      <c r="B691" t="s">
-        <v>506</v>
-      </c>
       <c r="C691">
         <v>1</v>
       </c>
@@ -45761,10 +45761,10 @@
         <v>0</v>
       </c>
       <c r="M691" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="N691" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="O691">
         <v>6</v>
@@ -45787,7 +45787,7 @@
     </row>
     <row r="692" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B692" t="s">
         <v>248</v>
@@ -45846,7 +45846,7 @@
     </row>
     <row r="693" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B693" t="s">
         <v>122</v>
@@ -45897,7 +45897,7 @@
         <v>1</v>
       </c>
       <c r="S693" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="T693" t="s">
         <v>24</v>
@@ -45905,7 +45905,7 @@
     </row>
     <row r="694" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B694" t="s">
         <v>249</v>
@@ -45970,7 +45970,7 @@
     </row>
     <row r="695" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B695" t="s">
         <v>332</v>
@@ -46035,10 +46035,10 @@
     </row>
     <row r="696" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B696" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C696">
         <v>1</v>
@@ -46094,7 +46094,7 @@
     </row>
     <row r="697" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B697" t="s">
         <v>59</v>
@@ -46159,10 +46159,10 @@
     </row>
     <row r="698" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B698" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C698">
         <v>1</v>
@@ -46218,10 +46218,10 @@
     </row>
     <row r="699" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
+        <v>507</v>
+      </c>
+      <c r="B699" t="s">
         <v>508</v>
-      </c>
-      <c r="B699" t="s">
-        <v>509</v>
       </c>
       <c r="C699">
         <v>1</v>
@@ -46272,7 +46272,7 @@
         <v>1</v>
       </c>
       <c r="S699" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="T699" t="s">
         <v>24</v>
@@ -46283,7 +46283,7 @@
     </row>
     <row r="700" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B700" t="s">
         <v>45</v>
@@ -46348,7 +46348,7 @@
     </row>
     <row r="701" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B701" t="s">
         <v>312</v>
@@ -46413,7 +46413,7 @@
     </row>
     <row r="702" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B702" t="s">
         <v>246</v>
@@ -46478,10 +46478,10 @@
     </row>
     <row r="703" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B703" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C703">
         <v>1</v>
@@ -46543,10 +46543,10 @@
     </row>
     <row r="704" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B704" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C704">
         <v>1</v>
@@ -46608,7 +46608,7 @@
     </row>
     <row r="705" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B705" t="s">
         <v>256</v>
@@ -46673,7 +46673,7 @@
     </row>
     <row r="706" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B706" t="s">
         <v>357</v>
@@ -46738,10 +46738,10 @@
     </row>
     <row r="707" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B707" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C707">
         <v>1</v>
@@ -46771,10 +46771,10 @@
         <v>0</v>
       </c>
       <c r="M707" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="N707" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="O707">
         <v>6</v>
@@ -46797,10 +46797,10 @@
     </row>
     <row r="708" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B708" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C708">
         <v>1</v>
@@ -46862,10 +46862,10 @@
     </row>
     <row r="709" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B709" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C709">
         <v>1</v>
@@ -46921,7 +46921,7 @@
     </row>
     <row r="710" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B710" t="s">
         <v>60</v>
@@ -46986,10 +46986,10 @@
     </row>
     <row r="711" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B711" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C711">
         <v>1</v>
@@ -47051,7 +47051,7 @@
     </row>
     <row r="712" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B712" t="s">
         <v>342</v>
@@ -47110,7 +47110,7 @@
     </row>
     <row r="713" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B713" t="s">
         <v>278</v>
@@ -47161,7 +47161,7 @@
         <v>1</v>
       </c>
       <c r="S713" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="T713" t="s">
         <v>24</v>
@@ -47169,7 +47169,7 @@
     </row>
     <row r="714" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B714" t="s">
         <v>180</v>
@@ -47234,7 +47234,7 @@
     </row>
     <row r="715" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B715" t="s">
         <v>265</v>
@@ -47299,7 +47299,7 @@
     </row>
     <row r="716" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B716" t="s">
         <v>409</v>
@@ -47364,7 +47364,7 @@
     </row>
     <row r="717" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B717" t="s">
         <v>32</v>
@@ -47429,7 +47429,7 @@
     </row>
     <row r="718" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B718" t="s">
         <v>184</v>
@@ -47494,7 +47494,7 @@
     </row>
     <row r="719" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B719" t="s">
         <v>37</v>
@@ -47559,7 +47559,7 @@
     </row>
     <row r="720" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B720" t="s">
         <v>266</v>
@@ -47618,10 +47618,10 @@
     </row>
     <row r="721" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B721" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C721">
         <v>1</v>
@@ -47683,7 +47683,7 @@
     </row>
     <row r="722" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B722" t="s">
         <v>201</v>
@@ -47748,10 +47748,10 @@
     </row>
     <row r="723" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
+        <v>516</v>
+      </c>
+      <c r="B723" t="s">
         <v>517</v>
-      </c>
-      <c r="B723" t="s">
-        <v>518</v>
       </c>
       <c r="C723">
         <v>1</v>
@@ -47807,10 +47807,10 @@
     </row>
     <row r="724" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B724" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C724">
         <v>1</v>
@@ -47872,7 +47872,7 @@
     </row>
     <row r="725" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B725" t="s">
         <v>230</v>
@@ -47931,10 +47931,10 @@
     </row>
     <row r="726" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B726" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C726">
         <v>1</v>
@@ -47996,7 +47996,7 @@
     </row>
     <row r="727" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B727" t="s">
         <v>116</v>
@@ -48061,10 +48061,10 @@
     </row>
     <row r="728" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B728" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C728">
         <v>1</v>
@@ -48126,7 +48126,7 @@
     </row>
     <row r="729" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B729" t="s">
         <v>119</v>
@@ -48185,10 +48185,10 @@
     </row>
     <row r="730" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B730" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C730">
         <v>1</v>
@@ -48244,7 +48244,7 @@
     </row>
     <row r="731" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B731" t="s">
         <v>137</v>
@@ -48303,10 +48303,10 @@
     </row>
     <row r="732" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B732" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C732">
         <v>1</v>
@@ -48368,7 +48368,7 @@
     </row>
     <row r="733" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B733" t="s">
         <v>39</v>
@@ -48427,10 +48427,10 @@
     </row>
     <row r="734" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B734" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C734">
         <v>1</v>
@@ -48492,7 +48492,7 @@
     </row>
     <row r="735" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B735" t="s">
         <v>214</v>
@@ -48551,10 +48551,10 @@
     </row>
     <row r="736" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B736" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C736">
         <v>1</v>
@@ -48610,7 +48610,7 @@
     </row>
     <row r="737" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B737" t="s">
         <v>235</v>
@@ -48669,7 +48669,7 @@
     </row>
     <row r="738" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B738" t="s">
         <v>25</v>
@@ -48728,7 +48728,7 @@
     </row>
     <row r="739" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B739" t="s">
         <v>205</v>
@@ -48787,7 +48787,7 @@
     </row>
     <row r="740" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B740" t="s">
         <v>164</v>
@@ -48852,7 +48852,7 @@
     </row>
     <row r="741" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B741" t="s">
         <v>308</v>
@@ -48911,10 +48911,10 @@
     </row>
     <row r="742" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
+        <v>524</v>
+      </c>
+      <c r="B742" t="s">
         <v>525</v>
-      </c>
-      <c r="B742" t="s">
-        <v>526</v>
       </c>
       <c r="C742">
         <v>1</v>
@@ -48976,10 +48976,10 @@
     </row>
     <row r="743" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B743" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C743">
         <v>1</v>
@@ -49035,10 +49035,10 @@
     </row>
     <row r="744" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B744" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C744">
         <v>1</v>
@@ -49100,7 +49100,7 @@
     </row>
     <row r="745" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B745" t="s">
         <v>309</v>
@@ -49165,7 +49165,7 @@
     </row>
     <row r="746" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B746" t="s">
         <v>399</v>
@@ -49224,7 +49224,7 @@
     </row>
     <row r="747" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B747" t="s">
         <v>41</v>
@@ -49289,7 +49289,7 @@
     </row>
     <row r="748" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B748" t="s">
         <v>202</v>
@@ -49348,7 +49348,7 @@
     </row>
     <row r="749" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B749" t="s">
         <v>130</v>
@@ -49407,7 +49407,7 @@
     </row>
     <row r="750" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B750" t="s">
         <v>204</v>
@@ -49466,7 +49466,7 @@
     </row>
     <row r="751" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B751" t="s">
         <v>301</v>
@@ -49525,10 +49525,10 @@
     </row>
     <row r="752" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B752" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C752">
         <v>1</v>
@@ -49584,10 +49584,10 @@
     </row>
     <row r="753" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B753" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C753">
         <v>1</v>
@@ -49649,7 +49649,7 @@
     </row>
     <row r="754" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B754" t="s">
         <v>208</v>
@@ -49708,7 +49708,7 @@
     </row>
     <row r="755" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B755" t="s">
         <v>212</v>
@@ -49773,7 +49773,7 @@
     </row>
     <row r="756" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B756" t="s">
         <v>138</v>
@@ -49838,7 +49838,7 @@
     </row>
     <row r="757" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B757" t="s">
         <v>139</v>
@@ -49897,10 +49897,10 @@
     </row>
     <row r="758" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
+        <v>527</v>
+      </c>
+      <c r="B758" t="s">
         <v>528</v>
-      </c>
-      <c r="B758" t="s">
-        <v>529</v>
       </c>
       <c r="C758">
         <v>1</v>
@@ -49956,7 +49956,7 @@
     </row>
     <row r="759" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B759" t="s">
         <v>140</v>
@@ -50021,7 +50021,7 @@
     </row>
     <row r="760" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B760" t="s">
         <v>370</v>
@@ -50078,7 +50078,7 @@
         <v>24</v>
       </c>
       <c r="T760" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="U760">
         <v>6</v>
@@ -50086,7 +50086,7 @@
     </row>
     <row r="761" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B761" t="s">
         <v>114</v>
@@ -50151,10 +50151,10 @@
     </row>
     <row r="762" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B762" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C762">
         <v>1</v>
@@ -50210,10 +50210,10 @@
     </row>
     <row r="763" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
+        <v>530</v>
+      </c>
+      <c r="B763" t="s">
         <v>531</v>
-      </c>
-      <c r="B763" t="s">
-        <v>532</v>
       </c>
       <c r="C763">
         <v>1</v>
@@ -50269,7 +50269,7 @@
     </row>
     <row r="764" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B764" t="s">
         <v>121</v>
@@ -50328,10 +50328,10 @@
     </row>
     <row r="765" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B765" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C765">
         <v>1</v>
@@ -50387,7 +50387,7 @@
     </row>
     <row r="766" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B766" t="s">
         <v>124</v>
@@ -50452,7 +50452,7 @@
     </row>
     <row r="767" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B767" t="s">
         <v>138</v>
@@ -50517,7 +50517,7 @@
     </row>
     <row r="768" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B768" t="s">
         <v>59</v>
@@ -50582,7 +50582,7 @@
     </row>
     <row r="769" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B769" t="s">
         <v>140</v>
@@ -50647,10 +50647,10 @@
     </row>
     <row r="770" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B770" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C770">
         <v>1</v>
@@ -50712,7 +50712,7 @@
     </row>
     <row r="771" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B771" t="s">
         <v>126</v>
@@ -50777,7 +50777,7 @@
     </row>
     <row r="772" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B772" t="s">
         <v>22</v>
@@ -50842,7 +50842,7 @@
     </row>
     <row r="773" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B773" t="s">
         <v>275</v>
@@ -50901,10 +50901,10 @@
     </row>
     <row r="774" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
+        <v>533</v>
+      </c>
+      <c r="B774" t="s">
         <v>534</v>
-      </c>
-      <c r="B774" t="s">
-        <v>535</v>
       </c>
       <c r="C774">
         <v>1</v>
@@ -50966,7 +50966,7 @@
     </row>
     <row r="775" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B775" t="s">
         <v>277</v>
@@ -51025,7 +51025,7 @@
     </row>
     <row r="776" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B776" t="s">
         <v>116</v>
@@ -51090,7 +51090,7 @@
     </row>
     <row r="777" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B777" t="s">
         <v>169</v>
@@ -51155,7 +51155,7 @@
     </row>
     <row r="778" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B778" t="s">
         <v>399</v>
@@ -51214,7 +51214,7 @@
     </row>
     <row r="779" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B779" t="s">
         <v>137</v>
@@ -51279,7 +51279,7 @@
     </row>
     <row r="780" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B780" t="s">
         <v>363</v>
@@ -51338,7 +51338,7 @@
     </row>
     <row r="781" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B781" t="s">
         <v>174</v>
@@ -51403,7 +51403,7 @@
     </row>
     <row r="782" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B782" t="s">
         <v>41</v>
@@ -51468,7 +51468,7 @@
     </row>
     <row r="783" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B783" t="s">
         <v>365</v>
@@ -51527,10 +51527,10 @@
     </row>
     <row r="784" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
+        <v>535</v>
+      </c>
+      <c r="B784" t="s">
         <v>536</v>
-      </c>
-      <c r="B784" t="s">
-        <v>537</v>
       </c>
       <c r="C784">
         <v>1</v>
@@ -51592,10 +51592,10 @@
     </row>
     <row r="785" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B785" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C785">
         <v>1</v>
@@ -51657,7 +51657,7 @@
     </row>
     <row r="786" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B786" t="s">
         <v>104</v>
@@ -51722,7 +51722,7 @@
     </row>
     <row r="787" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B787" t="s">
         <v>397</v>
@@ -51781,10 +51781,10 @@
     </row>
     <row r="788" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B788" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C788">
         <v>1</v>
@@ -51840,7 +51840,7 @@
     </row>
     <row r="789" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B789" t="s">
         <v>183</v>
@@ -51905,7 +51905,7 @@
     </row>
     <row r="790" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B790" t="s">
         <v>106</v>
@@ -51964,7 +51964,7 @@
     </row>
     <row r="791" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B791" t="s">
         <v>108</v>
@@ -52029,7 +52029,7 @@
     </row>
     <row r="792" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B792" t="s">
         <v>398</v>
@@ -52088,10 +52088,10 @@
     </row>
     <row r="793" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B793" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C793">
         <v>1</v>
@@ -52147,10 +52147,10 @@
     </row>
     <row r="794" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B794" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C794">
         <v>1</v>
@@ -52212,10 +52212,10 @@
     </row>
     <row r="795" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B795" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C795">
         <v>1</v>
@@ -52271,7 +52271,7 @@
     </row>
     <row r="796" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B796" t="s">
         <v>253</v>
@@ -52330,7 +52330,7 @@
     </row>
     <row r="797" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B797" t="s">
         <v>142</v>
@@ -52389,7 +52389,7 @@
     </row>
     <row r="798" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B798" t="s">
         <v>146</v>
@@ -52454,7 +52454,7 @@
     </row>
     <row r="799" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B799" t="s">
         <v>283</v>
@@ -52519,10 +52519,10 @@
     </row>
     <row r="800" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
+        <v>539</v>
+      </c>
+      <c r="B800" t="s">
         <v>540</v>
-      </c>
-      <c r="B800" t="s">
-        <v>541</v>
       </c>
       <c r="C800">
         <v>1</v>
@@ -52584,10 +52584,10 @@
     </row>
     <row r="801" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B801" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C801">
         <v>1</v>
@@ -52649,10 +52649,10 @@
     </row>
     <row r="802" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B802" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C802">
         <v>1</v>
@@ -52714,7 +52714,7 @@
     </row>
     <row r="803" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B803" t="s">
         <v>257</v>
@@ -52779,10 +52779,10 @@
     </row>
     <row r="804" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B804" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C804">
         <v>1</v>
@@ -52844,10 +52844,10 @@
     </row>
     <row r="805" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B805" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C805">
         <v>1</v>
@@ -52903,10 +52903,10 @@
     </row>
     <row r="806" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B806" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C806">
         <v>1</v>
@@ -52962,10 +52962,10 @@
     </row>
     <row r="807" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B807" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C807">
         <v>1</v>
@@ -53021,10 +53021,10 @@
     </row>
     <row r="808" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B808" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C808">
         <v>1</v>
@@ -53086,7 +53086,7 @@
     </row>
     <row r="809" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B809" t="s">
         <v>27</v>
@@ -53145,7 +53145,7 @@
     </row>
     <row r="810" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B810" t="s">
         <v>342</v>
@@ -53204,7 +53204,7 @@
     </row>
     <row r="811" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B811" t="s">
         <v>103</v>
@@ -53263,7 +53263,7 @@
     </row>
     <row r="812" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B812" t="s">
         <v>278</v>
@@ -53328,7 +53328,7 @@
     </row>
     <row r="813" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B813" t="s">
         <v>105</v>
@@ -53393,7 +53393,7 @@
     </row>
     <row r="814" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B814" t="s">
         <v>32</v>
@@ -53458,7 +53458,7 @@
     </row>
     <row r="815" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B815" t="s">
         <v>416</v>
@@ -53517,10 +53517,10 @@
     </row>
     <row r="816" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B816" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C816">
         <v>1</v>
@@ -53576,10 +53576,10 @@
     </row>
     <row r="817" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
+        <v>543</v>
+      </c>
+      <c r="B817" t="s">
         <v>544</v>
-      </c>
-      <c r="B817" t="s">
-        <v>545</v>
       </c>
       <c r="C817">
         <v>1</v>
@@ -53641,10 +53641,10 @@
     </row>
     <row r="818" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B818" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C818">
         <v>1</v>
@@ -53700,10 +53700,10 @@
     </row>
     <row r="819" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B819" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C819">
         <v>1</v>
@@ -53765,10 +53765,10 @@
     </row>
     <row r="820" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B820" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C820">
         <v>1</v>
@@ -53830,10 +53830,10 @@
     </row>
     <row r="821" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B821" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C821">
         <v>1</v>
@@ -53895,7 +53895,7 @@
     </row>
     <row r="822" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B822" t="s">
         <v>43</v>
@@ -53960,7 +53960,7 @@
     </row>
     <row r="823" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B823" t="s">
         <v>114</v>
@@ -54019,7 +54019,7 @@
     </row>
     <row r="824" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B824" t="s">
         <v>202</v>
@@ -54078,7 +54078,7 @@
     </row>
     <row r="825" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B825" t="s">
         <v>204</v>
@@ -54143,7 +54143,7 @@
     </row>
     <row r="826" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B826" t="s">
         <v>271</v>
@@ -54208,7 +54208,7 @@
     </row>
     <row r="827" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B827" t="s">
         <v>301</v>
@@ -54273,7 +54273,7 @@
     </row>
     <row r="828" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B828" t="s">
         <v>208</v>
@@ -54338,7 +54338,7 @@
     </row>
     <row r="829" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B829" t="s">
         <v>121</v>
@@ -54397,7 +54397,7 @@
     </row>
     <row r="830" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B830" t="s">
         <v>124</v>
@@ -54456,7 +54456,7 @@
     </row>
     <row r="831" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B831" t="s">
         <v>212</v>
@@ -54521,7 +54521,7 @@
     </row>
     <row r="832" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B832" t="s">
         <v>59</v>
@@ -54586,10 +54586,10 @@
     </row>
     <row r="833" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
+        <v>548</v>
+      </c>
+      <c r="B833" t="s">
         <v>549</v>
-      </c>
-      <c r="B833" t="s">
-        <v>550</v>
       </c>
       <c r="C833">
         <v>1</v>
@@ -54651,7 +54651,7 @@
     </row>
     <row r="834" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B834" t="s">
         <v>203</v>
@@ -54710,10 +54710,10 @@
     </row>
     <row r="835" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B835" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C835">
         <v>1</v>
@@ -54769,7 +54769,7 @@
     </row>
     <row r="836" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B836" t="s">
         <v>116</v>
@@ -54828,7 +54828,7 @@
     </row>
     <row r="837" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B837" t="s">
         <v>136</v>
@@ -54882,7 +54882,7 @@
         <v>0</v>
       </c>
       <c r="S837" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="T837" t="s">
         <v>24</v>
@@ -54893,10 +54893,10 @@
     </row>
     <row r="838" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B838" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C838">
         <v>1</v>
@@ -54952,7 +54952,7 @@
     </row>
     <row r="839" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B839" t="s">
         <v>196</v>
@@ -55017,10 +55017,10 @@
     </row>
     <row r="840" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B840" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C840">
         <v>1</v>
@@ -55082,10 +55082,10 @@
     </row>
     <row r="841" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
+        <v>550</v>
+      </c>
+      <c r="B841" t="s">
         <v>551</v>
-      </c>
-      <c r="B841" t="s">
-        <v>552</v>
       </c>
       <c r="C841">
         <v>1</v>
@@ -55141,7 +55141,7 @@
     </row>
     <row r="842" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B842" t="s">
         <v>138</v>
@@ -55206,7 +55206,7 @@
     </row>
     <row r="843" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B843" t="s">
         <v>369</v>
@@ -55271,7 +55271,7 @@
     </row>
     <row r="844" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B844" t="s">
         <v>140</v>
@@ -55330,10 +55330,10 @@
     </row>
     <row r="845" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B845" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C845">
         <v>1</v>
@@ -55389,10 +55389,10 @@
     </row>
     <row r="846" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B846" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C846">
         <v>1</v>
@@ -55454,7 +55454,7 @@
     </row>
     <row r="847" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B847" t="s">
         <v>125</v>
@@ -55513,10 +55513,10 @@
     </row>
     <row r="848" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B848" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C848">
         <v>1</v>
@@ -55572,10 +55572,10 @@
     </row>
     <row r="849" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B849" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C849">
         <v>1</v>
@@ -55631,10 +55631,10 @@
     </row>
     <row r="850" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
+        <v>554</v>
+      </c>
+      <c r="B850" t="s">
         <v>555</v>
-      </c>
-      <c r="B850" t="s">
-        <v>556</v>
       </c>
       <c r="C850">
         <v>1</v>
@@ -55690,7 +55690,7 @@
     </row>
     <row r="851" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B851" t="s">
         <v>87</v>
@@ -55749,7 +55749,7 @@
     </row>
     <row r="852" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B852" t="s">
         <v>347</v>
@@ -55814,7 +55814,7 @@
     </row>
     <row r="853" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B853" t="s">
         <v>407</v>
@@ -55873,10 +55873,10 @@
     </row>
     <row r="854" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B854" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C854">
         <v>1</v>
@@ -55932,7 +55932,7 @@
     </row>
     <row r="855" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B855" t="s">
         <v>336</v>
@@ -55997,7 +55997,7 @@
     </row>
     <row r="856" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B856" t="s">
         <v>67</v>
@@ -56062,7 +56062,7 @@
     </row>
     <row r="857" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B857" t="s">
         <v>374</v>
@@ -56121,7 +56121,7 @@
     </row>
     <row r="858" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B858" t="s">
         <v>225</v>
@@ -56186,7 +56186,7 @@
     </row>
     <row r="859" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B859" t="s">
         <v>349</v>
@@ -56245,7 +56245,7 @@
     </row>
     <row r="860" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B860" t="s">
         <v>350</v>
@@ -56310,7 +56310,7 @@
     </row>
     <row r="861" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B861" t="s">
         <v>95</v>
@@ -56369,7 +56369,7 @@
     </row>
     <row r="862" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B862" t="s">
         <v>79</v>
@@ -56434,7 +56434,7 @@
     </row>
     <row r="863" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B863" t="s">
         <v>311</v>
@@ -56493,7 +56493,7 @@
     </row>
     <row r="864" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B864" t="s">
         <v>312</v>
@@ -56552,7 +56552,7 @@
     </row>
     <row r="865" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B865" t="s">
         <v>314</v>
@@ -56617,10 +56617,10 @@
     </row>
     <row r="866" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B866" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C866">
         <v>1</v>
@@ -56682,10 +56682,10 @@
     </row>
     <row r="867" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B867" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C867">
         <v>1</v>
@@ -56741,7 +56741,7 @@
     </row>
     <row r="868" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B868" t="s">
         <v>393</v>
@@ -56806,7 +56806,7 @@
     </row>
     <row r="869" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B869" t="s">
         <v>248</v>
@@ -56871,7 +56871,7 @@
     </row>
     <row r="870" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B870" t="s">
         <v>249</v>
@@ -56936,10 +56936,10 @@
     </row>
     <row r="871" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B871" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C871">
         <v>1</v>
@@ -56995,7 +56995,7 @@
     </row>
     <row r="872" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B872" t="s">
         <v>250</v>
@@ -57060,7 +57060,7 @@
     </row>
     <row r="873" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B873" t="s">
         <v>332</v>
@@ -57125,7 +57125,7 @@
     </row>
     <row r="874" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B874" t="s">
         <v>45</v>
@@ -57190,10 +57190,10 @@
     </row>
     <row r="875" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
+        <v>558</v>
+      </c>
+      <c r="B875" t="s">
         <v>559</v>
-      </c>
-      <c r="B875" t="s">
-        <v>560</v>
       </c>
       <c r="C875">
         <v>1</v>
@@ -57249,7 +57249,7 @@
     </row>
     <row r="876" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B876" t="s">
         <v>142</v>
@@ -57314,7 +57314,7 @@
     </row>
     <row r="877" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B877" t="s">
         <v>146</v>
@@ -57373,7 +57373,7 @@
     </row>
     <row r="878" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B878" t="s">
         <v>246</v>
@@ -57438,10 +57438,10 @@
     </row>
     <row r="879" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B879" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C879">
         <v>1</v>
@@ -57497,7 +57497,7 @@
     </row>
     <row r="880" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B880" t="s">
         <v>357</v>
@@ -57562,10 +57562,10 @@
     </row>
     <row r="881" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B881" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C881">
         <v>1</v>
@@ -57627,10 +57627,10 @@
     </row>
     <row r="882" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B882" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C882">
         <v>1</v>
@@ -57692,7 +57692,7 @@
     </row>
     <row r="883" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B883" t="s">
         <v>60</v>
@@ -57757,10 +57757,10 @@
     </row>
     <row r="884" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B884" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C884">
         <v>1</v>
@@ -57822,7 +57822,7 @@
     </row>
     <row r="885" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B885" t="s">
         <v>102</v>
@@ -57887,10 +57887,10 @@
     </row>
     <row r="886" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B886" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C886">
         <v>1</v>
@@ -57946,7 +57946,7 @@
     </row>
     <row r="887" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B887" t="s">
         <v>414</v>
@@ -58011,7 +58011,7 @@
     </row>
     <row r="888" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B888" t="s">
         <v>104</v>
@@ -58070,7 +58070,7 @@
     </row>
     <row r="889" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B889" t="s">
         <v>397</v>
@@ -58135,7 +58135,7 @@
     </row>
     <row r="890" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B890" t="s">
         <v>164</v>
@@ -58200,10 +58200,10 @@
     </row>
     <row r="891" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
+        <v>560</v>
+      </c>
+      <c r="B891" t="s">
         <v>561</v>
-      </c>
-      <c r="B891" t="s">
-        <v>562</v>
       </c>
       <c r="C891">
         <v>1</v>
@@ -58259,7 +58259,7 @@
     </row>
     <row r="892" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B892" t="s">
         <v>308</v>
@@ -58324,7 +58324,7 @@
     </row>
     <row r="893" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B893" t="s">
         <v>108</v>
@@ -58389,10 +58389,10 @@
     </row>
     <row r="894" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B894" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C894">
         <v>1</v>
@@ -58454,7 +58454,7 @@
     </row>
     <row r="895" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B895" t="s">
         <v>309</v>
@@ -58519,7 +58519,7 @@
     </row>
     <row r="896" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B896" t="s">
         <v>267</v>
@@ -58584,7 +58584,7 @@
     </row>
     <row r="897" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B897" t="s">
         <v>25</v>
@@ -58649,7 +58649,7 @@
     </row>
     <row r="898" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B898" t="s">
         <v>178</v>
@@ -58714,7 +58714,7 @@
     </row>
     <row r="899" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B899" t="s">
         <v>203</v>
@@ -58773,7 +58773,7 @@
     </row>
     <row r="900" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B900" t="s">
         <v>180</v>
@@ -58832,7 +58832,7 @@
     </row>
     <row r="901" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B901" t="s">
         <v>265</v>
@@ -58897,7 +58897,7 @@
     </row>
     <row r="902" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B902" t="s">
         <v>207</v>
@@ -58956,7 +58956,7 @@
     </row>
     <row r="903" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B903" t="s">
         <v>184</v>
@@ -59021,7 +59021,7 @@
     </row>
     <row r="904" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B904" t="s">
         <v>185</v>
@@ -59086,7 +59086,7 @@
     </row>
     <row r="905" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B905" t="s">
         <v>119</v>
@@ -59145,10 +59145,10 @@
     </row>
     <row r="906" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
+        <v>562</v>
+      </c>
+      <c r="B906" t="s">
         <v>563</v>
-      </c>
-      <c r="B906" t="s">
-        <v>564</v>
       </c>
       <c r="C906">
         <v>1</v>
@@ -59204,7 +59204,7 @@
     </row>
     <row r="907" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B907" t="s">
         <v>196</v>
@@ -59269,10 +59269,10 @@
     </row>
     <row r="908" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B908" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C908">
         <v>1</v>
@@ -59328,7 +59328,7 @@
     </row>
     <row r="909" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B909" t="s">
         <v>266</v>
@@ -59393,7 +59393,7 @@
     </row>
     <row r="910" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B910" t="s">
         <v>41</v>
@@ -59458,7 +59458,7 @@
     </row>
     <row r="911" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B911" t="s">
         <v>114</v>
@@ -59523,10 +59523,10 @@
     </row>
     <row r="912" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B912" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C912">
         <v>1</v>
@@ -59588,7 +59588,7 @@
     </row>
     <row r="913" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B913" t="s">
         <v>271</v>
@@ -59653,10 +59653,10 @@
     </row>
     <row r="914" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B914" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C914">
         <v>1</v>
@@ -59712,7 +59712,7 @@
     </row>
     <row r="915" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B915" t="s">
         <v>121</v>
@@ -59777,7 +59777,7 @@
     </row>
     <row r="916" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B916" t="s">
         <v>367</v>
@@ -59842,10 +59842,10 @@
     </row>
     <row r="917" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
+        <v>565</v>
+      </c>
+      <c r="B917" t="s">
         <v>566</v>
-      </c>
-      <c r="B917" t="s">
-        <v>567</v>
       </c>
       <c r="C917">
         <v>1</v>
@@ -59901,7 +59901,7 @@
     </row>
     <row r="918" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B918" t="s">
         <v>368</v>
@@ -59960,7 +59960,7 @@
     </row>
     <row r="919" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B919" t="s">
         <v>126</v>
@@ -60025,10 +60025,10 @@
     </row>
     <row r="920" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B920" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C920">
         <v>1</v>
@@ -60084,7 +60084,7 @@
     </row>
     <row r="921" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B921" t="s">
         <v>235</v>
@@ -60149,7 +60149,7 @@
     </row>
     <row r="922" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B922" t="s">
         <v>277</v>
@@ -60208,10 +60208,10 @@
     </row>
     <row r="923" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B923" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C923">
         <v>1</v>
@@ -60273,7 +60273,7 @@
     </row>
     <row r="924" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B924" t="s">
         <v>161</v>
@@ -60338,7 +60338,7 @@
     </row>
     <row r="925" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B925" t="s">
         <v>384</v>
@@ -60397,7 +60397,7 @@
     </row>
     <row r="926" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B926" t="s">
         <v>183</v>
@@ -60456,7 +60456,7 @@
     </row>
     <row r="927" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B927" t="s">
         <v>169</v>
@@ -60521,7 +60521,7 @@
     </row>
     <row r="928" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B928" t="s">
         <v>188</v>
@@ -60586,10 +60586,10 @@
     </row>
     <row r="929" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B929" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C929">
         <v>1</v>
@@ -60651,10 +60651,10 @@
     </row>
     <row r="930" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B930" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C930">
         <v>1</v>
@@ -60716,7 +60716,7 @@
     </row>
     <row r="931" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B931" t="s">
         <v>363</v>
@@ -60775,7 +60775,7 @@
     </row>
     <row r="932" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B932" t="s">
         <v>365</v>
@@ -60834,10 +60834,10 @@
     </row>
     <row r="933" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B933" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C933">
         <v>1</v>
@@ -60899,7 +60899,7 @@
     </row>
     <row r="934" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B934" t="s">
         <v>376</v>
@@ -60964,10 +60964,10 @@
     </row>
     <row r="935" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
+        <v>568</v>
+      </c>
+      <c r="B935" t="s">
         <v>569</v>
-      </c>
-      <c r="B935" t="s">
-        <v>570</v>
       </c>
       <c r="C935">
         <v>1</v>
@@ -61023,7 +61023,7 @@
     </row>
     <row r="936" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B936" t="s">
         <v>377</v>
@@ -61082,10 +61082,10 @@
     </row>
     <row r="937" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B937" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C937">
         <v>1</v>
@@ -61141,10 +61141,10 @@
     </row>
     <row r="938" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B938" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C938">
         <v>1</v>
@@ -61200,7 +61200,7 @@
     </row>
     <row r="939" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B939" t="s">
         <v>314</v>
@@ -61265,10 +61265,10 @@
     </row>
     <row r="940" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B940" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C940">
         <v>1</v>
@@ -61324,10 +61324,10 @@
     </row>
     <row r="941" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B941" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C941">
         <v>1</v>
@@ -61383,7 +61383,7 @@
     </row>
     <row r="942" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B942" t="s">
         <v>54</v>
@@ -61448,7 +61448,7 @@
     </row>
     <row r="943" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B943" t="s">
         <v>257</v>
@@ -61507,7 +61507,7 @@
     </row>
     <row r="944" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B944" t="s">
         <v>317</v>
@@ -61566,7 +61566,7 @@
     </row>
     <row r="945" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B945" t="s">
         <v>259</v>
@@ -61625,7 +61625,7 @@
     </row>
     <row r="946" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B946" t="s">
         <v>59</v>
@@ -61684,7 +61684,7 @@
     </row>
     <row r="947" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B947" t="s">
         <v>86</v>
@@ -61743,7 +61743,7 @@
     </row>
     <row r="948" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B948" t="s">
         <v>321</v>
@@ -61802,7 +61802,7 @@
     </row>
     <row r="949" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B949" t="s">
         <v>322</v>
@@ -61861,7 +61861,7 @@
     </row>
     <row r="950" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B950" t="s">
         <v>232</v>
@@ -61926,7 +61926,7 @@
     </row>
     <row r="951" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B951" t="s">
         <v>116</v>
@@ -61985,10 +61985,10 @@
     </row>
     <row r="952" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B952" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C952">
         <v>1</v>
@@ -62050,7 +62050,7 @@
     </row>
     <row r="953" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B953" t="s">
         <v>117</v>
@@ -62115,7 +62115,7 @@
     </row>
     <row r="954" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B954" t="s">
         <v>196</v>
@@ -62180,10 +62180,10 @@
     </row>
     <row r="955" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
+        <v>572</v>
+      </c>
+      <c r="B955" t="s">
         <v>573</v>
-      </c>
-      <c r="B955" t="s">
-        <v>574</v>
       </c>
       <c r="C955">
         <v>1</v>
@@ -62239,10 +62239,10 @@
     </row>
     <row r="956" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B956" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C956">
         <v>1</v>
@@ -62298,10 +62298,10 @@
     </row>
     <row r="957" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B957" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C957">
         <v>1</v>
@@ -62363,7 +62363,7 @@
     </row>
     <row r="958" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B958" t="s">
         <v>125</v>
@@ -62422,7 +62422,7 @@
     </row>
     <row r="959" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B959" t="s">
         <v>41</v>
@@ -62487,7 +62487,7 @@
     </row>
     <row r="960" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B960" t="s">
         <v>347</v>
@@ -62552,7 +62552,7 @@
     </row>
     <row r="961" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B961" t="s">
         <v>407</v>
@@ -62617,7 +62617,7 @@
     </row>
     <row r="962" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B962" t="s">
         <v>348</v>
@@ -62682,7 +62682,7 @@
     </row>
     <row r="963" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B963" t="s">
         <v>204</v>
@@ -62747,10 +62747,10 @@
     </row>
     <row r="964" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
+        <v>577</v>
+      </c>
+      <c r="B964" t="s">
         <v>578</v>
-      </c>
-      <c r="B964" t="s">
-        <v>579</v>
       </c>
       <c r="C964">
         <v>1</v>
@@ -62812,7 +62812,7 @@
     </row>
     <row r="965" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B965" t="s">
         <v>301</v>
@@ -62877,10 +62877,10 @@
     </row>
     <row r="966" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B966" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C966">
         <v>1</v>
@@ -62936,7 +62936,7 @@
     </row>
     <row r="967" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B967" t="s">
         <v>208</v>
@@ -63001,7 +63001,7 @@
     </row>
     <row r="968" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B968" t="s">
         <v>212</v>
@@ -63066,7 +63066,7 @@
     </row>
     <row r="969" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B969" t="s">
         <v>350</v>
@@ -63125,7 +63125,7 @@
     </row>
     <row r="970" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B970" t="s">
         <v>215</v>
@@ -63190,10 +63190,10 @@
     </row>
     <row r="971" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B971" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C971">
         <v>1</v>
@@ -63255,7 +63255,7 @@
     </row>
     <row r="972" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B972" t="s">
         <v>114</v>
@@ -63320,7 +63320,7 @@
     </row>
     <row r="973" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B973" t="s">
         <v>223</v>
@@ -63385,10 +63385,10 @@
     </row>
     <row r="974" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
+        <v>579</v>
+      </c>
+      <c r="B974" t="s">
         <v>580</v>
-      </c>
-      <c r="B974" t="s">
-        <v>581</v>
       </c>
       <c r="C974">
         <v>1</v>
@@ -63450,7 +63450,7 @@
     </row>
     <row r="975" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B975" t="s">
         <v>271</v>
@@ -63509,7 +63509,7 @@
     </row>
     <row r="976" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B976" t="s">
         <v>340</v>
@@ -63568,7 +63568,7 @@
     </row>
     <row r="977" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B977" t="s">
         <v>337</v>
@@ -63627,7 +63627,7 @@
     </row>
     <row r="978" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B978" t="s">
         <v>121</v>
@@ -63692,7 +63692,7 @@
     </row>
     <row r="979" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B979" t="s">
         <v>225</v>
@@ -63757,7 +63757,7 @@
     </row>
     <row r="980" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B980" t="s">
         <v>122</v>
@@ -63822,7 +63822,7 @@
     </row>
     <row r="981" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B981" t="s">
         <v>124</v>
@@ -63887,7 +63887,7 @@
     </row>
     <row r="982" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B982" t="s">
         <v>59</v>
@@ -63946,10 +63946,10 @@
     </row>
     <row r="983" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B983" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C983">
         <v>1</v>
@@ -64011,10 +64011,10 @@
     </row>
     <row r="984" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B984" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C984">
         <v>1</v>
@@ -64070,7 +64070,7 @@
     </row>
     <row r="985" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B985" t="s">
         <v>103</v>
@@ -64129,7 +64129,7 @@
     </row>
     <row r="986" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B986" t="s">
         <v>180</v>
@@ -64194,10 +64194,10 @@
     </row>
     <row r="987" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
+        <v>581</v>
+      </c>
+      <c r="B987" t="s">
         <v>582</v>
-      </c>
-      <c r="B987" t="s">
-        <v>583</v>
       </c>
       <c r="C987">
         <v>1</v>
@@ -64259,7 +64259,7 @@
     </row>
     <row r="988" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B988" t="s">
         <v>184</v>
@@ -64324,7 +64324,7 @@
     </row>
     <row r="989" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B989" t="s">
         <v>185</v>
@@ -64383,10 +64383,10 @@
     </row>
     <row r="990" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B990" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C990">
         <v>1</v>
@@ -64442,10 +64442,10 @@
     </row>
     <row r="991" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B991" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C991">
         <v>1</v>
@@ -64501,10 +64501,10 @@
     </row>
     <row r="992" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B992" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C992">
         <v>1</v>
@@ -64555,7 +64555,7 @@
         <v>1</v>
       </c>
       <c r="S992" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="T992" t="s">
         <v>24</v>
@@ -64566,10 +64566,10 @@
     </row>
     <row r="993" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B993" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C993">
         <v>1</v>
@@ -64631,10 +64631,10 @@
     </row>
     <row r="994" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B994" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C994">
         <v>1</v>
@@ -64685,7 +64685,7 @@
         <v>0</v>
       </c>
       <c r="S994" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T994" t="s">
         <v>42</v>
@@ -64696,7 +64696,7 @@
     </row>
     <row r="995" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B995" t="s">
         <v>111</v>
@@ -64761,10 +64761,10 @@
     </row>
     <row r="996" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B996" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C996">
         <v>1</v>
@@ -64820,10 +64820,10 @@
     </row>
     <row r="997" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
+        <v>586</v>
+      </c>
+      <c r="B997" t="s">
         <v>587</v>
-      </c>
-      <c r="B997" t="s">
-        <v>588</v>
       </c>
       <c r="C997">
         <v>1</v>
@@ -64885,7 +64885,7 @@
     </row>
     <row r="998" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B998" t="s">
         <v>104</v>
@@ -64950,7 +64950,7 @@
     </row>
     <row r="999" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B999" t="s">
         <v>397</v>
@@ -65015,7 +65015,7 @@
     </row>
     <row r="1000" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B1000" t="s">
         <v>277</v>
@@ -65074,7 +65074,7 @@
     </row>
     <row r="1001" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B1001" t="s">
         <v>161</v>
@@ -65133,7 +65133,7 @@
     </row>
     <row r="1002" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B1002" t="s">
         <v>108</v>
@@ -65198,10 +65198,10 @@
     </row>
     <row r="1003" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B1003" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C1003">
         <v>1</v>
@@ -65252,7 +65252,7 @@
         <v>0</v>
       </c>
       <c r="S1003" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="T1003" t="s">
         <v>24</v>
@@ -65263,10 +65263,10 @@
     </row>
     <row r="1004" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B1004" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C1004">
         <v>1</v>
@@ -65328,10 +65328,10 @@
     </row>
     <row r="1005" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B1005" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C1005">
         <v>1</v>
@@ -65393,7 +65393,7 @@
     </row>
     <row r="1006" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B1006" t="s">
         <v>169</v>
@@ -65452,7 +65452,7 @@
     </row>
     <row r="1007" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B1007" t="s">
         <v>363</v>
@@ -65511,7 +65511,7 @@
     </row>
     <row r="1008" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B1008" t="s">
         <v>267</v>
@@ -65576,7 +65576,7 @@
     </row>
     <row r="1009" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B1009" t="s">
         <v>174</v>
@@ -65635,10 +65635,10 @@
     </row>
     <row r="1010" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B1010" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C1010">
         <v>1</v>
@@ -65694,7 +65694,7 @@
     </row>
     <row r="1011" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B1011" t="s">
         <v>312</v>
@@ -65753,7 +65753,7 @@
     </row>
     <row r="1012" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B1012" t="s">
         <v>291</v>
@@ -65812,7 +65812,7 @@
     </row>
     <row r="1013" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B1013" t="s">
         <v>314</v>
@@ -65877,7 +65877,7 @@
     </row>
     <row r="1014" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B1014" t="s">
         <v>392</v>
@@ -65942,10 +65942,10 @@
     </row>
     <row r="1015" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B1015" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C1015">
         <v>1</v>
@@ -66001,10 +66001,10 @@
     </row>
     <row r="1016" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B1016" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C1016">
         <v>1</v>
@@ -66060,10 +66060,10 @@
     </row>
     <row r="1017" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
+        <v>591</v>
+      </c>
+      <c r="B1017" t="s">
         <v>592</v>
-      </c>
-      <c r="B1017" t="s">
-        <v>593</v>
       </c>
       <c r="C1017">
         <v>1</v>
@@ -66119,7 +66119,7 @@
     </row>
     <row r="1018" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B1018" t="s">
         <v>257</v>
@@ -66178,7 +66178,7 @@
     </row>
     <row r="1019" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B1019" t="s">
         <v>259</v>
@@ -66243,10 +66243,10 @@
     </row>
     <row r="1020" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B1020" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C1020">
         <v>1</v>
@@ -66308,10 +66308,10 @@
     </row>
     <row r="1021" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B1021" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C1021">
         <v>1</v>
@@ -66367,7 +66367,7 @@
     </row>
     <row r="1022" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B1022" t="s">
         <v>394</v>
@@ -66432,7 +66432,7 @@
     </row>
     <row r="1023" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B1023" t="s">
         <v>176</v>
@@ -66491,7 +66491,7 @@
     </row>
     <row r="1024" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B1024" t="s">
         <v>25</v>
@@ -66556,10 +66556,10 @@
     </row>
     <row r="1025" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B1025" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C1025">
         <v>1</v>
@@ -66621,7 +66621,7 @@
     </row>
     <row r="1026" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B1026" t="s">
         <v>205</v>
@@ -66686,7 +66686,7 @@
     </row>
     <row r="1027" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B1027" t="s">
         <v>183</v>
@@ -66751,10 +66751,10 @@
     </row>
     <row r="1028" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
+        <v>594</v>
+      </c>
+      <c r="B1028" t="s">
         <v>595</v>
-      </c>
-      <c r="B1028" t="s">
-        <v>596</v>
       </c>
       <c r="C1028">
         <v>1</v>
@@ -66810,7 +66810,7 @@
     </row>
     <row r="1029" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B1029" t="s">
         <v>120</v>
@@ -66869,10 +66869,10 @@
     </row>
     <row r="1030" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B1030" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C1030">
         <v>1</v>
@@ -66923,7 +66923,7 @@
         <v>1</v>
       </c>
       <c r="S1030" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="T1030" t="s">
         <v>24</v>
@@ -66934,7 +66934,7 @@
     </row>
     <row r="1031" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B1031" t="s">
         <v>188</v>
@@ -66993,10 +66993,10 @@
     </row>
     <row r="1032" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B1032" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C1032">
         <v>1</v>
@@ -67052,7 +67052,7 @@
     </row>
     <row r="1033" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B1033" t="s">
         <v>41</v>
@@ -67117,10 +67117,10 @@
     </row>
     <row r="1034" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B1034" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C1034">
         <v>1</v>
@@ -67176,7 +67176,7 @@
     </row>
     <row r="1035" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1035" t="s">
         <v>45</v>
@@ -67241,7 +67241,7 @@
     </row>
     <row r="1036" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1036" t="s">
         <v>114</v>
@@ -67300,7 +67300,7 @@
     </row>
     <row r="1037" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1037" t="s">
         <v>403</v>
@@ -67359,10 +67359,10 @@
     </row>
     <row r="1038" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1038" t="s">
         <v>599</v>
-      </c>
-      <c r="B1038" t="s">
-        <v>600</v>
       </c>
       <c r="C1038">
         <v>1</v>
@@ -67418,7 +67418,7 @@
     </row>
     <row r="1039" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1039" t="s">
         <v>246</v>
@@ -67477,10 +67477,10 @@
     </row>
     <row r="1040" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1040" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C1040">
         <v>1</v>
@@ -67536,7 +67536,7 @@
     </row>
     <row r="1041" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1041" t="s">
         <v>357</v>
@@ -67595,7 +67595,7 @@
     </row>
     <row r="1042" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1042" t="s">
         <v>122</v>
@@ -67660,7 +67660,7 @@
     </row>
     <row r="1043" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1043" t="s">
         <v>124</v>
@@ -67725,10 +67725,10 @@
     </row>
     <row r="1044" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1044" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C1044">
         <v>1</v>
@@ -67790,7 +67790,7 @@
     </row>
     <row r="1045" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1045" t="s">
         <v>60</v>
@@ -67855,7 +67855,7 @@
     </row>
     <row r="1046" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1046" t="s">
         <v>126</v>
@@ -67920,10 +67920,10 @@
     </row>
     <row r="1047" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1047" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C1047">
         <v>1</v>
@@ -67979,10 +67979,10 @@
     </row>
     <row r="1048" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B1048" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C1048">
         <v>1</v>
@@ -68044,7 +68044,7 @@
     </row>
     <row r="1049" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B1049" t="s">
         <v>202</v>
@@ -68103,7 +68103,7 @@
     </row>
     <row r="1050" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B1050" t="s">
         <v>204</v>
@@ -68168,10 +68168,10 @@
     </row>
     <row r="1051" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1051" t="s">
         <v>602</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>603</v>
       </c>
       <c r="C1051">
         <v>1</v>
@@ -68233,7 +68233,7 @@
     </row>
     <row r="1052" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1052" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B1052" t="s">
         <v>301</v>
@@ -68298,10 +68298,10 @@
     </row>
     <row r="1053" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1053" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B1053" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C1053">
         <v>1</v>
@@ -68363,7 +68363,7 @@
     </row>
     <row r="1054" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B1054" t="s">
         <v>208</v>
@@ -68422,7 +68422,7 @@
     </row>
     <row r="1055" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1055" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B1055" t="s">
         <v>184</v>
@@ -68487,7 +68487,7 @@
     </row>
     <row r="1056" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1056" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B1056" t="s">
         <v>185</v>
@@ -68552,7 +68552,7 @@
     </row>
     <row r="1057" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1057" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B1057" t="s">
         <v>212</v>
@@ -68617,7 +68617,7 @@
     </row>
     <row r="1058" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1058" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B1058" t="s">
         <v>266</v>
@@ -68676,7 +68676,7 @@
     </row>
     <row r="1059" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1059" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B1059" t="s">
         <v>215</v>
@@ -68741,7 +68741,7 @@
     </row>
     <row r="1060" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1060" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B1060" t="s">
         <v>114</v>
@@ -68806,7 +68806,7 @@
     </row>
     <row r="1061" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1061" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B1061" t="s">
         <v>202</v>
@@ -68871,7 +68871,7 @@
     </row>
     <row r="1062" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B1062" t="s">
         <v>204</v>
@@ -68930,7 +68930,7 @@
     </row>
     <row r="1063" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1063" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B1063" t="s">
         <v>271</v>
@@ -68995,7 +68995,7 @@
     </row>
     <row r="1064" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1064" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B1064" t="s">
         <v>301</v>
@@ -69028,10 +69028,10 @@
         <v>0</v>
       </c>
       <c r="M1064" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="N1064" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="O1064">
         <v>24</v>
@@ -69054,7 +69054,7 @@
     </row>
     <row r="1065" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1065" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B1065" t="s">
         <v>121</v>
@@ -69113,7 +69113,7 @@
     </row>
     <row r="1066" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1066" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B1066" t="s">
         <v>122</v>
@@ -69178,10 +69178,10 @@
     </row>
     <row r="1067" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1067" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B1067" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C1067">
         <v>1</v>
@@ -69237,7 +69237,7 @@
     </row>
     <row r="1068" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1068" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B1068" t="s">
         <v>124</v>
@@ -69302,7 +69302,7 @@
     </row>
     <row r="1069" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1069" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B1069" t="s">
         <v>212</v>
@@ -69367,7 +69367,7 @@
     </row>
     <row r="1070" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1070" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B1070" t="s">
         <v>215</v>
@@ -69426,10 +69426,10 @@
     </row>
     <row r="1071" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B1071" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C1071">
         <v>1</v>

--- a/NV Play Midweek League bowling stats for season.xlsx
+++ b/NV Play Midweek League bowling stats for season.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,114 +429,138 @@
   </sheetPr>
   <dimension ref="A1:V1071"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="108" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Bowler</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Bowler ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Innings</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Overs</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Maidens</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Runs</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Wickets</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Runs Per Over</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Five Wickets in an Innings</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Ten Wickets in a Match</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Best Bowling in an Innings</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Best Bowling in a Match</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Balls</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Dots</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Fours</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Sixes</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Wides</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>No Balls</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Strike Rate</t>
         </is>
